--- a/outputs/results/experiment_results.xlsx
+++ b/outputs/results/experiment_results.xlsx
@@ -485,16 +485,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9400524025013067</v>
+        <v>0.733368061432884</v>
       </c>
       <c r="E2" t="n">
-        <v>3057.668066619196</v>
+        <v>8.555283320243431</v>
       </c>
       <c r="F2" t="n">
-        <v>22.46785853774004</v>
+        <v>1.463298633245535</v>
       </c>
       <c r="G2" t="n">
-        <v>44.65114642803684</v>
+        <v>2.895187190544179</v>
       </c>
     </row>
     <row r="3">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9427850960020662</v>
+        <v>0.6852030422576633</v>
       </c>
       <c r="E3" t="n">
-        <v>2918.285172195241</v>
+        <v>10.1007297786963</v>
       </c>
       <c r="F3" t="n">
-        <v>20.63634100754798</v>
+        <v>1.568593510175373</v>
       </c>
       <c r="G3" t="n">
-        <v>43.6253308071083</v>
+        <v>3.159145842460453</v>
       </c>
     </row>
     <row r="4">
@@ -543,16 +543,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.963792394625171</v>
+        <v>0.7764012790623055</v>
       </c>
       <c r="E4" t="n">
-        <v>1846.793588780228</v>
+        <v>7.174498366348186</v>
       </c>
       <c r="F4" t="n">
-        <v>17.90781735564331</v>
+        <v>1.429222463682855</v>
       </c>
       <c r="G4" t="n">
-        <v>35.69801008673765</v>
+        <v>2.619990435461164</v>
       </c>
     </row>
     <row r="5">
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9466658288980833</v>
+        <v>0.7407147505087405</v>
       </c>
       <c r="E5" t="n">
-        <v>2720.34574599074</v>
+        <v>8.31955384669476</v>
       </c>
       <c r="F5" t="n">
-        <v>19.99613833495851</v>
+        <v>1.441703872441011</v>
       </c>
       <c r="G5" t="n">
-        <v>41.39726523882003</v>
+        <v>2.865058721993581</v>
       </c>
     </row>
     <row r="6">
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9513058097643931</v>
+        <v>0.6911591780723104</v>
       </c>
       <c r="E6" t="n">
-        <v>2483.68035960976</v>
+        <v>9.909618279968889</v>
       </c>
       <c r="F6" t="n">
-        <v>18.09348701917582</v>
+        <v>1.546210280876772</v>
       </c>
       <c r="G6" t="n">
-        <v>39.81974937098362</v>
+        <v>3.133798531754253</v>
       </c>
     </row>
     <row r="7">
@@ -630,16 +630,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9695474122790002</v>
+        <v>0.7849271941101076</v>
       </c>
       <c r="E7" t="n">
-        <v>1553.254991118708</v>
+        <v>6.900931669161561</v>
       </c>
       <c r="F7" t="n">
-        <v>15.87065484267502</v>
+        <v>1.400113275166756</v>
       </c>
       <c r="G7" t="n">
-        <v>32.70180316085346</v>
+        <v>2.580592573269357</v>
       </c>
     </row>
     <row r="8">
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9193125987211891</v>
+        <v>0.7320762222060214</v>
       </c>
       <c r="E8" t="n">
-        <v>3990.849161155916</v>
+        <v>8.240218765152733</v>
       </c>
       <c r="F8" t="n">
-        <v>26.31760663036128</v>
+        <v>1.44093578175406</v>
       </c>
       <c r="G8" t="n">
-        <v>58.51005171721292</v>
+        <v>2.838507130599666</v>
       </c>
     </row>
     <row r="9">
@@ -688,16 +688,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.917014295954912</v>
+        <v>0.7064190493997634</v>
       </c>
       <c r="E9" t="n">
-        <v>4104.524648549364</v>
+        <v>9.029326467946719</v>
       </c>
       <c r="F9" t="n">
-        <v>32.61942001804984</v>
+        <v>1.478296044076899</v>
       </c>
       <c r="G9" t="n">
-        <v>62.09582286703966</v>
+        <v>2.978060400418576</v>
       </c>
     </row>
     <row r="10">
@@ -717,16 +717,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9357779178617291</v>
+        <v>0.7674017976689097</v>
       </c>
       <c r="E10" t="n">
-        <v>3176.464213335757</v>
+        <v>7.153751292142754</v>
       </c>
       <c r="F10" t="n">
-        <v>29.48760898456907</v>
+        <v>1.43326579582687</v>
       </c>
       <c r="G10" t="n">
-        <v>55.35240273556689</v>
+        <v>2.617140378051686</v>
       </c>
     </row>
     <row r="11">
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9260997211236156</v>
+        <v>0.7432601860868605</v>
       </c>
       <c r="E11" t="n">
-        <v>3655.153856596648</v>
+        <v>7.896246648163004</v>
       </c>
       <c r="F11" t="n">
-        <v>23.85437681783542</v>
+        <v>1.409498141062684</v>
       </c>
       <c r="G11" t="n">
-        <v>55.7188977031609</v>
+        <v>2.788599287220091</v>
       </c>
     </row>
     <row r="12">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9248090927727247</v>
+        <v>0.7131307929136529</v>
       </c>
       <c r="E12" t="n">
-        <v>3718.989139303541</v>
+        <v>8.822901210340165</v>
       </c>
       <c r="F12" t="n">
-        <v>30.51337015891831</v>
+        <v>1.459813297914285</v>
       </c>
       <c r="G12" t="n">
-        <v>59.50882663689752</v>
+        <v>2.950977042970826</v>
       </c>
     </row>
     <row r="13">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9423911539890023</v>
+        <v>0.7739393101809262</v>
       </c>
       <c r="E13" t="n">
-        <v>2849.369432332012</v>
+        <v>6.952684654002248</v>
       </c>
       <c r="F13" t="n">
-        <v>27.61053877096225</v>
+        <v>1.415710792057568</v>
       </c>
       <c r="G13" t="n">
-        <v>52.65421454147967</v>
+        <v>2.591069203314092</v>
       </c>
     </row>
     <row r="14">
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.9067166832452848</v>
+        <v>0.7293008737369711</v>
       </c>
       <c r="E14" t="n">
-        <v>4613.850991854412</v>
+        <v>8.325576917097322</v>
       </c>
       <c r="F14" t="n">
-        <v>33.09018958857911</v>
+        <v>1.445064357889944</v>
       </c>
       <c r="G14" t="n">
-        <v>66.93245573310473</v>
+        <v>2.854199239187755</v>
       </c>
     </row>
     <row r="15">
@@ -862,16 +862,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.9319215243498019</v>
+        <v>0.7033062237519566</v>
       </c>
       <c r="E15" t="n">
-        <v>3367.203840194993</v>
+        <v>9.12506401138876</v>
       </c>
       <c r="F15" t="n">
-        <v>28.32376973605673</v>
+        <v>1.475982283772601</v>
       </c>
       <c r="G15" t="n">
-        <v>54.33970274623579</v>
+        <v>2.997625085471234</v>
       </c>
     </row>
     <row r="16">
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.9466272524076675</v>
+        <v>0.7692721169045366</v>
       </c>
       <c r="E16" t="n">
-        <v>2639.849364108622</v>
+        <v>7.096228067481114</v>
       </c>
       <c r="F16" t="n">
-        <v>26.36520328300487</v>
+        <v>1.413162110098043</v>
       </c>
       <c r="G16" t="n">
-        <v>49.2444168600821</v>
+        <v>2.60192706214428</v>
       </c>
     </row>
     <row r="17">
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.9137066934205937</v>
+        <v>0.7380617308509502</v>
       </c>
       <c r="E17" t="n">
-        <v>4268.120731584791</v>
+        <v>8.05612946534877</v>
       </c>
       <c r="F17" t="n">
-        <v>30.71221362696329</v>
+        <v>1.417949268469599</v>
       </c>
       <c r="G17" t="n">
-        <v>64.04294507781132</v>
+        <v>2.817773466350075</v>
       </c>
     </row>
     <row r="18">
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9415305823649159</v>
+        <v>0.7073091198115176</v>
       </c>
       <c r="E18" t="n">
-        <v>2891.933841269067</v>
+        <v>9.001951611673668</v>
       </c>
       <c r="F18" t="n">
-        <v>25.6530400203458</v>
+        <v>1.4616654584226</v>
       </c>
       <c r="G18" t="n">
-        <v>50.49852431707163</v>
+        <v>2.982283718140724</v>
       </c>
     </row>
     <row r="19">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.953006549040607</v>
+        <v>0.7763307361005394</v>
       </c>
       <c r="E19" t="n">
-        <v>2324.325376313314</v>
+        <v>6.879134359584474</v>
       </c>
       <c r="F19" t="n">
-        <v>24.43126915109069</v>
+        <v>1.393583149101872</v>
       </c>
       <c r="G19" t="n">
-        <v>46.39346923403826</v>
+        <v>2.572550339874818</v>
       </c>
     </row>
     <row r="20">
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9310198126487043</v>
+        <v>0.7324912709541652</v>
       </c>
       <c r="E20" t="n">
-        <v>3411.803062984374</v>
+        <v>8.22745359547997</v>
       </c>
       <c r="F20" t="n">
-        <v>29.37108466055779</v>
+        <v>1.440764714983661</v>
       </c>
       <c r="G20" t="n">
-        <v>54.52890935964203</v>
+        <v>2.835170217281133</v>
       </c>
     </row>
     <row r="21">
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.9325137063882778</v>
+        <v>0.6978866920398582</v>
       </c>
       <c r="E21" t="n">
-        <v>3337.914147454283</v>
+        <v>9.291746219590211</v>
       </c>
       <c r="F21" t="n">
-        <v>27.35153989862451</v>
+        <v>1.479639060105246</v>
       </c>
       <c r="G21" t="n">
-        <v>53.54919330984362</v>
+        <v>3.024820793965154</v>
       </c>
     </row>
     <row r="22">
@@ -1065,16 +1065,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.9498129760641559</v>
+        <v>0.7706212667568185</v>
       </c>
       <c r="E22" t="n">
-        <v>2482.281486339957</v>
+        <v>7.054733840946562</v>
       </c>
       <c r="F22" t="n">
-        <v>25.34034214638625</v>
+        <v>1.413550598186365</v>
       </c>
       <c r="G22" t="n">
-        <v>46.89981173914331</v>
+        <v>2.595696349049179</v>
       </c>
     </row>
     <row r="23">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.9383999146022495</v>
+        <v>0.7413085705532879</v>
       </c>
       <c r="E23" t="n">
-        <v>3046.778620211979</v>
+        <v>7.956270208126668</v>
       </c>
       <c r="F23" t="n">
-        <v>26.964053690793</v>
+        <v>1.414562050415189</v>
       </c>
       <c r="G23" t="n">
-        <v>51.1900701821551</v>
+        <v>2.798125123197345</v>
       </c>
     </row>
     <row r="24">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.9421554037818729</v>
+        <v>0.7018727905804635</v>
       </c>
       <c r="E24" t="n">
-        <v>2861.029784523967</v>
+        <v>9.169150441550304</v>
       </c>
       <c r="F24" t="n">
-        <v>24.68278123092892</v>
+        <v>1.468798166636697</v>
       </c>
       <c r="G24" t="n">
-        <v>49.64595605487151</v>
+        <v>3.009160809895652</v>
       </c>
     </row>
     <row r="25">
@@ -1152,16 +1152,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.9563890451304977</v>
+        <v>0.7780715702241299</v>
       </c>
       <c r="E25" t="n">
-        <v>2157.025011336774</v>
+        <v>6.825593557307276</v>
       </c>
       <c r="F25" t="n">
-        <v>23.29973407881866</v>
+        <v>1.390597494698184</v>
       </c>
       <c r="G25" t="n">
-        <v>43.93143584710798</v>
+        <v>2.563920527182227</v>
       </c>
     </row>
   </sheetData>
@@ -1238,20 +1238,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9968030257619088</v>
+        <v>0.7936758319455359</v>
       </c>
       <c r="F2" t="n">
-        <v>163.0638498536798</v>
+        <v>6.620218579234972</v>
       </c>
       <c r="G2" t="n">
-        <v>7.426836556833519</v>
+        <v>1.213114754098361</v>
       </c>
       <c r="H2" t="n">
-        <v>12.76964564323066</v>
+        <v>2.572978542319188</v>
       </c>
     </row>
     <row r="3">
@@ -1272,20 +1272,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9972973126772772</v>
+        <v>0.7504037911645353</v>
       </c>
       <c r="F3" t="n">
-        <v>137.8524088630288</v>
+        <v>8.008666530054645</v>
       </c>
       <c r="G3" t="n">
-        <v>6.625282860391049</v>
+        <v>1.263032786885246</v>
       </c>
       <c r="H3" t="n">
-        <v>11.74105654798702</v>
+        <v>2.829958750592426</v>
       </c>
     </row>
     <row r="4">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9972677616852671</v>
+        <v>0.8463079264905765</v>
       </c>
       <c r="F4" t="n">
-        <v>139.3596773504461</v>
+        <v>4.9314393467451</v>
       </c>
       <c r="G4" t="n">
-        <v>6.68854863026555</v>
+        <v>1.164602598191787</v>
       </c>
       <c r="H4" t="n">
-        <v>11.80506998498722</v>
+        <v>2.22068443204907</v>
       </c>
     </row>
     <row r="5">
@@ -1340,20 +1340,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9969259615900878</v>
+        <v>0.789886551929678</v>
       </c>
       <c r="F5" t="n">
-        <v>156.7934241527199</v>
+        <v>6.741803278688525</v>
       </c>
       <c r="G5" t="n">
-        <v>7.002518468853983</v>
+        <v>1.237704918032787</v>
       </c>
       <c r="H5" t="n">
-        <v>12.5217180990757</v>
+        <v>2.596498272421633</v>
       </c>
     </row>
     <row r="6">
@@ -1374,20 +1374,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.9972973126772772</v>
+        <v>0.7509333068569984</v>
       </c>
       <c r="F6" t="n">
-        <v>137.8524088630282</v>
+        <v>7.991676229508196</v>
       </c>
       <c r="G6" t="n">
-        <v>6.62528286039106</v>
+        <v>1.25792349726776</v>
       </c>
       <c r="H6" t="n">
-        <v>11.74105654798699</v>
+        <v>2.826955293156967</v>
       </c>
     </row>
     <row r="7">
@@ -1408,20 +1408,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.997245856335843</v>
+        <v>0.8478753090262897</v>
       </c>
       <c r="F7" t="n">
-        <v>140.4769746270178</v>
+        <v>4.881147540983607</v>
       </c>
       <c r="G7" t="n">
-        <v>6.831806279507489</v>
+        <v>1.199453551912568</v>
       </c>
       <c r="H7" t="n">
-        <v>11.85229828459518</v>
+        <v>2.209331921867696</v>
       </c>
     </row>
     <row r="8">
@@ -1442,20 +1442,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9749808671534098</v>
+        <v>0.7948003355139387</v>
       </c>
       <c r="F8" t="n">
-        <v>1237.461905467063</v>
+        <v>6.311086458333333</v>
       </c>
       <c r="G8" t="n">
-        <v>12.12123151748791</v>
+        <v>1.153541666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>35.17757674239462</v>
+        <v>2.512187584224819</v>
       </c>
     </row>
     <row r="9">
@@ -1476,20 +1476,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9627060387527511</v>
+        <v>0.7755831248131256</v>
       </c>
       <c r="F9" t="n">
-        <v>1844.582569284575</v>
+        <v>6.902127766927083</v>
       </c>
       <c r="G9" t="n">
-        <v>27.28880704013617</v>
+        <v>1.1646484375</v>
       </c>
       <c r="H9" t="n">
-        <v>42.9486038106546</v>
+        <v>2.62719008960659</v>
       </c>
     </row>
     <row r="10">
@@ -1510,20 +1510,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.962861364586194</v>
+        <v>0.8566073981701908</v>
       </c>
       <c r="F10" t="n">
-        <v>1836.90005674511</v>
+        <v>4.410158807519707</v>
       </c>
       <c r="G10" t="n">
-        <v>26.06824607364064</v>
+        <v>1.154289717120984</v>
       </c>
       <c r="H10" t="n">
-        <v>42.85907204717701</v>
+        <v>2.100037810973818</v>
       </c>
     </row>
     <row r="11">
@@ -1544,20 +1544,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9746390483194954</v>
+        <v>0.7904146666513786</v>
       </c>
       <c r="F11" t="n">
-        <v>1254.368478054286</v>
+        <v>6.445971354166666</v>
       </c>
       <c r="G11" t="n">
-        <v>12.036712800716</v>
+        <v>1.161822916666667</v>
       </c>
       <c r="H11" t="n">
-        <v>35.41706478597974</v>
+        <v>2.538891757079586</v>
       </c>
     </row>
     <row r="12">
@@ -1578,20 +1578,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9581711170680989</v>
+        <v>0.7751458559530351</v>
       </c>
       <c r="F12" t="n">
-        <v>2068.882622505585</v>
+        <v>6.915576334635417</v>
       </c>
       <c r="G12" t="n">
-        <v>28.10710183201993</v>
+        <v>1.1662890625</v>
       </c>
       <c r="H12" t="n">
-        <v>45.48497139171999</v>
+        <v>2.62974834055189</v>
       </c>
     </row>
     <row r="13">
@@ -1612,20 +1612,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9621938552042105</v>
+        <v>0.8566073981701908</v>
       </c>
       <c r="F13" t="n">
-        <v>1869.915486848594</v>
+        <v>4.410158807519707</v>
       </c>
       <c r="G13" t="n">
-        <v>26.24478112569607</v>
+        <v>1.154289717120984</v>
       </c>
       <c r="H13" t="n">
-        <v>43.24251943225087</v>
+        <v>2.100037810973818</v>
       </c>
     </row>
     <row r="14">
@@ -1646,20 +1646,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9480502444468</v>
+        <v>0.7949206506006881</v>
       </c>
       <c r="F14" t="n">
-        <v>2569.46729087665</v>
+        <v>6.307386067708333</v>
       </c>
       <c r="G14" t="n">
-        <v>26.68645472638144</v>
+        <v>1.138255208333333</v>
       </c>
       <c r="H14" t="n">
-        <v>50.68991310780331</v>
+        <v>2.511450988514077</v>
       </c>
     </row>
     <row r="15">
@@ -1680,20 +1680,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9786139704310023</v>
+        <v>0.7680467408509526</v>
       </c>
       <c r="F15" t="n">
-        <v>1057.766352778835</v>
+        <v>7.13391552782618</v>
       </c>
       <c r="G15" t="n">
-        <v>20.80181794455994</v>
+        <v>1.215330930315326</v>
       </c>
       <c r="H15" t="n">
-        <v>32.5233201376925</v>
+        <v>2.67093907227892</v>
       </c>
     </row>
     <row r="16">
@@ -1714,20 +1714,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9784240338587937</v>
+        <v>0.8751068639258174</v>
       </c>
       <c r="F16" t="n">
-        <v>1067.160734031146</v>
+        <v>3.841192342057154</v>
       </c>
       <c r="G16" t="n">
-        <v>20.66692551850902</v>
+        <v>1.033516532165777</v>
       </c>
       <c r="H16" t="n">
-        <v>32.66742619232721</v>
+        <v>1.959896002867793</v>
       </c>
     </row>
     <row r="17">
@@ -1748,20 +1748,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9509012393094327</v>
+        <v>0.7908109329563064</v>
       </c>
       <c r="F17" t="n">
-        <v>2428.455307894545</v>
+        <v>6.433783854166666</v>
       </c>
       <c r="G17" t="n">
-        <v>33.12930427712962</v>
+        <v>1.148489583333333</v>
       </c>
       <c r="H17" t="n">
-        <v>49.27935985678532</v>
+        <v>2.536490460097705</v>
       </c>
     </row>
     <row r="18">
@@ -1782,20 +1782,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9786105007881604</v>
+        <v>0.7680467408509526</v>
       </c>
       <c r="F18" t="n">
-        <v>1057.93796347649</v>
+        <v>7.13391552782618</v>
       </c>
       <c r="G18" t="n">
-        <v>20.78242828799679</v>
+        <v>1.215330930315326</v>
       </c>
       <c r="H18" t="n">
-        <v>32.52595830220056</v>
+        <v>2.67093907227892</v>
       </c>
     </row>
     <row r="19">
@@ -1816,20 +1816,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9778512375228939</v>
+        <v>0.8751068639258174</v>
       </c>
       <c r="F19" t="n">
-        <v>1095.49159783899</v>
+        <v>3.841192342057154</v>
       </c>
       <c r="G19" t="n">
-        <v>20.82995426808088</v>
+        <v>1.033516532165777</v>
       </c>
       <c r="H19" t="n">
-        <v>33.09821139939423</v>
+        <v>1.959896002867793</v>
       </c>
     </row>
     <row r="20">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9775682015296455</v>
+        <v>0.7973142438510242</v>
       </c>
       <c r="F20" t="n">
-        <v>1109.490734486471</v>
+        <v>6.23376911523042</v>
       </c>
       <c r="G20" t="n">
-        <v>21.48172122022829</v>
+        <v>1.19337943048716</v>
       </c>
       <c r="H20" t="n">
-        <v>33.30901881602746</v>
+        <v>2.496751712772101</v>
       </c>
     </row>
     <row r="21">
@@ -1884,20 +1884,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9801142102757231</v>
+        <v>0.7692910985611885</v>
       </c>
       <c r="F21" t="n">
-        <v>983.5635549325143</v>
+        <v>7.095644270833335</v>
       </c>
       <c r="G21" t="n">
-        <v>19.58033015126376</v>
+        <v>1.176145833333333</v>
       </c>
       <c r="H21" t="n">
-        <v>31.36181683086161</v>
+        <v>2.663765055486939</v>
       </c>
     </row>
     <row r="22">
@@ -1918,20 +1918,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9821877748561016</v>
+        <v>0.8561937158488717</v>
       </c>
       <c r="F22" t="n">
-        <v>881.0037582969538</v>
+        <v>4.422881951598273</v>
       </c>
       <c r="G22" t="n">
-        <v>19.64468059556231</v>
+        <v>1.131402354048381</v>
       </c>
       <c r="H22" t="n">
-        <v>29.68170746936493</v>
+        <v>2.103064894766272</v>
       </c>
     </row>
     <row r="23">
@@ -1952,20 +1952,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9779744982144261</v>
+        <v>0.7973142438510242</v>
       </c>
       <c r="F23" t="n">
-        <v>1089.395047205211</v>
+        <v>6.23376911523042</v>
       </c>
       <c r="G23" t="n">
-        <v>21.49271004844468</v>
+        <v>1.19337943048716</v>
       </c>
       <c r="H23" t="n">
-        <v>33.00598502098082</v>
+        <v>2.496751712772101</v>
       </c>
     </row>
     <row r="24">
@@ -1986,20 +1986,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9798133671776948</v>
+        <v>0.7695029147552926</v>
       </c>
       <c r="F24" t="n">
-        <v>998.4434420818937</v>
+        <v>7.089129687500001</v>
       </c>
       <c r="G24" t="n">
-        <v>19.75334525356408</v>
+        <v>1.180625</v>
       </c>
       <c r="H24" t="n">
-        <v>31.59815567532215</v>
+        <v>2.662541959763264</v>
       </c>
     </row>
     <row r="25">
@@ -2020,20 +2020,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9819215517886639</v>
+        <v>0.8561937158488717</v>
       </c>
       <c r="F25" t="n">
-        <v>894.1713171540425</v>
+        <v>4.422881951598273</v>
       </c>
       <c r="G25" t="n">
-        <v>19.62671109358642</v>
+        <v>1.131402354048381</v>
       </c>
       <c r="H25" t="n">
-        <v>29.90269748959185</v>
+        <v>2.103064894766272</v>
       </c>
     </row>
   </sheetData>
@@ -2095,20 +2095,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2339.693751774852</v>
+        <v>14.40607454541022</v>
       </c>
       <c r="C2" t="n">
-        <v>48.37038093477094</v>
+        <v>3.795533499445133</v>
       </c>
       <c r="D2" t="n">
-        <v>29.56963542539033</v>
+        <v>2.435095392676823</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9526958296353389</v>
+        <v>0.5315986109846396</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2129,20 +2129,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2304.405630123703</v>
+        <v>6.902127766927083</v>
       </c>
       <c r="C3" t="n">
-        <v>48.00422512783332</v>
+        <v>2.62719008960659</v>
       </c>
       <c r="D3" t="n">
-        <v>29.32582353475414</v>
+        <v>1.1646484375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9534092885301916</v>
+        <v>0.7755831248131256</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2163,20 +2163,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1844.582569284575</v>
+        <v>7.319483537008693</v>
       </c>
       <c r="C4" t="n">
-        <v>42.9486038106546</v>
+        <v>2.705454404902935</v>
       </c>
       <c r="D4" t="n">
-        <v>27.28880704013617</v>
+        <v>1.23125584959547</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9627060387527511</v>
+        <v>0.7620131532151315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2197,20 +2197,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6251.652908487443</v>
+        <v>9.495694620935367</v>
       </c>
       <c r="C5" t="n">
-        <v>79.06739472429481</v>
+        <v>3.081508497625046</v>
       </c>
       <c r="D5" t="n">
-        <v>54.33260359116993</v>
+        <v>1.335213431573142</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8736034346292186</v>
+        <v>0.6912554814226696</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2231,20 +2231,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5873.697014141942</v>
+        <v>7.203620004065621</v>
       </c>
       <c r="C6" t="n">
-        <v>76.64004836990867</v>
+        <v>2.683956036164829</v>
       </c>
       <c r="D6" t="n">
-        <v>27.50051918228389</v>
+        <v>1.245229819782624</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8812449860087036</v>
+        <v>0.7657803584725869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2265,20 +2265,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6013.116017483667</v>
+        <v>8.848958333333334</v>
       </c>
       <c r="C7" t="n">
-        <v>77.54428423477559</v>
+        <v>2.974719874766922</v>
       </c>
       <c r="D7" t="n">
-        <v>27.69913133456464</v>
+        <v>1.458333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8784261981732677</v>
+        <v>0.712283567490428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2299,20 +2299,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1272.36910675329</v>
+        <v>14.13028773425243</v>
       </c>
       <c r="C8" t="n">
-        <v>35.67028324464623</v>
+        <v>3.759027498469842</v>
       </c>
       <c r="D8" t="n">
-        <v>11.97506146991439</v>
+        <v>2.438865982668724</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9742751097459096</v>
+        <v>0.5405655870343075</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2333,20 +2333,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1237.461905467063</v>
+        <v>6.311086458333333</v>
       </c>
       <c r="C9" t="n">
-        <v>35.17757674239462</v>
+        <v>2.512187584224819</v>
       </c>
       <c r="D9" t="n">
-        <v>12.12123151748791</v>
+        <v>1.153541666666667</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9749808671534098</v>
+        <v>0.7948003355139387</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2367,20 +2367,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1282.529577956812</v>
+        <v>8.03876522838754</v>
       </c>
       <c r="C10" t="n">
-        <v>35.812422117986</v>
+        <v>2.8352716322052</v>
       </c>
       <c r="D10" t="n">
-        <v>12.26273105776196</v>
+        <v>1.275286307077897</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9740696842877991</v>
+        <v>0.7386263144011876</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2401,20 +2401,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4730.87171459912</v>
+        <v>6.446006526491225</v>
       </c>
       <c r="C11" t="n">
-        <v>68.78133260267003</v>
+        <v>2.538898683778308</v>
       </c>
       <c r="D11" t="n">
-        <v>48.08978948309656</v>
+        <v>1.205196075450658</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9043507461645399</v>
+        <v>0.7904135230528482</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2435,20 +2435,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7593.152785930693</v>
+        <v>6.831572893451869</v>
       </c>
       <c r="C12" t="n">
-        <v>87.13869855541046</v>
+        <v>2.613727777227741</v>
       </c>
       <c r="D12" t="n">
-        <v>36.16598447712418</v>
+        <v>1.268037158660416</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8464808513002643</v>
+        <v>0.7778771571418783</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7828.709876228519</v>
+        <v>7.68359375</v>
       </c>
       <c r="C13" t="n">
-        <v>88.47999704017015</v>
+        <v>2.771929607692086</v>
       </c>
       <c r="D13" t="n">
-        <v>37.29084177678266</v>
+        <v>1.3046875</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8417183336752121</v>
+        <v>0.7501744160919682</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2503,20 +2503,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2129.426643550205</v>
+        <v>14.27864696464104</v>
       </c>
       <c r="C14" t="n">
-        <v>46.14571099842547</v>
+        <v>3.778709695734912</v>
       </c>
       <c r="D14" t="n">
-        <v>27.65282179498815</v>
+        <v>2.47394704184728</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9569470317860469</v>
+        <v>0.5357418115243153</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2537,20 +2537,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2111.578763766649</v>
+        <v>4.873335819010416</v>
       </c>
       <c r="C15" t="n">
-        <v>45.95191795525676</v>
+        <v>2.207563321630982</v>
       </c>
       <c r="D15" t="n">
-        <v>27.51354728976288</v>
+        <v>1.123299479166667</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9573078820662552</v>
+        <v>0.8415475874730879</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2571,20 +2571,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1836.90005674511</v>
+        <v>6.967877549695356</v>
       </c>
       <c r="C16" t="n">
-        <v>42.85907204717701</v>
+        <v>2.639673758193493</v>
       </c>
       <c r="D16" t="n">
-        <v>26.06824607364064</v>
+        <v>1.306788287971697</v>
       </c>
       <c r="E16" t="n">
-        <v>0.962861364586194</v>
+        <v>0.7734453259645191</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2605,20 +2605,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4690.268689201071</v>
+        <v>4.410158807519707</v>
       </c>
       <c r="C17" t="n">
-        <v>68.4855363503935</v>
+        <v>2.100037810973818</v>
       </c>
       <c r="D17" t="n">
-        <v>47.07922719521388</v>
+        <v>1.154289717120984</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9051716623332876</v>
+        <v>0.8566073981701908</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2639,20 +2639,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3825.608996049128</v>
+        <v>6.509676111990011</v>
       </c>
       <c r="C18" t="n">
-        <v>61.85150762955683</v>
+        <v>2.551406692785376</v>
       </c>
       <c r="D18" t="n">
-        <v>23.9998624259286</v>
+        <v>1.239186915521258</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9226534414769415</v>
+        <v>0.7883433600676675</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2673,20 +2673,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4465.002130702383</v>
+        <v>5.8828125</v>
       </c>
       <c r="C19" t="n">
-        <v>66.82067143259175</v>
+        <v>2.425450988991532</v>
       </c>
       <c r="D19" t="n">
-        <v>24.61194912788026</v>
+        <v>1.302083333333333</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9097261249216496</v>
+        <v>0.8087253028136777</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2707,20 +2707,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2339.69375177486</v>
+        <v>13.02943564528436</v>
       </c>
       <c r="C20" t="n">
-        <v>48.37038093477102</v>
+        <v>3.609630956937891</v>
       </c>
       <c r="D20" t="n">
-        <v>29.56963542539033</v>
+        <v>2.298979634380527</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9526958296353388</v>
+        <v>0.5763588661783052</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2332.430711635872</v>
+        <v>6.915576334635417</v>
       </c>
       <c r="C21" t="n">
-        <v>48.29524522803329</v>
+        <v>2.62974834055189</v>
       </c>
       <c r="D21" t="n">
-        <v>29.48653691627832</v>
+        <v>1.1662890625</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9528426745323855</v>
+        <v>0.7751458559530351</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2775,20 +2775,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2068.882622505585</v>
+        <v>7.319483537008693</v>
       </c>
       <c r="C22" t="n">
-        <v>45.48497139171999</v>
+        <v>2.705454404902935</v>
       </c>
       <c r="D22" t="n">
-        <v>28.10710183201993</v>
+        <v>1.23125584959547</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9581711170680989</v>
+        <v>0.7620131532151315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2809,20 +2809,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3688.83419040284</v>
+        <v>9.495694620935367</v>
       </c>
       <c r="C23" t="n">
-        <v>60.73577356387947</v>
+        <v>3.081508497625046</v>
       </c>
       <c r="D23" t="n">
-        <v>40.64648520124256</v>
+        <v>1.335213431573142</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9254187686497723</v>
+        <v>0.6912554814226696</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2843,20 +2843,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5870.977542018424</v>
+        <v>7.201956707510487</v>
       </c>
       <c r="C24" t="n">
-        <v>76.62230446820575</v>
+        <v>2.683646159148126</v>
       </c>
       <c r="D24" t="n">
-        <v>27.57133024401406</v>
+        <v>1.245370976103236</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8812999685774844</v>
+        <v>0.7658344391601686</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2877,20 +2877,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6013.116017483667</v>
+        <v>8.975260416666666</v>
       </c>
       <c r="C25" t="n">
-        <v>77.54428423477559</v>
+        <v>2.995873898659065</v>
       </c>
       <c r="D25" t="n">
-        <v>27.69913133456464</v>
+        <v>1.481770833333333</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8784261981732677</v>
+        <v>0.7081769615526075</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2911,20 +2911,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1272.369106753291</v>
+        <v>12.45786590105087</v>
       </c>
       <c r="C26" t="n">
-        <v>35.67028324464624</v>
+        <v>3.529570214778404</v>
       </c>
       <c r="D26" t="n">
-        <v>11.97506146991436</v>
+        <v>2.274010389056618</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9742751097459095</v>
+        <v>0.594942975352127</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2945,20 +2945,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1254.368478054286</v>
+        <v>6.445971354166666</v>
       </c>
       <c r="C27" t="n">
-        <v>35.41706478597974</v>
+        <v>2.538891757079586</v>
       </c>
       <c r="D27" t="n">
-        <v>12.036712800716</v>
+        <v>1.161822916666667</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9746390483194954</v>
+        <v>0.7904146666513786</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,20 +2979,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1290.191153983966</v>
+        <v>8.039008691173741</v>
       </c>
       <c r="C28" t="n">
-        <v>35.91923097706806</v>
+        <v>2.83531456652939</v>
       </c>
       <c r="D28" t="n">
-        <v>11.83298511175455</v>
+        <v>1.275678326307649</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9739147817509284</v>
+        <v>0.738618398413604</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3013,20 +3013,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2642.13494376257</v>
+        <v>6.446006526491225</v>
       </c>
       <c r="C29" t="n">
-        <v>51.40170175940258</v>
+        <v>2.538898683778308</v>
       </c>
       <c r="D29" t="n">
-        <v>33.58747755830247</v>
+        <v>1.205196075450658</v>
       </c>
       <c r="E29" t="n">
-        <v>0.946581042321732</v>
+        <v>0.7904135230528482</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3047,20 +3047,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7643.149580797251</v>
+        <v>6.815450332762185</v>
       </c>
       <c r="C30" t="n">
-        <v>87.42510841169859</v>
+        <v>2.610641747303177</v>
       </c>
       <c r="D30" t="n">
-        <v>36.40318218954248</v>
+        <v>1.26684363889451</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8454700109284162</v>
+        <v>0.7784013686331994</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3081,20 +3081,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7828.709876228519</v>
+        <v>7.173177083333333</v>
       </c>
       <c r="C31" t="n">
-        <v>88.47999704017015</v>
+        <v>2.678278753851685</v>
       </c>
       <c r="D31" t="n">
-        <v>37.29084177678266</v>
+        <v>1.2734375</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8417183336752121</v>
+        <v>0.7667701844180059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3115,20 +3115,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2129.426643550192</v>
+        <v>12.94081369323765</v>
       </c>
       <c r="C32" t="n">
-        <v>46.14571099842532</v>
+        <v>3.597334248195134</v>
       </c>
       <c r="D32" t="n">
-        <v>27.65282179498814</v>
+        <v>2.341174268684752</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9569470317860472</v>
+        <v>0.5792403343607087</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3149,20 +3149,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2117.981649018302</v>
+        <v>4.855042720052083</v>
       </c>
       <c r="C33" t="n">
-        <v>46.02153462259056</v>
+        <v>2.203416147724275</v>
       </c>
       <c r="D33" t="n">
-        <v>27.56069619556558</v>
+        <v>1.1256171875</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9571784278697221</v>
+        <v>0.8421423721893873</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3183,20 +3183,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1869.915486848594</v>
+        <v>7.065501787383496</v>
       </c>
       <c r="C34" t="n">
-        <v>43.24251943225087</v>
+        <v>2.658101161992052</v>
       </c>
       <c r="D34" t="n">
-        <v>26.24478112569607</v>
+        <v>1.314924671639692</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9621938552042105</v>
+        <v>0.7702711560412308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3217,20 +3217,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2684.894477491953</v>
+        <v>4.410158807519707</v>
       </c>
       <c r="C35" t="n">
-        <v>51.81596739897802</v>
+        <v>2.100037810973818</v>
       </c>
       <c r="D35" t="n">
-        <v>35.64545855702209</v>
+        <v>1.154289717120984</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9457165256444047</v>
+        <v>0.8566073981701908</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3251,20 +3251,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3828.996206380649</v>
+        <v>6.514903415820553</v>
       </c>
       <c r="C36" t="n">
-        <v>61.87888336404148</v>
+        <v>2.552430883652005</v>
       </c>
       <c r="D36" t="n">
-        <v>23.94752582462141</v>
+        <v>1.240550574066643</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9225849585079796</v>
+        <v>0.7881733986831617</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3285,20 +3285,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4465.002130702383</v>
+        <v>5.9296875</v>
       </c>
       <c r="C37" t="n">
-        <v>66.82067143259175</v>
+        <v>2.43509496734727</v>
       </c>
       <c r="D37" t="n">
-        <v>24.61194912788026</v>
+        <v>1.317708333333333</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9097261249216496</v>
+        <v>0.8072012016408784</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3319,20 +3319,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1218.669342439545</v>
+        <v>14.06611103663894</v>
       </c>
       <c r="C38" t="n">
-        <v>34.90944488873384</v>
+        <v>3.750481440647179</v>
       </c>
       <c r="D38" t="n">
-        <v>22.17567508966316</v>
+        <v>2.408424017038099</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9753608171371921</v>
+        <v>0.5426522383430887</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3353,20 +3353,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1199.021582752458</v>
+        <v>7.431727897135416</v>
       </c>
       <c r="C39" t="n">
-        <v>34.62689103503891</v>
+        <v>2.726119567652053</v>
       </c>
       <c r="D39" t="n">
-        <v>22.01623853253676</v>
+        <v>1.199466145833333</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9757580575755259</v>
+        <v>0.7583636223157342</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3387,20 +3387,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1057.766352778835</v>
+        <v>7.415072838564298</v>
       </c>
       <c r="C40" t="n">
-        <v>32.5233201376925</v>
+        <v>2.723063135251237</v>
       </c>
       <c r="D40" t="n">
-        <v>20.80181794455994</v>
+        <v>1.257122873589612</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9786139704310023</v>
+        <v>0.7589051475274948</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3421,20 +3421,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5337.339085275416</v>
+        <v>9.687931768167727</v>
       </c>
       <c r="C41" t="n">
-        <v>73.05709469500835</v>
+        <v>3.112544259631938</v>
       </c>
       <c r="D41" t="n">
-        <v>50.55357434516943</v>
+        <v>1.343258069192568</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8920891261122074</v>
+        <v>0.6850050523762174</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3455,20 +3455,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5552.743545462283</v>
+        <v>7.13391552782618</v>
       </c>
       <c r="C42" t="n">
-        <v>74.51673332522222</v>
+        <v>2.67093907227892</v>
       </c>
       <c r="D42" t="n">
-        <v>27.01965277777778</v>
+        <v>1.215330930315326</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8877340564479584</v>
+        <v>0.7680467408509526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3489,20 +3489,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5837.68313246142</v>
+        <v>9.015625</v>
       </c>
       <c r="C43" t="n">
-        <v>76.40473239571891</v>
+        <v>3.002603037366078</v>
       </c>
       <c r="D43" t="n">
-        <v>27.37565972663329</v>
+        <v>1.432291666666667</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8819731183949254</v>
+        <v>0.7068645410982525</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3523,20 +3523,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3608.655982652319</v>
+        <v>14.15454261836912</v>
       </c>
       <c r="C44" t="n">
-        <v>60.07208988084499</v>
+        <v>3.762252333160167</v>
       </c>
       <c r="D44" t="n">
-        <v>29.16481335365523</v>
+        <v>2.436855952043454</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9270398199502199</v>
+        <v>0.5397769598913025</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3557,20 +3557,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3472.68409937353</v>
+        <v>6.307386067708333</v>
       </c>
       <c r="C45" t="n">
-        <v>58.92948412614462</v>
+        <v>2.511450988514077</v>
       </c>
       <c r="D45" t="n">
-        <v>28.83322154682137</v>
+        <v>1.138255208333333</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9297889135555452</v>
+        <v>0.7949206506006881</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3591,20 +3591,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2569.46729087665</v>
+        <v>7.868532560431888</v>
       </c>
       <c r="C46" t="n">
-        <v>50.68991310780331</v>
+        <v>2.805090472771224</v>
       </c>
       <c r="D46" t="n">
-        <v>26.68645472638144</v>
+        <v>1.281772768371954</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9480502444468</v>
+        <v>0.7441612863239604</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3625,20 +3625,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4747.077260242733</v>
+        <v>6.596448999579057</v>
       </c>
       <c r="C47" t="n">
-        <v>68.89903671491157</v>
+        <v>2.568355310228524</v>
       </c>
       <c r="D47" t="n">
-        <v>47.79710001027981</v>
+        <v>1.208739251156961</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9040231007659076</v>
+        <v>0.7855220126598454</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3659,20 +3659,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6664.169893822528</v>
+        <v>6.938009589828869</v>
       </c>
       <c r="C48" t="n">
-        <v>81.63436711228016</v>
+        <v>2.634010172688949</v>
       </c>
       <c r="D48" t="n">
-        <v>32.93462184873949</v>
+        <v>1.255804634100629</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8652631235360235</v>
+        <v>0.7744164575413007</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3693,20 +3693,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6621.05142415871</v>
+        <v>8.088541666666666</v>
       </c>
       <c r="C49" t="n">
-        <v>81.36984345664375</v>
+        <v>2.844036157763587</v>
       </c>
       <c r="D49" t="n">
-        <v>33.12492604559735</v>
+        <v>1.348958333333333</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8661348972172129</v>
+        <v>0.7370078754047291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3727,20 +3727,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1281.525738456657</v>
+        <v>14.30474564252502</v>
       </c>
       <c r="C50" t="n">
-        <v>35.79840413281934</v>
+        <v>3.78216150402452</v>
       </c>
       <c r="D50" t="n">
-        <v>22.3560346976928</v>
+        <v>2.471588016630491</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9740899800186819</v>
+        <v>0.53489323497879</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3761,20 +3761,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1262.746310844653</v>
+        <v>4.993127173177083</v>
       </c>
       <c r="C51" t="n">
-        <v>35.53514191395123</v>
+        <v>2.234530638227429</v>
       </c>
       <c r="D51" t="n">
-        <v>22.21588169404514</v>
+        <v>1.123846354166667</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9744696644292741</v>
+        <v>0.8376526724143862</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3795,20 +3795,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1067.160734031146</v>
+        <v>6.782778822465871</v>
       </c>
       <c r="C52" t="n">
-        <v>32.66742619232721</v>
+        <v>2.604376858764083</v>
       </c>
       <c r="D52" t="n">
-        <v>20.66692551850902</v>
+        <v>1.281870647598566</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9784240338587937</v>
+        <v>0.7794636552926073</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3829,20 +3829,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4033.177713906903</v>
+        <v>3.841192342057154</v>
       </c>
       <c r="C53" t="n">
-        <v>63.50730441379876</v>
+        <v>1.959896002867793</v>
       </c>
       <c r="D53" t="n">
-        <v>44.256710799297</v>
+        <v>1.033516532165777</v>
       </c>
       <c r="E53" t="n">
-        <v>0.918456795661877</v>
+        <v>0.8751068639258174</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3863,20 +3863,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3844.026516520289</v>
+        <v>6.165941091328225</v>
       </c>
       <c r="C54" t="n">
-        <v>62.00021384253677</v>
+        <v>2.483131307709728</v>
       </c>
       <c r="D54" t="n">
-        <v>23.6872998366013</v>
+        <v>1.193151110026758</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9222810741423698</v>
+        <v>0.7995196149609549</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3897,20 +3897,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4350.459170892083</v>
+        <v>6.489583333333333</v>
       </c>
       <c r="C55" t="n">
-        <v>65.95801066505935</v>
+        <v>2.547466061272129</v>
       </c>
       <c r="D55" t="n">
-        <v>25.00836715188398</v>
+        <v>1.375</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9120419663350092</v>
+        <v>0.7889966598546635</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3931,20 +3931,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1218.669342439546</v>
+        <v>13.10566528418172</v>
       </c>
       <c r="C56" t="n">
-        <v>34.90944488873385</v>
+        <v>3.620174758790205</v>
       </c>
       <c r="D56" t="n">
-        <v>22.17567508966316</v>
+        <v>2.300752231604763</v>
       </c>
       <c r="E56" t="n">
-        <v>0.975360817137192</v>
+        <v>0.5738803236280002</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3965,20 +3965,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1209.405113467653</v>
+        <v>7.518082584635416</v>
       </c>
       <c r="C57" t="n">
-        <v>34.77650231791077</v>
+        <v>2.741912213152605</v>
       </c>
       <c r="D57" t="n">
-        <v>22.09191854669197</v>
+        <v>1.205611979166667</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9755481222771281</v>
+        <v>0.7555558723318306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3999,20 +3999,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1057.93796347649</v>
+        <v>7.415072838564298</v>
       </c>
       <c r="C58" t="n">
-        <v>32.52595830220056</v>
+        <v>2.723063135251237</v>
       </c>
       <c r="D58" t="n">
-        <v>20.78242828799679</v>
+        <v>1.257122873589612</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9786105007881604</v>
+        <v>0.7589051475274948</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4033,20 +4033,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2507.536669431467</v>
+        <v>9.687931768167727</v>
       </c>
       <c r="C59" t="n">
-        <v>50.07530997838622</v>
+        <v>3.112544259631938</v>
       </c>
       <c r="D59" t="n">
-        <v>34.61237464756019</v>
+        <v>1.343258069192568</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9493023641592238</v>
+        <v>0.6850050523762174</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4067,20 +4067,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>5520.370826337828</v>
+        <v>7.13391552782618</v>
       </c>
       <c r="C60" t="n">
-        <v>74.29919801947952</v>
+        <v>2.67093907227892</v>
       </c>
       <c r="D60" t="n">
-        <v>26.88018382352941</v>
+        <v>1.215330930315326</v>
       </c>
       <c r="E60" t="n">
-        <v>0.8883885714328658</v>
+        <v>0.7680467408509526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4101,20 +4101,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>5837.68313246142</v>
+        <v>9.151041666666666</v>
       </c>
       <c r="C61" t="n">
-        <v>76.40473239571891</v>
+        <v>3.025068869739442</v>
       </c>
       <c r="D61" t="n">
-        <v>27.37565972663329</v>
+        <v>1.447916666666667</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8819731183949254</v>
+        <v>0.7024615821546099</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4135,20 +4135,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3608.655982652352</v>
+        <v>12.49985723238198</v>
       </c>
       <c r="C62" t="n">
-        <v>60.07208988084526</v>
+        <v>3.535513715484919</v>
       </c>
       <c r="D62" t="n">
-        <v>29.16481335365526</v>
+        <v>2.27377654521874</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9270398199502193</v>
+        <v>0.593577662555772</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4169,20 +4169,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3530.824795404617</v>
+        <v>6.433783854166666</v>
       </c>
       <c r="C63" t="n">
-        <v>59.42074381396296</v>
+        <v>2.536490460097705</v>
       </c>
       <c r="D63" t="n">
-        <v>28.98056681898847</v>
+        <v>1.148489583333333</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9286134189472922</v>
+        <v>0.7908109329563064</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -4203,20 +4203,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2751.97469059272</v>
+        <v>7.868679783503251</v>
       </c>
       <c r="C64" t="n">
-        <v>52.45926696583474</v>
+        <v>2.805116714773781</v>
       </c>
       <c r="D64" t="n">
-        <v>26.98199876407477</v>
+        <v>1.281872730748717</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9443602909550529</v>
+        <v>0.744156499489705</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4237,20 +4237,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2428.455307894545</v>
+        <v>6.596448999579057</v>
       </c>
       <c r="C65" t="n">
-        <v>49.27935985678532</v>
+        <v>2.568355310228524</v>
       </c>
       <c r="D65" t="n">
-        <v>33.12930427712962</v>
+        <v>1.208739251156961</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9509012393094327</v>
+        <v>0.7855220126598454</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4271,20 +4271,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>6667.762188805799</v>
+        <v>6.848163172461672</v>
       </c>
       <c r="C66" t="n">
-        <v>81.65636649279588</v>
+        <v>2.616899534269834</v>
       </c>
       <c r="D66" t="n">
-        <v>32.89167250233427</v>
+        <v>1.248463333693178</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8651904941443521</v>
+        <v>0.7773377381830323</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4305,20 +4305,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6621.05142415871</v>
+        <v>8.08984375</v>
       </c>
       <c r="C67" t="n">
-        <v>81.36984345664375</v>
+        <v>2.844265063245688</v>
       </c>
       <c r="D67" t="n">
-        <v>33.12492604559735</v>
+        <v>1.346354166666667</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8661348972172129</v>
+        <v>0.7369655392610402</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4339,20 +4339,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1281.525738456656</v>
+        <v>12.97887920133208</v>
       </c>
       <c r="C68" t="n">
-        <v>35.79840413281932</v>
+        <v>3.602621157064962</v>
       </c>
       <c r="D68" t="n">
-        <v>22.35603469769277</v>
+        <v>2.341823085894539</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9740899800186819</v>
+        <v>0.5780026664027367</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4373,20 +4373,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1271.534317075107</v>
+        <v>4.957468945638021</v>
       </c>
       <c r="C69" t="n">
-        <v>35.65857985219135</v>
+        <v>2.226537434142534</v>
       </c>
       <c r="D69" t="n">
-        <v>22.27225172662912</v>
+        <v>1.12313671875</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9742919876099999</v>
+        <v>0.8388120696711805</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4407,20 +4407,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1095.49159783899</v>
+        <v>6.846473218586518</v>
       </c>
       <c r="C70" t="n">
-        <v>33.09821139939423</v>
+        <v>2.616576621959792</v>
       </c>
       <c r="D70" t="n">
-        <v>20.82995426808088</v>
+        <v>1.299746023713305</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9778512375228939</v>
+        <v>0.7773926856109383</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4441,20 +4441,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2099.346010669748</v>
+        <v>3.841192342057154</v>
       </c>
       <c r="C71" t="n">
-        <v>45.81862078532862</v>
+        <v>1.959896002867793</v>
       </c>
       <c r="D71" t="n">
-        <v>32.37636245441423</v>
+        <v>1.033516532165777</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9575552051341079</v>
+        <v>0.8751068639258174</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4475,20 +4475,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3847.595422947304</v>
+        <v>6.166417449893065</v>
       </c>
       <c r="C72" t="n">
-        <v>62.02898856943666</v>
+        <v>2.483227224780903</v>
       </c>
       <c r="D72" t="n">
-        <v>23.74464460784314</v>
+        <v>1.19348486742094</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9222089176229489</v>
+        <v>0.7995041265631448</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4509,20 +4509,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4350.459170892083</v>
+        <v>6.484375</v>
       </c>
       <c r="C73" t="n">
-        <v>65.95801066505935</v>
+        <v>2.54644359843292</v>
       </c>
       <c r="D73" t="n">
-        <v>25.00836715188398</v>
+        <v>1.369791666666667</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9120419663350092</v>
+        <v>0.789166004429419</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4543,20 +4543,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1052.736804593802</v>
+        <v>14.19005594854985</v>
       </c>
       <c r="C74" t="n">
-        <v>32.44590582174894</v>
+        <v>3.766969066577247</v>
       </c>
       <c r="D74" t="n">
-        <v>20.34613807945532</v>
+        <v>2.422228498334384</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9787156583566214</v>
+        <v>0.5386222738501618</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4577,20 +4577,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1020.617239617823</v>
+        <v>7.095644270833335</v>
       </c>
       <c r="C75" t="n">
-        <v>31.94710064493839</v>
+        <v>2.663765055486939</v>
       </c>
       <c r="D75" t="n">
-        <v>20.10981084713717</v>
+        <v>1.176145833333333</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9793650550447606</v>
+        <v>0.7692910985611885</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4611,20 +4611,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>983.5635549325143</v>
+        <v>7.162533646821227</v>
       </c>
       <c r="C76" t="n">
-        <v>31.36181683086161</v>
+        <v>2.676291024313542</v>
       </c>
       <c r="D76" t="n">
-        <v>19.58033015126376</v>
+        <v>1.253893317980446</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9801142102757231</v>
+        <v>0.7671162467981812</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4645,20 +4645,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>5203.0779168096</v>
+        <v>9.724621420293738</v>
       </c>
       <c r="C77" t="n">
-        <v>72.13236386539401</v>
+        <v>3.118432526173003</v>
       </c>
       <c r="D77" t="n">
-        <v>51.58914568873465</v>
+        <v>1.318999587074434</v>
       </c>
       <c r="E77" t="n">
-        <v>0.894803632308434</v>
+        <v>0.6838121192170739</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4679,20 +4679,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>5959.392503424565</v>
+        <v>8.017726197709775</v>
       </c>
       <c r="C78" t="n">
-        <v>77.19710165171077</v>
+        <v>2.831558969491855</v>
       </c>
       <c r="D78" t="n">
-        <v>26.64849673202614</v>
+        <v>1.295108790575545</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8795123857393594</v>
+        <v>0.7393103807762392</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4713,20 +4713,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>5808.096865347394</v>
+        <v>9.559895833333334</v>
       </c>
       <c r="C79" t="n">
-        <v>76.21087104440805</v>
+        <v>3.091908121748338</v>
       </c>
       <c r="D79" t="n">
-        <v>25.83531789313004</v>
+        <v>1.411458333333333</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8825712966047679</v>
+        <v>0.6891680330363041</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4747,20 +4747,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1196.60874559528</v>
+        <v>14.20829741850054</v>
       </c>
       <c r="C80" t="n">
-        <v>34.59203297863945</v>
+        <v>3.769389528624038</v>
       </c>
       <c r="D80" t="n">
-        <v>22.6036339658768</v>
+        <v>2.442905160797818</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9758068405668292</v>
+        <v>0.5380291678075927</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4781,20 +4781,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1201.512911980116</v>
+        <v>6.408752091471354</v>
       </c>
       <c r="C81" t="n">
-        <v>34.66284627638237</v>
+        <v>2.53155132112137</v>
       </c>
       <c r="D81" t="n">
-        <v>22.5787640512456</v>
+        <v>1.15416015625</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9757076876234199</v>
+        <v>0.7916248196524379</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4815,20 +4815,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1109.490734486471</v>
+        <v>8.119305660535959</v>
       </c>
       <c r="C82" t="n">
-        <v>33.30901881602746</v>
+        <v>2.849439534458655</v>
       </c>
       <c r="D82" t="n">
-        <v>21.48172122022829</v>
+        <v>1.321942730189919</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9775682015296455</v>
+        <v>0.7360076100364905</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4849,20 +4849,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4224.561626008411</v>
+        <v>6.23376911523042</v>
       </c>
       <c r="C83" t="n">
-        <v>64.99662780489777</v>
+        <v>2.496751712772101</v>
       </c>
       <c r="D83" t="n">
-        <v>46.64262955839744</v>
+        <v>1.19337943048716</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9145873759242565</v>
+        <v>0.7973142438510242</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4883,20 +4883,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6289.467586213235</v>
+        <v>6.838607703808216</v>
       </c>
       <c r="C84" t="n">
-        <v>79.30616360796452</v>
+        <v>2.61507317370054</v>
       </c>
       <c r="D84" t="n">
-        <v>30.88290849673203</v>
+        <v>1.2483466455104</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8728388935622228</v>
+        <v>0.7776484262039685</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4917,20 +4917,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6449.176773622734</v>
+        <v>7.555989583333333</v>
       </c>
       <c r="C85" t="n">
-        <v>80.30676667394059</v>
+        <v>2.748816033010091</v>
       </c>
       <c r="D85" t="n">
-        <v>32.03685067086662</v>
+        <v>1.283854166666667</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8696098766858519</v>
+        <v>0.7543233581734776</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -4951,20 +4951,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>935.2392200955865</v>
+        <v>14.33796500553242</v>
       </c>
       <c r="C86" t="n">
-        <v>30.58168111951314</v>
+        <v>3.786550541790301</v>
       </c>
       <c r="D86" t="n">
-        <v>20.01575403815376</v>
+        <v>2.471628838727938</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9810912366776403</v>
+        <v>0.5338131353495799</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -4985,20 +4985,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>908.7981367359426</v>
+        <v>4.76177138671875</v>
       </c>
       <c r="C87" t="n">
-        <v>30.14627898656719</v>
+        <v>2.182148342051647</v>
       </c>
       <c r="D87" t="n">
-        <v>19.79677832480687</v>
+        <v>1.101783854166667</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9816258252369003</v>
+        <v>0.8451750110911876</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -5019,20 +5019,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>881.0037582969538</v>
+        <v>6.837817590584454</v>
       </c>
       <c r="C88" t="n">
-        <v>29.68170746936493</v>
+        <v>2.614922100289883</v>
       </c>
       <c r="D88" t="n">
-        <v>19.64468059556231</v>
+        <v>1.309881094722067</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9821877748561016</v>
+        <v>0.7776741160704426</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -5053,20 +5053,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4019.507182003154</v>
+        <v>4.422881951598273</v>
       </c>
       <c r="C89" t="n">
-        <v>63.39958345291516</v>
+        <v>2.103064894766272</v>
       </c>
       <c r="D89" t="n">
-        <v>46.12791665459956</v>
+        <v>1.131402354048381</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9187331878904155</v>
+        <v>0.8561937158488717</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5087,20 +5087,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3795.252026582924</v>
+        <v>6.521352527912139</v>
       </c>
       <c r="C90" t="n">
-        <v>61.60561684280845</v>
+        <v>2.55369389863236</v>
       </c>
       <c r="D90" t="n">
-        <v>22.56629493464052</v>
+        <v>1.224419947453137</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9232672018266859</v>
+        <v>0.7879637112313793</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5121,20 +5121,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4353.888594325178</v>
+        <v>5.446614583333333</v>
       </c>
       <c r="C91" t="n">
-        <v>65.98400256369098</v>
+        <v>2.333798316764611</v>
       </c>
       <c r="D91" t="n">
-        <v>23.89062833055446</v>
+        <v>1.2421875</v>
       </c>
       <c r="E91" t="n">
-        <v>0.9119726298971917</v>
+        <v>0.8229079109494497</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5155,20 +5155,20 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1052.736804593803</v>
+        <v>13.2405913434712</v>
       </c>
       <c r="C92" t="n">
-        <v>32.44590582174896</v>
+        <v>3.63876233676661</v>
       </c>
       <c r="D92" t="n">
-        <v>20.34613807945532</v>
+        <v>2.312337159678259</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9787156583566214</v>
+        <v>0.5694933163703086</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5189,20 +5189,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1035.780497479807</v>
+        <v>7.089129687500001</v>
       </c>
       <c r="C93" t="n">
-        <v>32.18354389248965</v>
+        <v>2.662541959763264</v>
       </c>
       <c r="D93" t="n">
-        <v>20.22824017782058</v>
+        <v>1.180625</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9790584827283442</v>
+        <v>0.7695029147552926</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5223,20 +5223,20 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>998.4434420818937</v>
+        <v>7.164978383442748</v>
       </c>
       <c r="C94" t="n">
-        <v>31.59815567532215</v>
+        <v>2.676747725028032</v>
       </c>
       <c r="D94" t="n">
-        <v>19.75334525356408</v>
+        <v>1.255088123723449</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9798133671776948</v>
+        <v>0.7670367582445375</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5257,20 +5257,20 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2354.114343509134</v>
+        <v>9.724621420293738</v>
       </c>
       <c r="C95" t="n">
-        <v>48.51921622933673</v>
+        <v>3.118432526173003</v>
       </c>
       <c r="D95" t="n">
-        <v>35.30243754030933</v>
+        <v>1.318999587074434</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9524042726195371</v>
+        <v>0.6838121192170739</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5291,20 +5291,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5963.626132798883</v>
+        <v>8.015633897927469</v>
       </c>
       <c r="C96" t="n">
-        <v>77.22451769223866</v>
+        <v>2.831189484638474</v>
       </c>
       <c r="D96" t="n">
-        <v>26.72331290849673</v>
+        <v>1.295218296010705</v>
       </c>
       <c r="E96" t="n">
-        <v>0.87942678978261</v>
+        <v>0.7393784101426832</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5325,20 +5325,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5761.477486680281</v>
+        <v>9.779947916666666</v>
       </c>
       <c r="C97" t="n">
-        <v>75.90439701809296</v>
+        <v>3.127290827004528</v>
       </c>
       <c r="D97" t="n">
-        <v>25.74321342592746</v>
+        <v>1.450520833333333</v>
       </c>
       <c r="E97" t="n">
-        <v>0.8835138520264297</v>
+        <v>0.6820132247528847</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5359,20 +5359,20 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1196.608745595277</v>
+        <v>12.54717146178756</v>
       </c>
       <c r="C98" t="n">
-        <v>34.59203297863942</v>
+        <v>3.542198676216167</v>
       </c>
       <c r="D98" t="n">
-        <v>22.6036339658768</v>
+        <v>2.276144045464891</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9758068405668293</v>
+        <v>0.5920392802085261</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5393,20 +5393,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1197.403781728375</v>
+        <v>6.352518098958334</v>
       </c>
       <c r="C99" t="n">
-        <v>34.60352267802189</v>
+        <v>2.520420222692703</v>
       </c>
       <c r="D99" t="n">
-        <v>22.58779058817652</v>
+        <v>1.145703125</v>
       </c>
       <c r="E99" t="n">
-        <v>0.9757907664440268</v>
+        <v>0.7934532205898306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5427,20 +5427,20 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1089.395047205211</v>
+        <v>8.119305660535959</v>
       </c>
       <c r="C100" t="n">
-        <v>33.00598502098082</v>
+        <v>2.849439534458655</v>
       </c>
       <c r="D100" t="n">
-        <v>21.49271004844468</v>
+        <v>1.321942730189919</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9779744982144261</v>
+        <v>0.7360076100364905</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5461,20 +5461,20 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2048.884069234702</v>
+        <v>6.23376911523042</v>
       </c>
       <c r="C101" t="n">
-        <v>45.2646006194101</v>
+        <v>2.496751712772101</v>
       </c>
       <c r="D101" t="n">
-        <v>32.18045008411133</v>
+        <v>1.19337943048716</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9585754498874069</v>
+        <v>0.7973142438510242</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -5495,20 +5495,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>6299.103784470316</v>
+        <v>6.809075662247731</v>
       </c>
       <c r="C102" t="n">
-        <v>79.36689350396874</v>
+        <v>2.609420560631753</v>
       </c>
       <c r="D102" t="n">
-        <v>30.86583333333333</v>
+        <v>1.245515471349167</v>
       </c>
       <c r="E102" t="n">
-        <v>0.8726440679087906</v>
+        <v>0.778608635679755</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -5529,20 +5529,20 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>6449.276293037991</v>
+        <v>7.67578125</v>
       </c>
       <c r="C103" t="n">
-        <v>80.30738629190961</v>
+        <v>2.770520032412688</v>
       </c>
       <c r="D103" t="n">
-        <v>32.05390412481535</v>
+        <v>1.3046875</v>
       </c>
       <c r="E103" t="n">
-        <v>0.8696078645920168</v>
+        <v>0.7504284329541014</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -5563,20 +5563,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>935.2392200955833</v>
+        <v>13.01516505653451</v>
       </c>
       <c r="C104" t="n">
-        <v>30.58168111951309</v>
+        <v>3.607653677466077</v>
       </c>
       <c r="D104" t="n">
-        <v>20.01575403815372</v>
+        <v>2.342527503348371</v>
       </c>
       <c r="E104" t="n">
-        <v>0.9810912366776404</v>
+        <v>0.5768228623607092</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -5597,20 +5597,20 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>922.5967718490589</v>
+        <v>4.739283341471354</v>
       </c>
       <c r="C105" t="n">
-        <v>30.37427812885532</v>
+        <v>2.176989513404085</v>
       </c>
       <c r="D105" t="n">
-        <v>19.90988193132099</v>
+        <v>1.096829427083333</v>
       </c>
       <c r="E105" t="n">
-        <v>0.9813468430044199</v>
+        <v>0.8459061909554121</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -5631,20 +5631,20 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>894.1713171540425</v>
+        <v>6.848978718940498</v>
       </c>
       <c r="C106" t="n">
-        <v>29.90269748959185</v>
+        <v>2.617055352670344</v>
       </c>
       <c r="D106" t="n">
-        <v>19.62671109358642</v>
+        <v>1.314169027962364</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9819215517886639</v>
+        <v>0.7773112213756754</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -5665,20 +5665,20 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2028.527053474696</v>
+        <v>4.422881951598273</v>
       </c>
       <c r="C107" t="n">
-        <v>45.03917243327964</v>
+        <v>2.103064894766272</v>
       </c>
       <c r="D107" t="n">
-        <v>33.59596946211614</v>
+        <v>1.131402354048381</v>
       </c>
       <c r="E107" t="n">
-        <v>0.9589870301384107</v>
+        <v>0.8561937158488717</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -5699,20 +5699,20 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3807.727111122087</v>
+        <v>6.521002275299026</v>
       </c>
       <c r="C108" t="n">
-        <v>61.70678334771702</v>
+        <v>2.553625320069298</v>
       </c>
       <c r="D108" t="n">
-        <v>22.75945961718021</v>
+        <v>1.224281655746656</v>
       </c>
       <c r="E108" t="n">
-        <v>0.9230149792766593</v>
+        <v>0.7879750994003056</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -5733,20 +5733,20 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>4353.888594325178</v>
+        <v>5.40625</v>
       </c>
       <c r="C109" t="n">
-        <v>65.98400256369098</v>
+        <v>2.325134404717284</v>
       </c>
       <c r="D109" t="n">
-        <v>23.89062833055446</v>
+        <v>1.234375</v>
       </c>
       <c r="E109" t="n">
-        <v>0.9119726298971917</v>
+        <v>0.8242203314038048</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -5767,20 +5767,20 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>137.8524088630288</v>
+        <v>14.87043321204156</v>
       </c>
       <c r="C110" t="n">
-        <v>11.74105654798702</v>
+        <v>3.856220067895705</v>
       </c>
       <c r="D110" t="n">
-        <v>6.625282860391049</v>
+        <v>2.494184858708053</v>
       </c>
       <c r="E110" t="n">
-        <v>0.9972973126772772</v>
+        <v>0.5365515920112571</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5801,20 +5801,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>138.2563638728759</v>
+        <v>8.008666530054645</v>
       </c>
       <c r="C111" t="n">
-        <v>11.75824663259263</v>
+        <v>2.829958750592426</v>
       </c>
       <c r="D111" t="n">
-        <v>6.766858520389755</v>
+        <v>1.263032786885246</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9972893928730963</v>
+        <v>0.7504037911645353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -5835,20 +5835,20 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>151.2996699449108</v>
+        <v>8.252315787393226</v>
       </c>
       <c r="C112" t="n">
-        <v>12.3003930809105</v>
+        <v>2.872684421824511</v>
       </c>
       <c r="D112" t="n">
-        <v>7.215526731366722</v>
+        <v>1.322194113271492</v>
       </c>
       <c r="E112" t="n">
-        <v>0.9970336702618047</v>
+        <v>0.7428102759783222</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -5869,20 +5869,20 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>4749.035378521183</v>
+        <v>10.67125457121626</v>
       </c>
       <c r="C113" t="n">
-        <v>68.91324530539237</v>
+        <v>3.266688624772226</v>
       </c>
       <c r="D113" t="n">
-        <v>48.45334861507236</v>
+        <v>1.448192620252738</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9068920317131015</v>
+        <v>0.6674222013741996</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5903,20 +5903,20 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>5986.323803993974</v>
+        <v>8.829030975843679</v>
       </c>
       <c r="C114" t="n">
-        <v>77.37133709581329</v>
+        <v>2.971368535850725</v>
       </c>
       <c r="D114" t="n">
-        <v>27.22944003527337</v>
+        <v>1.337508594503017</v>
       </c>
       <c r="E114" t="n">
-        <v>0.8826341767386582</v>
+        <v>0.7248365066779189</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5937,20 +5937,20 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>6346.943407975475</v>
+        <v>9.972677595628415</v>
       </c>
       <c r="C115" t="n">
-        <v>79.66770617995397</v>
+        <v>3.157954653827128</v>
       </c>
       <c r="D115" t="n">
-        <v>27.52758928279464</v>
+        <v>1.546448087431694</v>
       </c>
       <c r="E115" t="n">
-        <v>0.8755639917484594</v>
+        <v>0.6891938863397467</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -5971,20 +5971,20 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>163.5785298222185</v>
+        <v>14.40977076800421</v>
       </c>
       <c r="C116" t="n">
-        <v>12.78978224295545</v>
+        <v>3.796020385614942</v>
       </c>
       <c r="D116" t="n">
-        <v>7.366202931094968</v>
+        <v>2.474495228081621</v>
       </c>
       <c r="E116" t="n">
-        <v>0.9967929351219432</v>
+        <v>0.5509084888995355</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -6005,20 +6005,20 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>168.0937003222335</v>
+        <v>6.796429892418032</v>
       </c>
       <c r="C117" t="n">
-        <v>12.96509546136215</v>
+        <v>2.606996335328846</v>
       </c>
       <c r="D117" t="n">
-        <v>7.657108025702747</v>
+        <v>1.190908469945355</v>
       </c>
       <c r="E117" t="n">
-        <v>0.9967044122287201</v>
+        <v>0.7881840717930365</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -6039,20 +6039,20 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>163.0638498536798</v>
+        <v>8.206125857111934</v>
       </c>
       <c r="C118" t="n">
-        <v>12.76964564323066</v>
+        <v>2.864633634011849</v>
       </c>
       <c r="D118" t="n">
-        <v>7.426836556833519</v>
+        <v>1.321637536129103</v>
       </c>
       <c r="E118" t="n">
-        <v>0.9968030257619088</v>
+        <v>0.7442498204319862</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -6073,20 +6073,20 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3858.679738856254</v>
+        <v>7.347379490456304</v>
       </c>
       <c r="C119" t="n">
-        <v>62.11827218183273</v>
+        <v>2.710605004506615</v>
       </c>
       <c r="D119" t="n">
-        <v>44.68115147001677</v>
+        <v>1.275300903876867</v>
       </c>
       <c r="E119" t="n">
-        <v>0.9243480407874743</v>
+        <v>0.7710133067956784</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -6107,20 +6107,20 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>6761.058417214139</v>
+        <v>7.951775334235136</v>
       </c>
       <c r="C120" t="n">
-        <v>82.22565546843721</v>
+        <v>2.819889241483633</v>
       </c>
       <c r="D120" t="n">
-        <v>32.54675044091712</v>
+        <v>1.304334907341904</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8674449940838582</v>
+        <v>0.7521768487315318</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -6141,20 +6141,20 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>7231.534163646649</v>
+        <v>6.620218579234972</v>
       </c>
       <c r="C121" t="n">
-        <v>85.03842757040283</v>
+        <v>2.572978542319188</v>
       </c>
       <c r="D121" t="n">
-        <v>35.12910180187514</v>
+        <v>1.213114754098361</v>
       </c>
       <c r="E121" t="n">
-        <v>0.8582210070239358</v>
+        <v>0.7936758319455359</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -6175,20 +6175,20 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>143.1226135061521</v>
+        <v>14.49438625267525</v>
       </c>
       <c r="C122" t="n">
-        <v>11.96338637285247</v>
+        <v>3.80714936043692</v>
       </c>
       <c r="D122" t="n">
-        <v>6.712176585690197</v>
+        <v>2.51308617188589</v>
       </c>
       <c r="E122" t="n">
-        <v>0.9971939868420988</v>
+        <v>0.5482713826967225</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -6209,20 +6209,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>139.3596773504461</v>
+        <v>5.027872897540983</v>
       </c>
       <c r="C123" t="n">
-        <v>11.80506998498722</v>
+        <v>2.242291885000921</v>
       </c>
       <c r="D123" t="n">
-        <v>6.68854863026555</v>
+        <v>1.128363387978142</v>
       </c>
       <c r="E123" t="n">
-        <v>0.9972677616852671</v>
+        <v>0.8433025012312194</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -6243,20 +6243,20 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>139.6506927703864</v>
+        <v>7.032789844724642</v>
       </c>
       <c r="C124" t="n">
-        <v>11.81738942281189</v>
+        <v>2.651940769460102</v>
       </c>
       <c r="D124" t="n">
-        <v>6.793576133068236</v>
+        <v>1.306476838809563</v>
       </c>
       <c r="E124" t="n">
-        <v>0.9972620561361752</v>
+        <v>0.780817733365176</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -6277,20 +6277,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3349.141960411131</v>
+        <v>4.9314393467451</v>
       </c>
       <c r="C125" t="n">
-        <v>57.87177170617062</v>
+        <v>2.22068443204907</v>
       </c>
       <c r="D125" t="n">
-        <v>42.40600505673567</v>
+        <v>1.164602598191787</v>
       </c>
       <c r="E125" t="n">
-        <v>0.9343378647275138</v>
+        <v>0.8463079264905765</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -6311,20 +6311,20 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3258.288975989513</v>
+        <v>6.544108413780192</v>
       </c>
       <c r="C126" t="n">
-        <v>57.08142408866052</v>
+        <v>2.558145502855573</v>
       </c>
       <c r="D126" t="n">
-        <v>21.8686470143613</v>
+        <v>1.238762069384752</v>
       </c>
       <c r="E126" t="n">
-        <v>0.9361190973606832</v>
+        <v>0.7960478633792413</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -6345,20 +6345,20 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>4051.197612653737</v>
+        <v>5.016393442622951</v>
       </c>
       <c r="C127" t="n">
-        <v>63.64901894494319</v>
+        <v>2.2397306629644</v>
       </c>
       <c r="D127" t="n">
-        <v>22.97795071373891</v>
+        <v>1.224043715846995</v>
       </c>
       <c r="E127" t="n">
-        <v>0.9205736009992875</v>
+        <v>0.8436602672108973</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -6379,20 +6379,20 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>137.8524088630282</v>
+        <v>13.72845943825635</v>
       </c>
       <c r="C128" t="n">
-        <v>11.74105654798699</v>
+        <v>3.70519357635419</v>
       </c>
       <c r="D128" t="n">
-        <v>6.62528286039106</v>
+        <v>2.36226253209677</v>
       </c>
       <c r="E128" t="n">
-        <v>0.9972973126772772</v>
+        <v>0.572142076826258</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -6413,20 +6413,20 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>138.209072697427</v>
+        <v>7.991676229508196</v>
       </c>
       <c r="C129" t="n">
-        <v>11.75623548154029</v>
+        <v>2.826955293156967</v>
       </c>
       <c r="D129" t="n">
-        <v>6.741859026153173</v>
+        <v>1.25792349726776</v>
       </c>
       <c r="E129" t="n">
-        <v>0.9972903200477565</v>
+        <v>0.7509333068569984</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -6447,20 +6447,20 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>145.3364147270968</v>
+        <v>8.252315787393226</v>
       </c>
       <c r="C130" t="n">
-        <v>12.05555534710437</v>
+        <v>2.872684421824511</v>
       </c>
       <c r="D130" t="n">
-        <v>7.054610279321213</v>
+        <v>1.322194113271492</v>
       </c>
       <c r="E130" t="n">
-        <v>0.9971505838102314</v>
+        <v>0.7428102759783222</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6481,20 +6481,20 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2144.271812878923</v>
+        <v>10.67125457121626</v>
       </c>
       <c r="C131" t="n">
-        <v>46.30628265018606</v>
+        <v>3.266688624772226</v>
       </c>
       <c r="D131" t="n">
-        <v>33.39019177750596</v>
+        <v>1.448192620252738</v>
       </c>
       <c r="E131" t="n">
-        <v>0.9579601379987633</v>
+        <v>0.6674222013741996</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6515,20 +6515,20 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>5989.469040516608</v>
+        <v>8.829030975843679</v>
       </c>
       <c r="C132" t="n">
-        <v>77.39166001913003</v>
+        <v>2.971368535850725</v>
       </c>
       <c r="D132" t="n">
-        <v>27.22138888888889</v>
+        <v>1.337508594503017</v>
       </c>
       <c r="E132" t="n">
-        <v>0.8825725123038703</v>
+        <v>0.7248365066779189</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -6549,20 +6549,20 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>6346.943407975475</v>
+        <v>9.984972677595628</v>
       </c>
       <c r="C133" t="n">
-        <v>79.66770617995397</v>
+        <v>3.159900738566898</v>
       </c>
       <c r="D133" t="n">
-        <v>27.52758928279464</v>
+        <v>1.549180327868853</v>
       </c>
       <c r="E133" t="n">
-        <v>0.8755639917484594</v>
+        <v>0.6888107007201656</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -6583,20 +6583,20 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>163.5785298222184</v>
+        <v>12.79271156190146</v>
       </c>
       <c r="C134" t="n">
-        <v>12.78978224295544</v>
+        <v>3.57669002876982</v>
       </c>
       <c r="D134" t="n">
-        <v>7.366202931094991</v>
+        <v>2.311776993139845</v>
       </c>
       <c r="E134" t="n">
-        <v>0.9967929351219432</v>
+        <v>0.6013053740477775</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -6617,20 +6617,20 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>165.3574700343498</v>
+        <v>6.843666982581968</v>
       </c>
       <c r="C135" t="n">
-        <v>12.85913955264309</v>
+        <v>2.616040325106241</v>
       </c>
       <c r="D135" t="n">
-        <v>7.501758780658883</v>
+        <v>1.19667349726776</v>
       </c>
       <c r="E135" t="n">
-        <v>0.996758057826734</v>
+        <v>0.7867118918018867</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6651,20 +6651,20 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>156.7934241527199</v>
+        <v>8.206825745910425</v>
       </c>
       <c r="C136" t="n">
-        <v>12.5217180990757</v>
+        <v>2.864755791670631</v>
       </c>
       <c r="D136" t="n">
-        <v>7.002518468853983</v>
+        <v>1.32209300281908</v>
       </c>
       <c r="E136" t="n">
-        <v>0.9969259615900878</v>
+        <v>0.744228007863058</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -6685,20 +6685,20 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1845.538249072601</v>
+        <v>7.347379490456304</v>
       </c>
       <c r="C137" t="n">
-        <v>42.95972822391455</v>
+        <v>2.710605004506615</v>
       </c>
       <c r="D137" t="n">
-        <v>30.40924538176541</v>
+        <v>1.275300903876867</v>
       </c>
       <c r="E137" t="n">
-        <v>0.9638170063874281</v>
+        <v>0.7710133067956784</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -6719,20 +6719,20 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>6759.272639215902</v>
+        <v>7.98493602062988</v>
       </c>
       <c r="C138" t="n">
-        <v>82.2147957439286</v>
+        <v>2.825762909486548</v>
       </c>
       <c r="D138" t="n">
-        <v>32.56800264550265</v>
+        <v>1.306673919509726</v>
       </c>
       <c r="E138" t="n">
-        <v>0.8674800054383702</v>
+        <v>0.7511433706143635</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -6753,20 +6753,20 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>7231.534163646649</v>
+        <v>6.741803278688525</v>
       </c>
       <c r="C139" t="n">
-        <v>85.03842757040283</v>
+        <v>2.596498272421633</v>
       </c>
       <c r="D139" t="n">
-        <v>35.12910180187514</v>
+        <v>1.237704918032787</v>
       </c>
       <c r="E139" t="n">
-        <v>0.8582210070239358</v>
+        <v>0.789886551929678</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6787,20 +6787,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>143.1226135061525</v>
+        <v>13.0302233856245</v>
       </c>
       <c r="C140" t="n">
-        <v>11.96338637285248</v>
+        <v>3.609740071753712</v>
       </c>
       <c r="D140" t="n">
-        <v>6.712176585690217</v>
+        <v>2.370166356375336</v>
       </c>
       <c r="E140" t="n">
-        <v>0.9971939868420988</v>
+        <v>0.59390313666751</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6821,20 +6821,20 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>140.8212421469272</v>
+        <v>5.006354318306011</v>
       </c>
       <c r="C141" t="n">
-        <v>11.86681263637912</v>
+        <v>2.237488395122087</v>
       </c>
       <c r="D141" t="n">
-        <v>6.695103645821207</v>
+        <v>1.119674863387978</v>
       </c>
       <c r="E141" t="n">
-        <v>0.9972391067442372</v>
+        <v>0.8439731441873742</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6855,20 +6855,20 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>140.4769746270178</v>
+        <v>6.99879978176956</v>
       </c>
       <c r="C142" t="n">
-        <v>11.85229828459518</v>
+        <v>2.645524481415653</v>
       </c>
       <c r="D142" t="n">
-        <v>6.831806279507489</v>
+        <v>1.307005347339744</v>
       </c>
       <c r="E142" t="n">
-        <v>0.997245856335843</v>
+        <v>0.7818770596362636</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -6889,20 +6889,20 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1579.852633550218</v>
+        <v>4.9314393467451</v>
       </c>
       <c r="C143" t="n">
-        <v>39.74736008278057</v>
+        <v>2.22068443204907</v>
       </c>
       <c r="D143" t="n">
-        <v>30.099638114991</v>
+        <v>1.164602598191787</v>
       </c>
       <c r="E143" t="n">
-        <v>0.9690259479708547</v>
+        <v>0.8463079264905765</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -6923,20 +6923,20 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3264.058870228197</v>
+        <v>6.557625641540588</v>
       </c>
       <c r="C144" t="n">
-        <v>57.13194264357021</v>
+        <v>2.560786137407923</v>
       </c>
       <c r="D144" t="n">
-        <v>21.90725371630133</v>
+        <v>1.239776933793123</v>
       </c>
       <c r="E144" t="n">
-        <v>0.9360059747816803</v>
+        <v>0.7956265886526311</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -6957,20 +6957,20 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4051.197612653737</v>
+        <v>4.881147540983607</v>
       </c>
       <c r="C145" t="n">
-        <v>63.64901894494319</v>
+        <v>2.209331921867696</v>
       </c>
       <c r="D145" t="n">
-        <v>22.97795071373891</v>
+        <v>1.199453551912568</v>
       </c>
       <c r="E145" t="n">
-        <v>0.9205736009992875</v>
+        <v>0.8478753090262897</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -7056,27 +7056,27 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9695474122790002</v>
+        <v>0.7849271941101076</v>
       </c>
       <c r="E2" t="n">
-        <v>1553.254991118708</v>
+        <v>6.900931669161561</v>
       </c>
       <c r="F2" t="n">
-        <v>15.87065484267502</v>
+        <v>1.400113275166756</v>
       </c>
       <c r="G2" t="n">
-        <v>32.70180316085346</v>
+        <v>2.580592573269357</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7085,27 +7085,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.963792394625171</v>
+        <v>0.7780715702241299</v>
       </c>
       <c r="E3" t="n">
-        <v>1846.793588780228</v>
+        <v>6.825593557307276</v>
       </c>
       <c r="F3" t="n">
-        <v>17.90781735564331</v>
+        <v>1.390597494698184</v>
       </c>
       <c r="G3" t="n">
-        <v>35.69801008673765</v>
+        <v>2.563920527182227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7114,16 +7114,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9563890451304977</v>
+        <v>0.7764012790623055</v>
       </c>
       <c r="E4" t="n">
-        <v>2157.025011336774</v>
+        <v>7.174498366348186</v>
       </c>
       <c r="F4" t="n">
-        <v>23.29973407881866</v>
+        <v>1.429222463682855</v>
       </c>
       <c r="G4" t="n">
-        <v>43.93143584710798</v>
+        <v>2.619990435461164</v>
       </c>
     </row>
     <row r="5">
@@ -7143,22 +7143,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.953006549040607</v>
+        <v>0.7763307361005394</v>
       </c>
       <c r="E5" t="n">
-        <v>2324.325376313314</v>
+        <v>6.879134359584474</v>
       </c>
       <c r="F5" t="n">
-        <v>24.43126915109069</v>
+        <v>1.393583149101872</v>
       </c>
       <c r="G5" t="n">
-        <v>46.39346923403826</v>
+        <v>2.572550339874818</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7168,20 +7168,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>zscore</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9513058097643931</v>
+        <v>0.7739393101809262</v>
       </c>
       <c r="E6" t="n">
-        <v>2483.68035960976</v>
+        <v>6.952684654002248</v>
       </c>
       <c r="F6" t="n">
-        <v>18.09348701917582</v>
+        <v>1.415710792057568</v>
       </c>
       <c r="G6" t="n">
-        <v>39.81974937098362</v>
+        <v>2.591069203314092</v>
       </c>
     </row>
     <row r="7">
@@ -7201,51 +7201,51 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9498129760641559</v>
+        <v>0.7706212667568185</v>
       </c>
       <c r="E7" t="n">
-        <v>2482.281486339957</v>
+        <v>7.054733840946562</v>
       </c>
       <c r="F7" t="n">
-        <v>25.34034214638625</v>
+        <v>1.413550598186365</v>
       </c>
       <c r="G7" t="n">
-        <v>46.89981173914331</v>
+        <v>2.595696349049179</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9466658288980833</v>
+        <v>0.7692721169045366</v>
       </c>
       <c r="E8" t="n">
-        <v>2720.34574599074</v>
+        <v>7.096228067481114</v>
       </c>
       <c r="F8" t="n">
-        <v>19.99613833495851</v>
+        <v>1.413162110098043</v>
       </c>
       <c r="G8" t="n">
-        <v>41.39726523882003</v>
+        <v>2.60192706214428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7259,51 +7259,51 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9466272524076675</v>
+        <v>0.7674017976689097</v>
       </c>
       <c r="E9" t="n">
-        <v>2639.849364108622</v>
+        <v>7.153751292142754</v>
       </c>
       <c r="F9" t="n">
-        <v>26.36520328300487</v>
+        <v>1.43326579582687</v>
       </c>
       <c r="G9" t="n">
-        <v>49.2444168600821</v>
+        <v>2.617140378051686</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9427850960020662</v>
+        <v>0.7432601860868605</v>
       </c>
       <c r="E10" t="n">
-        <v>2918.285172195241</v>
+        <v>7.896246648163004</v>
       </c>
       <c r="F10" t="n">
-        <v>20.63634100754798</v>
+        <v>1.409498141062684</v>
       </c>
       <c r="G10" t="n">
-        <v>43.6253308071083</v>
+        <v>2.788599287220091</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7313,26 +7313,26 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9423911539890023</v>
+        <v>0.7413085705532879</v>
       </c>
       <c r="E11" t="n">
-        <v>2849.369432332012</v>
+        <v>7.956270208126668</v>
       </c>
       <c r="F11" t="n">
-        <v>27.61053877096225</v>
+        <v>1.414562050415189</v>
       </c>
       <c r="G11" t="n">
-        <v>52.65421454147967</v>
+        <v>2.798125123197345</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7342,20 +7342,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9421554037818729</v>
+        <v>0.7407147505087405</v>
       </c>
       <c r="E12" t="n">
-        <v>2861.029784523967</v>
+        <v>8.31955384669476</v>
       </c>
       <c r="F12" t="n">
-        <v>24.68278123092892</v>
+        <v>1.441703872441011</v>
       </c>
       <c r="G12" t="n">
-        <v>49.64595605487151</v>
+        <v>2.865058721993581</v>
       </c>
     </row>
     <row r="13">
@@ -7371,20 +7371,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9415305823649159</v>
+        <v>0.7380617308509502</v>
       </c>
       <c r="E13" t="n">
-        <v>2891.933841269067</v>
+        <v>8.05612946534877</v>
       </c>
       <c r="F13" t="n">
-        <v>25.6530400203458</v>
+        <v>1.417949268469599</v>
       </c>
       <c r="G13" t="n">
-        <v>50.49852431707163</v>
+        <v>2.817773466350075</v>
       </c>
     </row>
     <row r="14">
@@ -7404,16 +7404,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.9400524025013067</v>
+        <v>0.733368061432884</v>
       </c>
       <c r="E14" t="n">
-        <v>3057.668066619196</v>
+        <v>8.555283320243431</v>
       </c>
       <c r="F14" t="n">
-        <v>22.46785853774004</v>
+        <v>1.463298633245535</v>
       </c>
       <c r="G14" t="n">
-        <v>44.65114642803684</v>
+        <v>2.895187190544179</v>
       </c>
     </row>
     <row r="15">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -7433,16 +7433,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.9383999146022495</v>
+        <v>0.7324912709541652</v>
       </c>
       <c r="E15" t="n">
-        <v>3046.778620211979</v>
+        <v>8.22745359547997</v>
       </c>
       <c r="F15" t="n">
-        <v>26.964053690793</v>
+        <v>1.440764714983661</v>
       </c>
       <c r="G15" t="n">
-        <v>51.1900701821551</v>
+        <v>2.835170217281133</v>
       </c>
     </row>
     <row r="16">
@@ -7458,26 +7458,26 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.9357779178617291</v>
+        <v>0.7320762222060214</v>
       </c>
       <c r="E16" t="n">
-        <v>3176.464213335757</v>
+        <v>8.240218765152733</v>
       </c>
       <c r="F16" t="n">
-        <v>29.48760898456907</v>
+        <v>1.44093578175406</v>
       </c>
       <c r="G16" t="n">
-        <v>55.35240273556689</v>
+        <v>2.838507130599666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7487,31 +7487,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.9325137063882778</v>
+        <v>0.7293008737369711</v>
       </c>
       <c r="E17" t="n">
-        <v>3337.914147454283</v>
+        <v>8.325576917097322</v>
       </c>
       <c r="F17" t="n">
-        <v>27.35153989862451</v>
+        <v>1.445064357889944</v>
       </c>
       <c r="G17" t="n">
-        <v>53.54919330984362</v>
+        <v>2.854199239187755</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -7520,45 +7520,45 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9319215243498019</v>
+        <v>0.7131307929136529</v>
       </c>
       <c r="E18" t="n">
-        <v>3367.203840194993</v>
+        <v>8.822901210340165</v>
       </c>
       <c r="F18" t="n">
-        <v>28.32376973605673</v>
+        <v>1.459813297914285</v>
       </c>
       <c r="G18" t="n">
-        <v>54.33970274623579</v>
+        <v>2.950977042970826</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9310198126487043</v>
+        <v>0.7073091198115176</v>
       </c>
       <c r="E19" t="n">
-        <v>3411.803062984374</v>
+        <v>9.001951611673668</v>
       </c>
       <c r="F19" t="n">
-        <v>29.37108466055779</v>
+        <v>1.4616654584226</v>
       </c>
       <c r="G19" t="n">
-        <v>54.52890935964203</v>
+        <v>2.982283718140724</v>
       </c>
     </row>
     <row r="20">
@@ -7569,36 +7569,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9260997211236156</v>
+        <v>0.7064190493997634</v>
       </c>
       <c r="E20" t="n">
-        <v>3655.153856596648</v>
+        <v>9.029326467946719</v>
       </c>
       <c r="F20" t="n">
-        <v>23.85437681783542</v>
+        <v>1.478296044076899</v>
       </c>
       <c r="G20" t="n">
-        <v>55.7188977031609</v>
+        <v>2.978060400418576</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7607,51 +7607,51 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.9248090927727247</v>
+        <v>0.7033062237519566</v>
       </c>
       <c r="E21" t="n">
-        <v>3718.989139303541</v>
+        <v>9.12506401138876</v>
       </c>
       <c r="F21" t="n">
-        <v>30.51337015891831</v>
+        <v>1.475982283772601</v>
       </c>
       <c r="G21" t="n">
-        <v>59.50882663689752</v>
+        <v>2.997625085471234</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.9193125987211891</v>
+        <v>0.7018727905804635</v>
       </c>
       <c r="E22" t="n">
-        <v>3990.849161155916</v>
+        <v>9.169150441550304</v>
       </c>
       <c r="F22" t="n">
-        <v>26.31760663036128</v>
+        <v>1.468798166636697</v>
       </c>
       <c r="G22" t="n">
-        <v>58.51005171721292</v>
+        <v>3.009160809895652</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7665,22 +7665,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.917014295954912</v>
+        <v>0.6978866920398582</v>
       </c>
       <c r="E23" t="n">
-        <v>4104.524648549364</v>
+        <v>9.291746219590211</v>
       </c>
       <c r="F23" t="n">
-        <v>32.61942001804984</v>
+        <v>1.479639060105246</v>
       </c>
       <c r="G23" t="n">
-        <v>62.09582286703966</v>
+        <v>3.024820793965154</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7690,26 +7690,26 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.9137066934205937</v>
+        <v>0.6911591780723104</v>
       </c>
       <c r="E24" t="n">
-        <v>4268.120731584791</v>
+        <v>9.909618279968889</v>
       </c>
       <c r="F24" t="n">
-        <v>30.71221362696329</v>
+        <v>1.546210280876772</v>
       </c>
       <c r="G24" t="n">
-        <v>64.04294507781132</v>
+        <v>3.133798531754253</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7719,20 +7719,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.9067166832452848</v>
+        <v>0.6852030422576633</v>
       </c>
       <c r="E25" t="n">
-        <v>4613.850991854412</v>
+        <v>10.1007297786963</v>
       </c>
       <c r="F25" t="n">
-        <v>33.09018958857911</v>
+        <v>1.568593510175373</v>
       </c>
       <c r="G25" t="n">
-        <v>66.93245573310473</v>
+        <v>3.159145842460453</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/experiment_results.xlsx
+++ b/outputs/results/experiment_results.xlsx
@@ -485,16 +485,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.733368061432884</v>
+        <v>0.7279407279681209</v>
       </c>
       <c r="E2" t="n">
-        <v>8.555283320243431</v>
+        <v>8.7294274070847</v>
       </c>
       <c r="F2" t="n">
-        <v>1.463298633245535</v>
+        <v>1.488941607420576</v>
       </c>
       <c r="G2" t="n">
-        <v>2.895187190544179</v>
+        <v>2.920838841138348</v>
       </c>
     </row>
     <row r="3">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6852030422576633</v>
+        <v>0.6893743936746362</v>
       </c>
       <c r="E3" t="n">
-        <v>10.1007297786963</v>
+        <v>9.966885748636415</v>
       </c>
       <c r="F3" t="n">
-        <v>1.568593510175373</v>
+        <v>1.57589644650905</v>
       </c>
       <c r="G3" t="n">
-        <v>3.159145842460453</v>
+        <v>3.13131259038262</v>
       </c>
     </row>
     <row r="4">
@@ -543,16 +543,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7764012790623055</v>
+        <v>0.7597737896642778</v>
       </c>
       <c r="E4" t="n">
-        <v>7.174498366348186</v>
+        <v>7.70801615671096</v>
       </c>
       <c r="F4" t="n">
-        <v>1.429222463682855</v>
+        <v>1.484660811812581</v>
       </c>
       <c r="G4" t="n">
-        <v>2.619990435461164</v>
+        <v>2.705476920323415</v>
       </c>
     </row>
     <row r="5">
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7407147505087405</v>
+        <v>0.7384313989539995</v>
       </c>
       <c r="E5" t="n">
-        <v>8.31955384669476</v>
+        <v>8.392818586003585</v>
       </c>
       <c r="F5" t="n">
-        <v>1.441703872441011</v>
+        <v>1.455022630045817</v>
       </c>
       <c r="G5" t="n">
-        <v>2.865058721993581</v>
+        <v>2.874622307341991</v>
       </c>
     </row>
     <row r="6">
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6911591780723104</v>
+        <v>0.6973501461986943</v>
       </c>
       <c r="E6" t="n">
-        <v>9.909618279968889</v>
+        <v>9.710971836364093</v>
       </c>
       <c r="F6" t="n">
-        <v>1.546210280876772</v>
+        <v>1.547033802742398</v>
       </c>
       <c r="G6" t="n">
-        <v>3.133798531754253</v>
+        <v>3.097020781186702</v>
       </c>
     </row>
     <row r="7">
@@ -630,16 +630,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7849271941101076</v>
+        <v>0.7684014337337335</v>
       </c>
       <c r="E7" t="n">
-        <v>6.900931669161561</v>
+        <v>7.431185332177795</v>
       </c>
       <c r="F7" t="n">
-        <v>1.400113275166756</v>
+        <v>1.461107580309341</v>
       </c>
       <c r="G7" t="n">
-        <v>2.580592573269357</v>
+        <v>2.668931832342693</v>
       </c>
     </row>
     <row r="8">
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7320762222060214</v>
+        <v>0.721360312483511</v>
       </c>
       <c r="E8" t="n">
-        <v>8.240218765152733</v>
+        <v>8.569795486965806</v>
       </c>
       <c r="F8" t="n">
-        <v>1.44093578175406</v>
+        <v>1.495804948216018</v>
       </c>
       <c r="G8" t="n">
-        <v>2.838507130599666</v>
+        <v>2.896906652148339</v>
       </c>
     </row>
     <row r="9">
@@ -688,16 +688,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7064190493997634</v>
+        <v>0.688369542223954</v>
       </c>
       <c r="E9" t="n">
-        <v>9.029326467946719</v>
+        <v>9.584454082809753</v>
       </c>
       <c r="F9" t="n">
-        <v>1.478296044076899</v>
+        <v>1.523528669025294</v>
       </c>
       <c r="G9" t="n">
-        <v>2.978060400418576</v>
+        <v>3.068408159475235</v>
       </c>
     </row>
     <row r="10">
@@ -717,16 +717,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7674017976689097</v>
+        <v>0.752499335738111</v>
       </c>
       <c r="E10" t="n">
-        <v>7.153751292142754</v>
+        <v>7.612088911372538</v>
       </c>
       <c r="F10" t="n">
-        <v>1.43326579582687</v>
+        <v>1.493318797654427</v>
       </c>
       <c r="G10" t="n">
-        <v>2.617140378051686</v>
+        <v>2.693331512129927</v>
       </c>
     </row>
     <row r="11">
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7432601860868605</v>
+        <v>0.7319436368633315</v>
       </c>
       <c r="E11" t="n">
-        <v>7.896246648163004</v>
+        <v>8.244296537711081</v>
       </c>
       <c r="F11" t="n">
-        <v>1.409498141062684</v>
+        <v>1.462879937893037</v>
       </c>
       <c r="G11" t="n">
-        <v>2.788599287220091</v>
+        <v>2.8513450755519</v>
       </c>
     </row>
     <row r="12">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7131307929136529</v>
+        <v>0.6937095556455837</v>
       </c>
       <c r="E12" t="n">
-        <v>8.822901210340165</v>
+        <v>9.420217525810633</v>
       </c>
       <c r="F12" t="n">
-        <v>1.459813297914285</v>
+        <v>1.501678063253718</v>
       </c>
       <c r="G12" t="n">
-        <v>2.950977042970826</v>
+        <v>3.048321474812925</v>
       </c>
     </row>
     <row r="13">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7739393101809262</v>
+        <v>0.7608995577195691</v>
       </c>
       <c r="E13" t="n">
-        <v>6.952684654002248</v>
+        <v>7.353733093262636</v>
       </c>
       <c r="F13" t="n">
-        <v>1.415710792057568</v>
+        <v>1.471758053345773</v>
       </c>
       <c r="G13" t="n">
-        <v>2.591069203314092</v>
+        <v>2.658583743193927</v>
       </c>
     </row>
     <row r="14">
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.7293008737369711</v>
+        <v>0.7210339436317338</v>
       </c>
       <c r="E14" t="n">
-        <v>8.325576917097322</v>
+        <v>8.579833232622121</v>
       </c>
       <c r="F14" t="n">
-        <v>1.445064357889944</v>
+        <v>1.496604910981668</v>
       </c>
       <c r="G14" t="n">
-        <v>2.854199239187755</v>
+        <v>2.898606411703435</v>
       </c>
     </row>
     <row r="15">
@@ -862,16 +862,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.7033062237519566</v>
+        <v>0.6903983233378498</v>
       </c>
       <c r="E15" t="n">
-        <v>9.12506401138876</v>
+        <v>9.522057231202329</v>
       </c>
       <c r="F15" t="n">
-        <v>1.475982283772601</v>
+        <v>1.528527446624669</v>
       </c>
       <c r="G15" t="n">
-        <v>2.997625085471234</v>
+        <v>3.057944844552671</v>
       </c>
     </row>
     <row r="16">
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.7692721169045366</v>
+        <v>0.7541928888739091</v>
       </c>
       <c r="E16" t="n">
-        <v>7.096228067481114</v>
+        <v>7.56000227522441</v>
       </c>
       <c r="F16" t="n">
-        <v>1.413162110098043</v>
+        <v>1.474694267909985</v>
       </c>
       <c r="G16" t="n">
-        <v>2.60192706214428</v>
+        <v>2.682392262736036</v>
       </c>
     </row>
     <row r="17">
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7380617308509502</v>
+        <v>0.7314217202433815</v>
       </c>
       <c r="E17" t="n">
-        <v>8.05612946534877</v>
+        <v>8.260348517721848</v>
       </c>
       <c r="F17" t="n">
-        <v>1.417949268469599</v>
+        <v>1.464084904706317</v>
       </c>
       <c r="G17" t="n">
-        <v>2.817773466350075</v>
+        <v>2.854148826320528</v>
       </c>
     </row>
     <row r="18">
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.7073091198115176</v>
+        <v>0.6984895474710907</v>
       </c>
       <c r="E18" t="n">
-        <v>9.001951611673668</v>
+        <v>9.273204899077268</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4616654584226</v>
+        <v>1.499214670416661</v>
       </c>
       <c r="G18" t="n">
-        <v>2.982283718140724</v>
+        <v>3.023727105358379</v>
       </c>
     </row>
     <row r="19">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.7763307361005394</v>
+        <v>0.7625833435452005</v>
       </c>
       <c r="E19" t="n">
-        <v>6.879134359584474</v>
+        <v>7.301946858867508</v>
       </c>
       <c r="F19" t="n">
-        <v>1.393583149101872</v>
+        <v>1.453374252935564</v>
       </c>
       <c r="G19" t="n">
-        <v>2.572550339874818</v>
+        <v>2.647721551907941</v>
       </c>
     </row>
     <row r="20">
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.7324912709541652</v>
+        <v>0.7214742162190524</v>
       </c>
       <c r="E20" t="n">
-        <v>8.22745359547997</v>
+        <v>8.566292282783042</v>
       </c>
       <c r="F20" t="n">
-        <v>1.440764714983661</v>
+        <v>1.492709522129138</v>
       </c>
       <c r="G20" t="n">
-        <v>2.835170217281133</v>
+        <v>2.895841381991699</v>
       </c>
     </row>
     <row r="21">
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6978866920398582</v>
+        <v>0.6896906156082456</v>
       </c>
       <c r="E21" t="n">
-        <v>9.291746219590211</v>
+        <v>9.543823371414835</v>
       </c>
       <c r="F21" t="n">
-        <v>1.479639060105246</v>
+        <v>1.526324702240442</v>
       </c>
       <c r="G21" t="n">
-        <v>3.024820793965154</v>
+        <v>3.062139175540382</v>
       </c>
     </row>
     <row r="22">
@@ -1065,16 +1065,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7706212667568185</v>
+        <v>0.7503464079802475</v>
       </c>
       <c r="E22" t="n">
-        <v>7.054733840946562</v>
+        <v>7.678303996336015</v>
       </c>
       <c r="F22" t="n">
-        <v>1.413550598186365</v>
+        <v>1.496554686975512</v>
       </c>
       <c r="G22" t="n">
-        <v>2.595696349049179</v>
+        <v>2.7055008119037</v>
       </c>
     </row>
     <row r="23">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7413085705532879</v>
+        <v>0.7318582799590385</v>
       </c>
       <c r="E23" t="n">
-        <v>7.956270208126668</v>
+        <v>8.246921760340751</v>
       </c>
       <c r="F23" t="n">
-        <v>1.414562050415189</v>
+        <v>1.459459520639837</v>
       </c>
       <c r="G23" t="n">
-        <v>2.798125123197345</v>
+        <v>2.851317214600118</v>
       </c>
     </row>
     <row r="24">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.7018727905804635</v>
+        <v>0.6968320813903595</v>
       </c>
       <c r="E24" t="n">
-        <v>9.169150441550304</v>
+        <v>9.324181647813425</v>
       </c>
       <c r="F24" t="n">
-        <v>1.468798166636697</v>
+        <v>1.502992490705599</v>
       </c>
       <c r="G24" t="n">
-        <v>3.009160809895652</v>
+        <v>3.032739646614405</v>
       </c>
     </row>
     <row r="25">
@@ -1152,16 +1152,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.7780715702241299</v>
+        <v>0.7588234559079498</v>
       </c>
       <c r="E25" t="n">
-        <v>6.825593557307276</v>
+        <v>7.417585332311118</v>
       </c>
       <c r="F25" t="n">
-        <v>1.390597494698184</v>
+        <v>1.474271432047075</v>
       </c>
       <c r="G25" t="n">
-        <v>2.563920527182227</v>
+        <v>2.670403692621864</v>
       </c>
     </row>
   </sheetData>
@@ -1238,20 +1238,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.7936758319455359</v>
+        <v>0.792234478173077</v>
       </c>
       <c r="F2" t="n">
-        <v>6.620218579234972</v>
+        <v>6.666466564207651</v>
       </c>
       <c r="G2" t="n">
-        <v>1.213114754098361</v>
+        <v>1.15957650273224</v>
       </c>
       <c r="H2" t="n">
-        <v>2.572978542319188</v>
+        <v>2.58195014750627</v>
       </c>
     </row>
     <row r="3">
@@ -1272,20 +1272,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.7504037911645353</v>
+        <v>0.7607017181311997</v>
       </c>
       <c r="F3" t="n">
-        <v>8.008666530054645</v>
+        <v>7.678242188228045</v>
       </c>
       <c r="G3" t="n">
-        <v>1.263032786885246</v>
+        <v>1.28388548304942</v>
       </c>
       <c r="H3" t="n">
-        <v>2.829958750592426</v>
+        <v>2.770964126117125</v>
       </c>
     </row>
     <row r="4">
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8463079264905765</v>
+        <v>0.8714480623028008</v>
       </c>
       <c r="F4" t="n">
-        <v>4.9314393467451</v>
+        <v>4.124780603089613</v>
       </c>
       <c r="G4" t="n">
-        <v>1.164602598191787</v>
+        <v>1.081322766388076</v>
       </c>
       <c r="H4" t="n">
-        <v>2.22068443204907</v>
+        <v>2.030955588655157</v>
       </c>
     </row>
     <row r="5">
@@ -1340,20 +1340,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.789886551929678</v>
+        <v>0.7895576072989532</v>
       </c>
       <c r="F5" t="n">
-        <v>6.741803278688525</v>
+        <v>6.752357957650273</v>
       </c>
       <c r="G5" t="n">
-        <v>1.237704918032787</v>
+        <v>1.163811475409836</v>
       </c>
       <c r="H5" t="n">
-        <v>2.596498272421633</v>
+        <v>2.598529960891402</v>
       </c>
     </row>
     <row r="6">
@@ -1374,20 +1374,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7509333068569984</v>
+        <v>0.7606033590963361</v>
       </c>
       <c r="F6" t="n">
-        <v>7.991676229508196</v>
+        <v>7.681398184523484</v>
       </c>
       <c r="G6" t="n">
-        <v>1.25792349726776</v>
+        <v>1.286100831315334</v>
       </c>
       <c r="H6" t="n">
-        <v>2.826955293156967</v>
+        <v>2.771533543820728</v>
       </c>
     </row>
     <row r="7">
@@ -1408,20 +1408,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8478753090262897</v>
+        <v>0.8714480623028008</v>
       </c>
       <c r="F7" t="n">
-        <v>4.881147540983607</v>
+        <v>4.124780603089613</v>
       </c>
       <c r="G7" t="n">
-        <v>1.199453551912568</v>
+        <v>1.081322766388076</v>
       </c>
       <c r="H7" t="n">
-        <v>2.209331921867696</v>
+        <v>2.030955588655157</v>
       </c>
     </row>
     <row r="8">
@@ -1446,16 +1446,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7948003355139387</v>
+        <v>0.7852966830513423</v>
       </c>
       <c r="F8" t="n">
-        <v>6.311086458333333</v>
+        <v>6.60337919921875</v>
       </c>
       <c r="G8" t="n">
-        <v>1.153541666666667</v>
+        <v>1.182434895833333</v>
       </c>
       <c r="H8" t="n">
-        <v>2.512187584224819</v>
+        <v>2.569704107328069</v>
       </c>
     </row>
     <row r="9">
@@ -1476,20 +1476,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7755831248131256</v>
+        <v>0.7633867899815057</v>
       </c>
       <c r="F9" t="n">
-        <v>6.902127766927083</v>
+        <v>7.277236195052044</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1646484375</v>
+        <v>1.226473334554635</v>
       </c>
       <c r="H9" t="n">
-        <v>2.62719008960659</v>
+        <v>2.697635296894679</v>
       </c>
     </row>
     <row r="10">
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8566073981701908</v>
+        <v>0.8645966857339015</v>
       </c>
       <c r="F10" t="n">
-        <v>4.410158807519707</v>
+        <v>4.164441619427081</v>
       </c>
       <c r="G10" t="n">
-        <v>1.154289717120984</v>
+        <v>1.107890466223807</v>
       </c>
       <c r="H10" t="n">
-        <v>2.100037810973818</v>
+        <v>2.040696356498703</v>
       </c>
     </row>
     <row r="11">
@@ -1548,16 +1548,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.7904146666513786</v>
+        <v>0.7826693273756971</v>
       </c>
       <c r="F11" t="n">
-        <v>6.445971354166666</v>
+        <v>6.684185709635417</v>
       </c>
       <c r="G11" t="n">
-        <v>1.161822916666667</v>
+        <v>1.186028645833333</v>
       </c>
       <c r="H11" t="n">
-        <v>2.538891757079586</v>
+        <v>2.585379219695907</v>
       </c>
     </row>
     <row r="12">
@@ -1578,20 +1578,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.7751458559530351</v>
+        <v>0.7633681944944954</v>
       </c>
       <c r="F12" t="n">
-        <v>6.915576334635417</v>
+        <v>7.277808114731106</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1662890625</v>
+        <v>1.227003489121217</v>
       </c>
       <c r="H12" t="n">
-        <v>2.62974834055189</v>
+        <v>2.697741298703622</v>
       </c>
     </row>
     <row r="13">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8566073981701908</v>
+        <v>0.8645966857339015</v>
       </c>
       <c r="F13" t="n">
-        <v>4.410158807519707</v>
+        <v>4.164441619427081</v>
       </c>
       <c r="G13" t="n">
-        <v>1.154289717120984</v>
+        <v>1.107890466223807</v>
       </c>
       <c r="H13" t="n">
-        <v>2.100037810973818</v>
+        <v>2.040696356498703</v>
       </c>
     </row>
     <row r="14">
@@ -1650,16 +1650,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.7949206506006881</v>
+        <v>0.7866208433183421</v>
       </c>
       <c r="F14" t="n">
-        <v>6.307386067708333</v>
+        <v>6.562653548177084</v>
       </c>
       <c r="G14" t="n">
-        <v>1.138255208333333</v>
+        <v>1.1729296875</v>
       </c>
       <c r="H14" t="n">
-        <v>2.511450988514077</v>
+        <v>2.56176766085004</v>
       </c>
     </row>
     <row r="15">
@@ -1680,20 +1680,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7680467408509526</v>
+        <v>0.7665019904937718</v>
       </c>
       <c r="F15" t="n">
-        <v>7.13391552782618</v>
+        <v>7.181425610677084</v>
       </c>
       <c r="G15" t="n">
-        <v>1.215330930315326</v>
+        <v>1.184356770833333</v>
       </c>
       <c r="H15" t="n">
-        <v>2.67093907227892</v>
+        <v>2.679818204781265</v>
       </c>
     </row>
     <row r="16">
@@ -1718,16 +1718,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8751068639258174</v>
+        <v>0.8664022178760558</v>
       </c>
       <c r="F16" t="n">
-        <v>3.841192342057154</v>
+        <v>4.108910975744135</v>
       </c>
       <c r="G16" t="n">
-        <v>1.033516532165777</v>
+        <v>1.081957858672392</v>
       </c>
       <c r="H16" t="n">
-        <v>1.959896002867793</v>
+        <v>2.027044887451715</v>
       </c>
     </row>
     <row r="17">
@@ -1752,16 +1752,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.7908109329563064</v>
+        <v>0.7838902467226974</v>
       </c>
       <c r="F17" t="n">
-        <v>6.433783854166666</v>
+        <v>6.646635319010417</v>
       </c>
       <c r="G17" t="n">
-        <v>1.148489583333333</v>
+        <v>1.177513020833333</v>
       </c>
       <c r="H17" t="n">
-        <v>2.536490460097705</v>
+        <v>2.578106925441693</v>
       </c>
     </row>
     <row r="18">
@@ -1782,20 +1782,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.7680467408509526</v>
+        <v>0.7684897835723414</v>
       </c>
       <c r="F18" t="n">
-        <v>7.13391552782618</v>
+        <v>7.120289380208334</v>
       </c>
       <c r="G18" t="n">
-        <v>1.215330930315326</v>
+        <v>1.178119791666667</v>
       </c>
       <c r="H18" t="n">
-        <v>2.67093907227892</v>
+        <v>2.668387037183387</v>
       </c>
     </row>
     <row r="19">
@@ -1820,16 +1820,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8751068639258174</v>
+        <v>0.8664022178760558</v>
       </c>
       <c r="F19" t="n">
-        <v>3.841192342057154</v>
+        <v>4.108910975744135</v>
       </c>
       <c r="G19" t="n">
-        <v>1.033516532165777</v>
+        <v>1.081957858672392</v>
       </c>
       <c r="H19" t="n">
-        <v>1.959896002867793</v>
+        <v>2.027044887451715</v>
       </c>
     </row>
     <row r="20">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.7973142438510242</v>
+        <v>0.7832337359088997</v>
       </c>
       <c r="F20" t="n">
-        <v>6.23376911523042</v>
+        <v>6.66682685546875</v>
       </c>
       <c r="G20" t="n">
-        <v>1.19337943048716</v>
+        <v>1.179934895833333</v>
       </c>
       <c r="H20" t="n">
-        <v>2.496751712772101</v>
+        <v>2.582019917713407</v>
       </c>
     </row>
     <row r="21">
@@ -1888,16 +1888,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.7692910985611885</v>
+        <v>0.7689197068574851</v>
       </c>
       <c r="F21" t="n">
-        <v>7.095644270833335</v>
+        <v>7.107066731770833</v>
       </c>
       <c r="G21" t="n">
-        <v>1.176145833333333</v>
+        <v>1.187213541666667</v>
       </c>
       <c r="H21" t="n">
-        <v>2.663765055486939</v>
+        <v>2.665908237687643</v>
       </c>
     </row>
     <row r="22">
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8561937158488717</v>
+        <v>0.8636945821201067</v>
       </c>
       <c r="F22" t="n">
-        <v>4.422881951598273</v>
+        <v>4.192186566843507</v>
       </c>
       <c r="G22" t="n">
-        <v>1.131402354048381</v>
+        <v>1.097003378590595</v>
       </c>
       <c r="H22" t="n">
-        <v>2.103064894766272</v>
+        <v>2.047482983285455</v>
       </c>
     </row>
     <row r="23">
@@ -1952,20 +1952,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.7973142438510242</v>
+        <v>0.7805991238182262</v>
       </c>
       <c r="F23" t="n">
-        <v>6.23376911523042</v>
+        <v>6.74785654296875</v>
       </c>
       <c r="G23" t="n">
-        <v>1.19337943048716</v>
+        <v>1.183841145833333</v>
       </c>
       <c r="H23" t="n">
-        <v>2.496751712772101</v>
+        <v>2.597663670102184</v>
       </c>
     </row>
     <row r="24">
@@ -1990,16 +1990,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.7695029147552926</v>
+        <v>0.7708161427715885</v>
       </c>
       <c r="F24" t="n">
-        <v>7.089129687500001</v>
+        <v>7.048740266927084</v>
       </c>
       <c r="G24" t="n">
-        <v>1.180625</v>
+        <v>1.1812890625</v>
       </c>
       <c r="H24" t="n">
-        <v>2.662541959763264</v>
+        <v>2.654946377410867</v>
       </c>
     </row>
     <row r="25">
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8561937158488717</v>
+        <v>0.8636945821201067</v>
       </c>
       <c r="F25" t="n">
-        <v>4.422881951598273</v>
+        <v>4.192186566843507</v>
       </c>
       <c r="G25" t="n">
-        <v>1.131402354048381</v>
+        <v>1.097003378590595</v>
       </c>
       <c r="H25" t="n">
-        <v>2.103064894766272</v>
+        <v>2.047482983285455</v>
       </c>
     </row>
   </sheetData>
@@ -2047,7 +2047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2099,16 +2099,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.40607454541022</v>
+        <v>14.60794876394004</v>
       </c>
       <c r="C2" t="n">
-        <v>3.795533499445133</v>
+        <v>3.82203463667456</v>
       </c>
       <c r="D2" t="n">
-        <v>2.435095392676823</v>
+        <v>2.450784007202378</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5315986109846396</v>
+        <v>0.5250348406759622</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2133,16 +2133,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.902127766927083</v>
+        <v>7.384395011718749</v>
       </c>
       <c r="C3" t="n">
-        <v>2.62719008960659</v>
+        <v>2.717424334129425</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1646484375</v>
+        <v>1.2092265625</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7755831248131256</v>
+        <v>0.7599026112474786</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2167,16 +2167,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.319483537008693</v>
+        <v>7.277236195052044</v>
       </c>
       <c r="C4" t="n">
-        <v>2.705454404902935</v>
+        <v>2.697635296894679</v>
       </c>
       <c r="D4" t="n">
-        <v>1.23125584959547</v>
+        <v>1.226473334554635</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7620131532151315</v>
+        <v>0.7633867899815057</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2201,16 +2201,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.495694620935367</v>
+        <v>9.897482110004605</v>
       </c>
       <c r="C5" t="n">
-        <v>3.081508497625046</v>
+        <v>3.14602640008068</v>
       </c>
       <c r="D5" t="n">
-        <v>1.335213431573142</v>
+        <v>1.356159440869457</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6912554814226696</v>
+        <v>0.6781916993787966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2231,20 +2231,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.203620004065621</v>
+        <v>8.755208333333334</v>
       </c>
       <c r="C6" t="n">
-        <v>2.683956036164829</v>
+        <v>2.958920129596832</v>
       </c>
       <c r="D6" t="n">
-        <v>1.245229819782624</v>
+        <v>1.375</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7657803584725869</v>
+        <v>0.7153317698360269</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2265,20 +2265,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.848958333333334</v>
+        <v>13.86346909457347</v>
       </c>
       <c r="C7" t="n">
-        <v>2.974719874766922</v>
+        <v>3.723367977325565</v>
       </c>
       <c r="D7" t="n">
-        <v>1.458333333333333</v>
+        <v>2.419482628563245</v>
       </c>
       <c r="E7" t="n">
-        <v>0.712283567490428</v>
+        <v>0.5492409705363757</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2292,27 +2292,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.13028773425243</v>
+        <v>6.60337919921875</v>
       </c>
       <c r="C8" t="n">
-        <v>3.759027498469842</v>
+        <v>2.569704107328069</v>
       </c>
       <c r="D8" t="n">
-        <v>2.438865982668724</v>
+        <v>1.182434895833333</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5405655870343075</v>
+        <v>0.7852966830513423</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2333,20 +2333,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.311086458333333</v>
+        <v>8.018005737097463</v>
       </c>
       <c r="C9" t="n">
-        <v>2.512187584224819</v>
+        <v>2.831608330454172</v>
       </c>
       <c r="D9" t="n">
-        <v>1.153541666666667</v>
+        <v>1.325615816616178</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7948003355139387</v>
+        <v>0.7393012917883219</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2367,20 +2367,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.03876522838754</v>
+        <v>7.222196320606013</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8352716322052</v>
+        <v>2.687414430378391</v>
       </c>
       <c r="D10" t="n">
-        <v>1.275286307077897</v>
+        <v>1.283262233400668</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7386263144011876</v>
+        <v>0.7651763651749761</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2401,20 +2401,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.446006526491225</v>
+        <v>7.141927083333333</v>
       </c>
       <c r="C11" t="n">
-        <v>2.538898683778308</v>
+        <v>2.672438415255501</v>
       </c>
       <c r="D11" t="n">
-        <v>1.205196075450658</v>
+        <v>1.268229166666667</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7904135230528482</v>
+        <v>0.7677862518665388</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2435,20 +2435,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.831572893451869</v>
+        <v>14.05171147684802</v>
       </c>
       <c r="C12" t="n">
-        <v>2.613727777227741</v>
+        <v>3.748561254247824</v>
       </c>
       <c r="D12" t="n">
-        <v>1.268037158660416</v>
+        <v>2.464783595527964</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7778771571418783</v>
+        <v>0.543120427910345</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2462,27 +2462,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7.68359375</v>
+        <v>4.891963458333334</v>
       </c>
       <c r="C13" t="n">
-        <v>2.771929607692086</v>
+        <v>2.211778347469143</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3046875</v>
+        <v>1.143010416666667</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7501744160919682</v>
+        <v>0.840941925458399</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2496,27 +2496,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.27864696464104</v>
+        <v>6.990088418920929</v>
       </c>
       <c r="C14" t="n">
-        <v>3.778709695734912</v>
+        <v>2.64387753478124</v>
       </c>
       <c r="D14" t="n">
-        <v>2.47394704184728</v>
+        <v>1.35768034318703</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5357418115243153</v>
+        <v>0.7727231582453599</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2537,20 +2537,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.873335819010416</v>
+        <v>4.164441619427081</v>
       </c>
       <c r="C15" t="n">
-        <v>2.207563321630982</v>
+        <v>2.040696356498703</v>
       </c>
       <c r="D15" t="n">
-        <v>1.123299479166667</v>
+        <v>1.107890466223807</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8415475874730879</v>
+        <v>0.8645966857339015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2571,20 +2571,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.967877549695356</v>
+        <v>7.962239583333333</v>
       </c>
       <c r="C16" t="n">
-        <v>2.639673758193493</v>
+        <v>2.821744067652723</v>
       </c>
       <c r="D16" t="n">
-        <v>1.306788287971697</v>
+        <v>1.393229166666667</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7734453259645191</v>
+        <v>0.7411144813425496</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2605,20 +2605,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.410158807519707</v>
+        <v>13.48114083660913</v>
       </c>
       <c r="C17" t="n">
-        <v>2.100037810973818</v>
+        <v>3.671667310175192</v>
       </c>
       <c r="D17" t="n">
-        <v>1.154289717120984</v>
+        <v>2.327680511277916</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8566073981701908</v>
+        <v>0.5616720520586753</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2627,32 +2627,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.509676111990011</v>
+        <v>7.315750317708333</v>
       </c>
       <c r="C18" t="n">
-        <v>2.551406692785376</v>
+        <v>2.704764373787176</v>
       </c>
       <c r="D18" t="n">
-        <v>1.239186915521258</v>
+        <v>1.209526041666667</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7883433600676675</v>
+        <v>0.7621345356986301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2661,32 +2661,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.8828125</v>
+        <v>7.277808114731106</v>
       </c>
       <c r="C19" t="n">
-        <v>2.425450988991532</v>
+        <v>2.697741298703622</v>
       </c>
       <c r="D19" t="n">
-        <v>1.302083333333333</v>
+        <v>1.227003489121217</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8087253028136777</v>
+        <v>0.7633681944944954</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,32 +2695,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13.02943564528436</v>
+        <v>9.897482110004605</v>
       </c>
       <c r="C20" t="n">
-        <v>3.609630956937891</v>
+        <v>3.14602640008068</v>
       </c>
       <c r="D20" t="n">
-        <v>2.298979634380527</v>
+        <v>1.356159440869457</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5763588661783052</v>
+        <v>0.6781916993787966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.915576334635417</v>
+        <v>9.12890625</v>
       </c>
       <c r="C21" t="n">
-        <v>2.62974834055189</v>
+        <v>3.021407991317955</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1662890625</v>
+        <v>1.388020833333333</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7751458559530351</v>
+        <v>0.7031812965973205</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2775,20 +2775,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7.319483537008693</v>
+        <v>12.30747637503531</v>
       </c>
       <c r="C22" t="n">
-        <v>2.705454404902935</v>
+        <v>3.508201301954508</v>
       </c>
       <c r="D22" t="n">
-        <v>1.23125584959547</v>
+        <v>2.265576069564856</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7620131532151315</v>
+        <v>0.5998327642156378</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2802,27 +2802,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9.495694620935367</v>
+        <v>6.684185709635417</v>
       </c>
       <c r="C23" t="n">
-        <v>3.081508497625046</v>
+        <v>2.585379219695907</v>
       </c>
       <c r="D23" t="n">
-        <v>1.335213431573142</v>
+        <v>1.186028645833333</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6912554814226696</v>
+        <v>0.7826693273756971</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2836,27 +2836,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7.201956707510487</v>
+        <v>7.990697199945338</v>
       </c>
       <c r="C24" t="n">
-        <v>2.683646159148126</v>
+        <v>2.826782128135336</v>
       </c>
       <c r="D24" t="n">
-        <v>1.245370976103236</v>
+        <v>1.321720240666331</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7658344391601686</v>
+        <v>0.7401892058896764</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2870,27 +2870,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.975260416666666</v>
+        <v>7.222196320606013</v>
       </c>
       <c r="C25" t="n">
-        <v>2.995873898659065</v>
+        <v>2.687414430378391</v>
       </c>
       <c r="D25" t="n">
-        <v>1.481770833333333</v>
+        <v>1.283262233400668</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7081769615526075</v>
+        <v>0.7651763651749761</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2904,27 +2904,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12.45786590105087</v>
+        <v>7.016927083333333</v>
       </c>
       <c r="C26" t="n">
-        <v>3.529570214778404</v>
+        <v>2.648948297595356</v>
       </c>
       <c r="D26" t="n">
-        <v>2.274010389056618</v>
+        <v>1.2578125</v>
       </c>
       <c r="E26" t="n">
-        <v>0.594942975352127</v>
+        <v>0.7718505216606705</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2945,20 +2945,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.445971354166666</v>
+        <v>12.70522392275683</v>
       </c>
       <c r="C27" t="n">
-        <v>2.538891757079586</v>
+        <v>3.56443879492366</v>
       </c>
       <c r="D27" t="n">
-        <v>1.161822916666667</v>
+        <v>2.33497466565136</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7904146666513786</v>
+        <v>0.5869003374644813</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2972,27 +2972,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8.039008691173741</v>
+        <v>4.906307338541667</v>
       </c>
       <c r="C28" t="n">
-        <v>2.83531456652939</v>
+        <v>2.215018586500273</v>
       </c>
       <c r="D28" t="n">
-        <v>1.275678326307649</v>
+        <v>1.146786458333333</v>
       </c>
       <c r="E28" t="n">
-        <v>0.738618398413604</v>
+        <v>0.840475546265908</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3006,27 +3006,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6.446006526491225</v>
+        <v>6.990088418920929</v>
       </c>
       <c r="C29" t="n">
-        <v>2.538898683778308</v>
+        <v>2.64387753478124</v>
       </c>
       <c r="D29" t="n">
-        <v>1.205196075450658</v>
+        <v>1.35768034318703</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7904135230528482</v>
+        <v>0.7727231582453599</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3040,27 +3040,27 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6.815450332762185</v>
+        <v>4.164441619427081</v>
       </c>
       <c r="C30" t="n">
-        <v>2.610641747303177</v>
+        <v>2.040696356498703</v>
       </c>
       <c r="D30" t="n">
-        <v>1.26684363889451</v>
+        <v>1.107890466223807</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7784013686331994</v>
+        <v>0.8645966857339015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7.173177083333333</v>
+        <v>8.002604166666666</v>
       </c>
       <c r="C31" t="n">
-        <v>2.678278753851685</v>
+        <v>2.828887443265756</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2734375</v>
+        <v>1.411458333333333</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7667701844180059</v>
+        <v>0.7398020608881946</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
@@ -3119,30 +3119,30 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>12.94081369323765</v>
+        <v>14.62754429687408</v>
       </c>
       <c r="C32" t="n">
-        <v>3.597334248195134</v>
+        <v>3.824597272507797</v>
       </c>
       <c r="D32" t="n">
-        <v>2.341174268684752</v>
+        <v>2.449263688889946</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5792403343607087</v>
+        <v>0.5243977084151321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
@@ -3153,30 +3153,30 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.855042720052083</v>
+        <v>7.181425610677084</v>
       </c>
       <c r="C33" t="n">
-        <v>2.203416147724275</v>
+        <v>2.679818204781265</v>
       </c>
       <c r="D33" t="n">
-        <v>1.1256171875</v>
+        <v>1.184356770833333</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8421423721893873</v>
+        <v>0.7665019904937718</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
@@ -3187,30 +3187,30 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7.065501787383496</v>
+        <v>7.338588243826723</v>
       </c>
       <c r="C34" t="n">
-        <v>2.658101161992052</v>
+        <v>2.708982879943453</v>
       </c>
       <c r="D34" t="n">
-        <v>1.314924671639692</v>
+        <v>1.242082918155629</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7702711560412308</v>
+        <v>0.7613919797523615</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
@@ -3221,118 +3221,118 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4.410158807519707</v>
+        <v>9.04606133796708</v>
       </c>
       <c r="C35" t="n">
-        <v>2.100037810973818</v>
+        <v>3.007667092277182</v>
       </c>
       <c r="D35" t="n">
-        <v>1.154289717120984</v>
+        <v>1.33464218857777</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8566073981701908</v>
+        <v>0.7058749291859038</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6.514903415820553</v>
+        <v>9.416666666666666</v>
       </c>
       <c r="C36" t="n">
-        <v>2.552430883652005</v>
+        <v>3.068658773253661</v>
       </c>
       <c r="D36" t="n">
-        <v>1.240550574066643</v>
+        <v>1.432291666666667</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7881733986831617</v>
+        <v>0.69382500884208</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5.9296875</v>
+        <v>13.87265249496716</v>
       </c>
       <c r="C37" t="n">
-        <v>2.43509496734727</v>
+        <v>3.724600984664955</v>
       </c>
       <c r="D37" t="n">
-        <v>1.317708333333333</v>
+        <v>2.420509662653716</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8072012016408784</v>
+        <v>0.5489423800017558</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14.06611103663894</v>
+        <v>6.562653548177084</v>
       </c>
       <c r="C38" t="n">
-        <v>3.750481440647179</v>
+        <v>2.56176766085004</v>
       </c>
       <c r="D38" t="n">
-        <v>2.408424017038099</v>
+        <v>1.1729296875</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5426522383430887</v>
+        <v>0.7866208433183421</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3346,27 +3346,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7.431727897135416</v>
+        <v>8.009253332519807</v>
       </c>
       <c r="C39" t="n">
-        <v>2.726119567652053</v>
+        <v>2.830062425551742</v>
       </c>
       <c r="D39" t="n">
-        <v>1.199466145833333</v>
+        <v>1.323560415327578</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7583636223157342</v>
+        <v>0.7395858688567298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3380,27 +3380,27 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7.415072838564298</v>
+        <v>7.327002620779894</v>
       </c>
       <c r="C40" t="n">
-        <v>2.723063135251237</v>
+        <v>2.706843663897103</v>
       </c>
       <c r="D40" t="n">
-        <v>1.257122873589612</v>
+        <v>1.300399789427047</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7589051475274948</v>
+        <v>0.7617686765347249</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3414,27 +3414,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>9.687931768167727</v>
+        <v>7.127604166666667</v>
       </c>
       <c r="C41" t="n">
-        <v>3.112544259631938</v>
+        <v>2.669757323553335</v>
       </c>
       <c r="D41" t="n">
-        <v>1.343258069192568</v>
+        <v>1.265625</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6850050523762174</v>
+        <v>0.7682519494471164</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3448,27 +3448,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7.13391552782618</v>
+        <v>14.05633128457117</v>
       </c>
       <c r="C42" t="n">
-        <v>2.67093907227892</v>
+        <v>3.749177414389878</v>
       </c>
       <c r="D42" t="n">
-        <v>1.215330930315326</v>
+        <v>2.461773244413503</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7680467408509526</v>
+        <v>0.5429702187504737</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3482,27 +3482,27 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9.015625</v>
+        <v>4.812175697916667</v>
       </c>
       <c r="C43" t="n">
-        <v>3.002603037366078</v>
+        <v>2.193667180298021</v>
       </c>
       <c r="D43" t="n">
-        <v>1.432291666666667</v>
+        <v>1.12228125</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7068645410982525</v>
+        <v>0.843536157335222</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3516,27 +3516,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>14.15454261836912</v>
+        <v>6.947593417890073</v>
       </c>
       <c r="C44" t="n">
-        <v>3.762252333160167</v>
+        <v>2.635828791460112</v>
       </c>
       <c r="D44" t="n">
-        <v>2.436855952043454</v>
+        <v>1.337667319797364</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5397769598913025</v>
+        <v>0.7741048474380903</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3550,27 +3550,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>6.307386067708333</v>
+        <v>4.108910975744135</v>
       </c>
       <c r="C45" t="n">
-        <v>2.511450988514077</v>
+        <v>2.027044887451715</v>
       </c>
       <c r="D45" t="n">
-        <v>1.138255208333333</v>
+        <v>1.081957858672392</v>
       </c>
       <c r="E45" t="n">
-        <v>0.7949206506006881</v>
+        <v>0.8664022178760558</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3584,27 +3584,27 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7.868532560431888</v>
+        <v>7.875</v>
       </c>
       <c r="C46" t="n">
-        <v>2.805090472771224</v>
+        <v>2.806243040080456</v>
       </c>
       <c r="D46" t="n">
-        <v>1.281772768371954</v>
+        <v>1.369791666666667</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7441612863239604</v>
+        <v>0.7439510029697041</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3618,27 +3618,27 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6.596448999579057</v>
+        <v>13.50822095005087</v>
       </c>
       <c r="C47" t="n">
-        <v>2.568355310228524</v>
+        <v>3.675353173512836</v>
       </c>
       <c r="D47" t="n">
-        <v>1.208739251156961</v>
+        <v>2.327165953683237</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7855220126598454</v>
+        <v>0.5607915649620119</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3647,32 +3647,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6.938009589828869</v>
+        <v>7.120289380208334</v>
       </c>
       <c r="C48" t="n">
-        <v>2.634010172688949</v>
+        <v>2.668387037183387</v>
       </c>
       <c r="D48" t="n">
-        <v>1.255804634100629</v>
+        <v>1.178119791666667</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7744164575413007</v>
+        <v>0.7684897835723414</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8.088541666666666</v>
+        <v>7.338588243826723</v>
       </c>
       <c r="C49" t="n">
-        <v>2.844036157763587</v>
+        <v>2.708982879943453</v>
       </c>
       <c r="D49" t="n">
-        <v>1.348958333333333</v>
+        <v>1.242082918155629</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7370078754047291</v>
+        <v>0.7613919797523615</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3715,32 +3715,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>14.30474564252502</v>
+        <v>9.04606133796708</v>
       </c>
       <c r="C50" t="n">
-        <v>3.78216150402452</v>
+        <v>3.007667092277182</v>
       </c>
       <c r="D50" t="n">
-        <v>2.471588016630491</v>
+        <v>1.33464218857777</v>
       </c>
       <c r="E50" t="n">
-        <v>0.53489323497879</v>
+        <v>0.7058749291859038</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3749,32 +3749,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4.993127173177083</v>
+        <v>9.352864583333334</v>
       </c>
       <c r="C51" t="n">
-        <v>2.234530638227429</v>
+        <v>3.058245343875035</v>
       </c>
       <c r="D51" t="n">
-        <v>1.123846354166667</v>
+        <v>1.4140625</v>
       </c>
       <c r="E51" t="n">
-        <v>0.8376526724143862</v>
+        <v>0.6958994798828346</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3783,32 +3783,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6.782778822465871</v>
+        <v>12.31517698817004</v>
       </c>
       <c r="C52" t="n">
-        <v>2.604376858764083</v>
+        <v>3.509298646192718</v>
       </c>
       <c r="D52" t="n">
-        <v>1.281870647598566</v>
+        <v>2.262989260909706</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7794636552926073</v>
+        <v>0.5995823852607594</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3817,32 +3817,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3.841192342057154</v>
+        <v>6.646635319010417</v>
       </c>
       <c r="C53" t="n">
-        <v>1.959896002867793</v>
+        <v>2.578106925441693</v>
       </c>
       <c r="D53" t="n">
-        <v>1.033516532165777</v>
+        <v>1.177513020833333</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8751068639258174</v>
+        <v>0.7838902467226974</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3851,32 +3851,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>6.165941091328225</v>
+        <v>8.010323493982217</v>
       </c>
       <c r="C54" t="n">
-        <v>2.483131307709728</v>
+        <v>2.830251489529193</v>
       </c>
       <c r="D54" t="n">
-        <v>1.193151110026758</v>
+        <v>1.324314119028163</v>
       </c>
       <c r="E54" t="n">
-        <v>0.7995196149609549</v>
+        <v>0.7395510734574777</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3885,32 +3885,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6.489583333333333</v>
+        <v>7.327002620779894</v>
       </c>
       <c r="C55" t="n">
-        <v>2.547466061272129</v>
+        <v>2.706843663897103</v>
       </c>
       <c r="D55" t="n">
-        <v>1.375</v>
+        <v>1.300399789427047</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7889966598546635</v>
+        <v>0.7617686765347249</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3919,32 +3919,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>13.10566528418172</v>
+        <v>7.002604166666667</v>
       </c>
       <c r="C56" t="n">
-        <v>3.620174758790205</v>
+        <v>2.646243406541935</v>
       </c>
       <c r="D56" t="n">
-        <v>2.300752231604763</v>
+        <v>1.255208333333333</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5738803236280002</v>
+        <v>0.772316219241248</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3958,27 +3958,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7.518082584635416</v>
+        <v>12.71046696320333</v>
       </c>
       <c r="C57" t="n">
-        <v>2.741912213152605</v>
+        <v>3.565174184132289</v>
       </c>
       <c r="D57" t="n">
-        <v>1.205611979166667</v>
+        <v>2.333089836208065</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7555558723318306</v>
+        <v>0.5867298644171525</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3992,27 +3992,27 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7.415072838564298</v>
+        <v>4.827398354166667</v>
       </c>
       <c r="C58" t="n">
-        <v>2.723063135251237</v>
+        <v>2.197134122935299</v>
       </c>
       <c r="D58" t="n">
-        <v>1.257122873589612</v>
+        <v>1.126135416666667</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7589051475274948</v>
+        <v>0.8430412054793553</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4026,27 +4026,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>9.687931768167727</v>
+        <v>6.947593417890073</v>
       </c>
       <c r="C59" t="n">
-        <v>3.112544259631938</v>
+        <v>2.635828791460112</v>
       </c>
       <c r="D59" t="n">
-        <v>1.343258069192568</v>
+        <v>1.337667319797364</v>
       </c>
       <c r="E59" t="n">
-        <v>0.6850050523762174</v>
+        <v>0.7741048474380903</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4060,27 +4060,27 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7.13391552782618</v>
+        <v>4.108910975744135</v>
       </c>
       <c r="C60" t="n">
-        <v>2.67093907227892</v>
+        <v>2.027044887451715</v>
       </c>
       <c r="D60" t="n">
-        <v>1.215330930315326</v>
+        <v>1.081957858672392</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7680467408509526</v>
+        <v>0.8664022178760558</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
@@ -4105,16 +4105,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>9.151041666666666</v>
+        <v>7.915364583333333</v>
       </c>
       <c r="C61" t="n">
-        <v>3.025068869739442</v>
+        <v>2.813425773560293</v>
       </c>
       <c r="D61" t="n">
-        <v>1.447916666666667</v>
+        <v>1.388020833333333</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7024615821546099</v>
+        <v>0.742638582515349</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
@@ -4139,30 +4139,30 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>12.49985723238198</v>
+        <v>14.66075845287511</v>
       </c>
       <c r="C62" t="n">
-        <v>3.535513715484919</v>
+        <v>3.828936987321039</v>
       </c>
       <c r="D62" t="n">
-        <v>2.27377654521874</v>
+        <v>2.453247114415234</v>
       </c>
       <c r="E62" t="n">
-        <v>0.593577662555772</v>
+        <v>0.5233177780873517</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
@@ -4173,30 +4173,30 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>6.433783854166666</v>
+        <v>7.107066731770833</v>
       </c>
       <c r="C63" t="n">
-        <v>2.536490460097705</v>
+        <v>2.665908237687643</v>
       </c>
       <c r="D63" t="n">
-        <v>1.148489583333333</v>
+        <v>1.187213541666667</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7908109329563064</v>
+        <v>0.7689197068574851</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
@@ -4207,30 +4207,30 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>7.868679783503251</v>
+        <v>7.64877452991</v>
       </c>
       <c r="C64" t="n">
-        <v>2.805116714773781</v>
+        <v>2.765641793492064</v>
       </c>
       <c r="D64" t="n">
-        <v>1.281872730748717</v>
+        <v>1.287068127821274</v>
       </c>
       <c r="E64" t="n">
-        <v>0.744156499489705</v>
+        <v>0.7513065337277043</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
@@ -4241,93 +4241,93 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>6.596448999579057</v>
+        <v>9.159287975851562</v>
       </c>
       <c r="C65" t="n">
-        <v>2.568355310228524</v>
+        <v>3.026431558098012</v>
       </c>
       <c r="D65" t="n">
-        <v>1.208739251156961</v>
+        <v>1.323886393965703</v>
       </c>
       <c r="E65" t="n">
-        <v>0.7855220126598454</v>
+        <v>0.7021934603519439</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>6.848163172461672</v>
+        <v>9.143229166666666</v>
       </c>
       <c r="C66" t="n">
-        <v>2.616899534269834</v>
+        <v>3.023777301103153</v>
       </c>
       <c r="D66" t="n">
-        <v>1.248463333693178</v>
+        <v>1.380208333333333</v>
       </c>
       <c r="E66" t="n">
-        <v>0.7773377381830323</v>
+        <v>0.7027155990167431</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>8.08984375</v>
+        <v>13.89455715268638</v>
       </c>
       <c r="C67" t="n">
-        <v>2.844265063245688</v>
+        <v>3.727540362314858</v>
       </c>
       <c r="D67" t="n">
-        <v>1.346354166666667</v>
+        <v>2.422884108118047</v>
       </c>
       <c r="E67" t="n">
-        <v>0.7369655392610402</v>
+        <v>0.5482301684920035</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4339,165 +4339,165 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>12.97887920133208</v>
+        <v>6.66682685546875</v>
       </c>
       <c r="C68" t="n">
-        <v>3.602621157064962</v>
+        <v>2.582019917713407</v>
       </c>
       <c r="D68" t="n">
-        <v>2.341823085894539</v>
+        <v>1.179934895833333</v>
       </c>
       <c r="E68" t="n">
-        <v>0.5780026664027367</v>
+        <v>0.7832337359088997</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4.957468945638021</v>
+        <v>8.066787055892421</v>
       </c>
       <c r="C69" t="n">
-        <v>2.226537434142534</v>
+        <v>2.840208981024534</v>
       </c>
       <c r="D69" t="n">
-        <v>1.12313671875</v>
+        <v>1.339081316837714</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8388120696711805</v>
+        <v>0.737715208264352</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6.846473218586518</v>
+        <v>7.263186183200996</v>
       </c>
       <c r="C70" t="n">
-        <v>2.616576621959792</v>
+        <v>2.695029903953015</v>
       </c>
       <c r="D70" t="n">
-        <v>1.299746023713305</v>
+        <v>1.282063956523264</v>
       </c>
       <c r="E70" t="n">
-        <v>0.7773926856109383</v>
+        <v>0.7638436142916929</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3.841192342057154</v>
+        <v>6.940104166666667</v>
       </c>
       <c r="C71" t="n">
-        <v>1.959896002867793</v>
+        <v>2.63440774495268</v>
       </c>
       <c r="D71" t="n">
-        <v>1.033516532165777</v>
+        <v>1.239583333333333</v>
       </c>
       <c r="E71" t="n">
-        <v>0.8751068639258174</v>
+        <v>0.7743483541383139</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>6.166417449893065</v>
+        <v>14.07704423771455</v>
       </c>
       <c r="C72" t="n">
-        <v>2.483227224780903</v>
+        <v>3.75193873053846</v>
       </c>
       <c r="D72" t="n">
-        <v>1.19348486742094</v>
+        <v>2.459500383713669</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7995041265631448</v>
+        <v>0.5422967545120103</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4509,29 +4509,29 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6.484375</v>
+        <v>4.917894968750001</v>
       </c>
       <c r="C73" t="n">
-        <v>2.54644359843292</v>
+        <v>2.217632739826413</v>
       </c>
       <c r="D73" t="n">
-        <v>1.369791666666667</v>
+        <v>1.1311875</v>
       </c>
       <c r="E73" t="n">
-        <v>0.789166004429419</v>
+        <v>0.8400987842223776</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4543,20 +4543,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>14.19005594854985</v>
+        <v>7.026008791705352</v>
       </c>
       <c r="C74" t="n">
-        <v>3.766969066577247</v>
+        <v>2.650661953494891</v>
       </c>
       <c r="D74" t="n">
-        <v>2.422228498334384</v>
+        <v>1.360186339239964</v>
       </c>
       <c r="E74" t="n">
-        <v>0.5386222738501618</v>
+        <v>0.7715552375565464</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4570,27 +4570,27 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>7.095644270833335</v>
+        <v>4.192186566843507</v>
       </c>
       <c r="C75" t="n">
-        <v>2.663765055486939</v>
+        <v>2.047482983285455</v>
       </c>
       <c r="D75" t="n">
-        <v>1.176145833333333</v>
+        <v>1.097003378590595</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7692910985611885</v>
+        <v>0.8636945821201067</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4604,27 +4604,27 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>7.162533646821227</v>
+        <v>8.178385416666666</v>
       </c>
       <c r="C76" t="n">
-        <v>2.676291024313542</v>
+        <v>2.859787652373278</v>
       </c>
       <c r="D76" t="n">
-        <v>1.253893317980446</v>
+        <v>1.434895833333333</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7671162467981812</v>
+        <v>0.734086681490197</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4638,27 +4638,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>9.724621420293738</v>
+        <v>13.54405338304514</v>
       </c>
       <c r="C77" t="n">
-        <v>3.118432526173003</v>
+        <v>3.680224637579226</v>
       </c>
       <c r="D77" t="n">
-        <v>1.318999587074434</v>
+        <v>2.329489702574353</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6838121192170739</v>
+        <v>0.5596265035614609</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4679,20 +4679,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>8.017726197709775</v>
+        <v>7.048740266927084</v>
       </c>
       <c r="C78" t="n">
-        <v>2.831558969491855</v>
+        <v>2.654946377410867</v>
       </c>
       <c r="D78" t="n">
-        <v>1.295108790575545</v>
+        <v>1.1812890625</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7393103807762392</v>
+        <v>0.7708161427715885</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4713,20 +4713,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>9.559895833333334</v>
+        <v>7.64877452991</v>
       </c>
       <c r="C79" t="n">
-        <v>3.091908121748338</v>
+        <v>2.765641793492064</v>
       </c>
       <c r="D79" t="n">
-        <v>1.411458333333333</v>
+        <v>1.287068127821274</v>
       </c>
       <c r="E79" t="n">
-        <v>0.6891680330363041</v>
+        <v>0.7513065337277043</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4747,20 +4747,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>14.20829741850054</v>
+        <v>9.159287975851562</v>
       </c>
       <c r="C80" t="n">
-        <v>3.769389528624038</v>
+        <v>3.026431558098012</v>
       </c>
       <c r="D80" t="n">
-        <v>2.442905160797818</v>
+        <v>1.323886393965703</v>
       </c>
       <c r="E80" t="n">
-        <v>0.5380291678075927</v>
+        <v>0.7021934603519439</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4769,32 +4769,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>6.408752091471354</v>
+        <v>9.220052083333334</v>
       </c>
       <c r="C81" t="n">
-        <v>2.53155132112137</v>
+        <v>3.036453866491855</v>
       </c>
       <c r="D81" t="n">
-        <v>1.15416015625</v>
+        <v>1.393229166666667</v>
       </c>
       <c r="E81" t="n">
-        <v>0.7916248196524379</v>
+        <v>0.7002177665390996</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4803,32 +4803,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>8.119305660535959</v>
+        <v>12.3406046915125</v>
       </c>
       <c r="C82" t="n">
-        <v>2.849439534458655</v>
+        <v>3.51291968190457</v>
       </c>
       <c r="D82" t="n">
-        <v>1.321942730189919</v>
+        <v>2.262390813637619</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7360076100364905</v>
+        <v>0.598755624887728</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4849,20 +4849,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6.23376911523042</v>
+        <v>6.74785654296875</v>
       </c>
       <c r="C83" t="n">
-        <v>2.496751712772101</v>
+        <v>2.597663670102184</v>
       </c>
       <c r="D83" t="n">
-        <v>1.19337943048716</v>
+        <v>1.183841145833333</v>
       </c>
       <c r="E83" t="n">
-        <v>0.7973142438510242</v>
+        <v>0.7805991238182262</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4883,20 +4883,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6.838607703808216</v>
+        <v>8.067857217354829</v>
       </c>
       <c r="C84" t="n">
-        <v>2.61507317370054</v>
+        <v>2.840397369621869</v>
       </c>
       <c r="D84" t="n">
-        <v>1.2483466455104</v>
+        <v>1.3398350205383</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7776484262039685</v>
+        <v>0.7376804128650999</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4917,20 +4917,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>7.555989583333333</v>
+        <v>7.263186183200996</v>
       </c>
       <c r="C85" t="n">
-        <v>2.748816033010091</v>
+        <v>2.695029903953015</v>
       </c>
       <c r="D85" t="n">
-        <v>1.283854166666667</v>
+        <v>1.282063956523264</v>
       </c>
       <c r="E85" t="n">
-        <v>0.7543233581734776</v>
+        <v>0.7638436142916929</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4951,20 +4951,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>14.33796500553242</v>
+        <v>6.815104166666667</v>
       </c>
       <c r="C86" t="n">
-        <v>3.786550541790301</v>
+        <v>2.610575447418953</v>
       </c>
       <c r="D86" t="n">
-        <v>2.471628838727938</v>
+        <v>1.229166666666667</v>
       </c>
       <c r="E86" t="n">
-        <v>0.5338131353495799</v>
+        <v>0.7784126239324456</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -4973,32 +4973,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4.76177138671875</v>
+        <v>12.7268584696734</v>
       </c>
       <c r="C87" t="n">
-        <v>2.182148342051647</v>
+        <v>3.567472280154871</v>
       </c>
       <c r="D87" t="n">
-        <v>1.101783854166667</v>
+        <v>2.330688275738151</v>
       </c>
       <c r="E87" t="n">
-        <v>0.8451750110911876</v>
+        <v>0.5861969083801396</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5019,20 +5019,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>6.837817590584454</v>
+        <v>4.934539500000001</v>
       </c>
       <c r="C88" t="n">
-        <v>2.614922100289883</v>
+        <v>2.221382339895589</v>
       </c>
       <c r="D88" t="n">
-        <v>1.309881094722067</v>
+        <v>1.1355625</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7776741160704426</v>
+        <v>0.8395576012976028</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5053,20 +5053,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4.422881951598273</v>
+        <v>7.026008791705352</v>
       </c>
       <c r="C89" t="n">
-        <v>2.103064894766272</v>
+        <v>2.650661953494891</v>
       </c>
       <c r="D89" t="n">
-        <v>1.131402354048381</v>
+        <v>1.360186339239964</v>
       </c>
       <c r="E89" t="n">
-        <v>0.8561937158488717</v>
+        <v>0.7715552375565464</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5087,20 +5087,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>6.521352527912139</v>
+        <v>4.192186566843507</v>
       </c>
       <c r="C90" t="n">
-        <v>2.55369389863236</v>
+        <v>2.047482983285455</v>
       </c>
       <c r="D90" t="n">
-        <v>1.224419947453137</v>
+        <v>1.097003378590595</v>
       </c>
       <c r="E90" t="n">
-        <v>0.7879637112313793</v>
+        <v>0.8636945821201067</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5125,16 +5125,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>5.446614583333333</v>
+        <v>8.208333333333334</v>
       </c>
       <c r="C91" t="n">
-        <v>2.333798316764611</v>
+        <v>2.865018906278514</v>
       </c>
       <c r="D91" t="n">
-        <v>1.2421875</v>
+        <v>1.447916666666667</v>
       </c>
       <c r="E91" t="n">
-        <v>0.8229079109494497</v>
+        <v>0.7331129501853528</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5159,25 +5159,25 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>13.2405913434712</v>
+        <v>14.94827431030217</v>
       </c>
       <c r="C92" t="n">
-        <v>3.63876233676661</v>
+        <v>3.866299821573874</v>
       </c>
       <c r="D92" t="n">
-        <v>2.312337159678259</v>
+        <v>2.495309613221678</v>
       </c>
       <c r="E92" t="n">
-        <v>0.5694933163703086</v>
+        <v>0.5341256147346998</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5193,25 +5193,25 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>7.089129687500001</v>
+        <v>7.708303367904539</v>
       </c>
       <c r="C93" t="n">
-        <v>2.662541959763264</v>
+        <v>2.776383145011606</v>
       </c>
       <c r="D93" t="n">
-        <v>1.180625</v>
+        <v>1.224106167056987</v>
       </c>
       <c r="E93" t="n">
-        <v>0.7695029147552926</v>
+        <v>0.7597648385080793</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5227,25 +5227,25 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>7.164978383442748</v>
+        <v>7.678242188228045</v>
       </c>
       <c r="C94" t="n">
-        <v>2.676747725028032</v>
+        <v>2.770964126117125</v>
       </c>
       <c r="D94" t="n">
-        <v>1.255088123723449</v>
+        <v>1.28388548304942</v>
       </c>
       <c r="E94" t="n">
-        <v>0.7670367582445375</v>
+        <v>0.7607017181311997</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5261,25 +5261,25 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>9.724621420293738</v>
+        <v>10.24551051609158</v>
       </c>
       <c r="C95" t="n">
-        <v>3.118432526173003</v>
+        <v>3.200860902334181</v>
       </c>
       <c r="D95" t="n">
-        <v>1.318999587074434</v>
+        <v>1.373448728780005</v>
       </c>
       <c r="E95" t="n">
-        <v>0.6838121192170739</v>
+        <v>0.6806908400039355</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5291,29 +5291,29 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>8.015633897927469</v>
+        <v>9.254098360655737</v>
       </c>
       <c r="C96" t="n">
-        <v>2.831189484638474</v>
+        <v>3.042054956876311</v>
       </c>
       <c r="D96" t="n">
-        <v>1.295218296010705</v>
+        <v>1.502732240437158</v>
       </c>
       <c r="E96" t="n">
-        <v>0.7393784101426832</v>
+        <v>0.7115889569952663</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5325,63 +5325,63 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>9.779947916666666</v>
+        <v>14.3507287695129</v>
       </c>
       <c r="C97" t="n">
-        <v>3.127290827004528</v>
+        <v>3.788235574711913</v>
       </c>
       <c r="D97" t="n">
-        <v>1.450520833333333</v>
+        <v>2.471510011728463</v>
       </c>
       <c r="E97" t="n">
-        <v>0.6820132247528847</v>
+        <v>0.5527485778744226</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>12.54717146178756</v>
+        <v>6.666466564207651</v>
       </c>
       <c r="C98" t="n">
-        <v>3.542198676216167</v>
+        <v>2.58195014750627</v>
       </c>
       <c r="D98" t="n">
-        <v>2.276144045464891</v>
+        <v>1.15957650273224</v>
       </c>
       <c r="E98" t="n">
-        <v>0.5920392802085261</v>
+        <v>0.792234478173077</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5393,29 +5393,29 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>6.352518098958334</v>
+        <v>8.287833824785851</v>
       </c>
       <c r="C99" t="n">
-        <v>2.520420222692703</v>
+        <v>2.878859813326424</v>
       </c>
       <c r="D99" t="n">
-        <v>1.145703125</v>
+        <v>1.329805644994232</v>
       </c>
       <c r="E99" t="n">
-        <v>0.7934532205898306</v>
+        <v>0.7417033292169348</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5427,29 +5427,29 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>8.119305660535959</v>
+        <v>7.38855596434879</v>
       </c>
       <c r="C100" t="n">
-        <v>2.849439534458655</v>
+        <v>2.718189832287067</v>
       </c>
       <c r="D100" t="n">
-        <v>1.321942730189919</v>
+        <v>1.276165604423903</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7360076100364905</v>
+        <v>0.7697300105392781</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5461,29 +5461,29 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>6.23376911523042</v>
+        <v>6.953551912568306</v>
       </c>
       <c r="C101" t="n">
-        <v>2.496751712772101</v>
+        <v>2.636958837860065</v>
       </c>
       <c r="D101" t="n">
-        <v>1.19337943048716</v>
+        <v>1.207650273224044</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7973142438510242</v>
+        <v>0.7832872440368919</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5495,97 +5495,97 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>6.809075662247731</v>
+        <v>14.55867869860561</v>
       </c>
       <c r="C102" t="n">
-        <v>2.609420560631753</v>
+        <v>3.815583664212542</v>
       </c>
       <c r="D102" t="n">
-        <v>1.245515471349167</v>
+        <v>2.514117722757477</v>
       </c>
       <c r="E102" t="n">
-        <v>0.778608635679755</v>
+        <v>0.5462676595174947</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>7.67578125</v>
+        <v>4.891569721311476</v>
       </c>
       <c r="C103" t="n">
-        <v>2.770520032412688</v>
+        <v>2.211689336527957</v>
       </c>
       <c r="D103" t="n">
-        <v>1.3046875</v>
+        <v>1.115863387978142</v>
       </c>
       <c r="E103" t="n">
-        <v>0.7504284329541014</v>
+        <v>0.8475504938166822</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>13.01516505653451</v>
+        <v>7.111226623936073</v>
       </c>
       <c r="C104" t="n">
-        <v>3.607653677466077</v>
+        <v>2.666688325233392</v>
       </c>
       <c r="D104" t="n">
-        <v>2.342527503348371</v>
+        <v>1.337683242048498</v>
       </c>
       <c r="E104" t="n">
-        <v>0.5768228623607092</v>
+        <v>0.7783731912368494</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5597,29 +5597,29 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>4.739283341471354</v>
+        <v>4.124780603089613</v>
       </c>
       <c r="C105" t="n">
-        <v>2.176989513404085</v>
+        <v>2.030955588655157</v>
       </c>
       <c r="D105" t="n">
-        <v>1.096829427083333</v>
+        <v>1.081322766388076</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8459061909554121</v>
+        <v>0.8714480623028008</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5631,29 +5631,29 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>6.848978718940498</v>
+        <v>7.853825136612022</v>
       </c>
       <c r="C106" t="n">
-        <v>2.617055352670344</v>
+        <v>2.802467686988027</v>
       </c>
       <c r="D106" t="n">
-        <v>1.314169027962364</v>
+        <v>1.37431693989071</v>
       </c>
       <c r="E106" t="n">
-        <v>0.7773112213756754</v>
+        <v>0.7552295414475622</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5665,24 +5665,24 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>4.422881951598273</v>
+        <v>13.73486255045933</v>
       </c>
       <c r="C107" t="n">
-        <v>2.103064894766272</v>
+        <v>3.706057548185042</v>
       </c>
       <c r="D107" t="n">
-        <v>1.131402354048381</v>
+        <v>2.359791975084253</v>
       </c>
       <c r="E107" t="n">
-        <v>0.8561937158488717</v>
+        <v>0.5719425189442293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -5692,31 +5692,31 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>6.521002275299026</v>
+        <v>7.684071537303446</v>
       </c>
       <c r="C108" t="n">
-        <v>2.553625320069298</v>
+        <v>2.77201578951193</v>
       </c>
       <c r="D108" t="n">
-        <v>1.224281655746656</v>
+        <v>1.221291959406714</v>
       </c>
       <c r="E108" t="n">
-        <v>0.7879750994003056</v>
+        <v>0.7605200420152398</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -5726,31 +5726,31 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5.40625</v>
+        <v>7.681398184523484</v>
       </c>
       <c r="C109" t="n">
-        <v>2.325134404717284</v>
+        <v>2.771533543820728</v>
       </c>
       <c r="D109" t="n">
-        <v>1.234375</v>
+        <v>1.286100831315334</v>
       </c>
       <c r="E109" t="n">
-        <v>0.8242203314038048</v>
+        <v>0.7606033590963361</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5760,27 +5760,27 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>14.87043321204156</v>
+        <v>10.24551051609158</v>
       </c>
       <c r="C110" t="n">
-        <v>3.856220067895705</v>
+        <v>3.200860902334181</v>
       </c>
       <c r="D110" t="n">
-        <v>2.494184858708053</v>
+        <v>1.373448728780005</v>
       </c>
       <c r="E110" t="n">
-        <v>0.5365515920112571</v>
+        <v>0.6806908400039355</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5801,20 +5801,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>8.008666530054645</v>
+        <v>9.209016393442623</v>
       </c>
       <c r="C111" t="n">
-        <v>2.829958750592426</v>
+        <v>3.034636122081628</v>
       </c>
       <c r="D111" t="n">
-        <v>1.263032786885246</v>
+        <v>1.494535519125683</v>
       </c>
       <c r="E111" t="n">
-        <v>0.7504037911645353</v>
+        <v>0.7129939709337305</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5835,20 +5835,20 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>8.252315787393226</v>
+        <v>12.71181801929431</v>
       </c>
       <c r="C112" t="n">
-        <v>2.872684421824511</v>
+        <v>3.565363658772315</v>
       </c>
       <c r="D112" t="n">
-        <v>1.322194113271492</v>
+        <v>2.307818342830007</v>
       </c>
       <c r="E112" t="n">
-        <v>0.7428102759783222</v>
+        <v>0.6038264830836254</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -5857,32 +5857,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>10.67125457121626</v>
+        <v>6.752357957650273</v>
       </c>
       <c r="C113" t="n">
-        <v>3.266688624772226</v>
+        <v>2.598529960891402</v>
       </c>
       <c r="D113" t="n">
-        <v>1.448192620252738</v>
+        <v>1.163811475409836</v>
       </c>
       <c r="E113" t="n">
-        <v>0.6674222013741996</v>
+        <v>0.7895576072989532</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5891,32 +5891,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>8.829030975843679</v>
+        <v>8.288956617139855</v>
       </c>
       <c r="C114" t="n">
-        <v>2.971368535850725</v>
+        <v>2.879054813153069</v>
       </c>
       <c r="D114" t="n">
-        <v>1.337508594503017</v>
+        <v>1.330596416089928</v>
       </c>
       <c r="E114" t="n">
-        <v>0.7248365066779189</v>
+        <v>0.7416683365357166</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5925,32 +5925,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>9.972677595628415</v>
+        <v>7.38855596434879</v>
       </c>
       <c r="C115" t="n">
-        <v>3.157954653827128</v>
+        <v>2.718189832287067</v>
       </c>
       <c r="D115" t="n">
-        <v>1.546448087431694</v>
+        <v>1.276165604423903</v>
       </c>
       <c r="E115" t="n">
-        <v>0.6891938863397467</v>
+        <v>0.7697300105392781</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -5959,32 +5959,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>14.40977076800421</v>
+        <v>6.8224043715847</v>
       </c>
       <c r="C116" t="n">
-        <v>3.796020385614942</v>
+        <v>2.611973271606105</v>
       </c>
       <c r="D116" t="n">
-        <v>2.474495228081621</v>
+        <v>1.19672131147541</v>
       </c>
       <c r="E116" t="n">
-        <v>0.5509084888995355</v>
+        <v>0.787374557312424</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6005,20 +6005,20 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>6.796429892418032</v>
+        <v>13.11534861965564</v>
       </c>
       <c r="C117" t="n">
-        <v>2.606996335328846</v>
+        <v>3.621511924549695</v>
       </c>
       <c r="D117" t="n">
-        <v>1.190908469945355</v>
+        <v>2.372963587099203</v>
       </c>
       <c r="E117" t="n">
-        <v>0.7881840717930365</v>
+        <v>0.5912501437365807</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -6027,32 +6027,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>8.206125857111934</v>
+        <v>4.908395950819672</v>
       </c>
       <c r="C118" t="n">
-        <v>2.864633634011849</v>
+        <v>2.215490002419255</v>
       </c>
       <c r="D118" t="n">
-        <v>1.321637536129103</v>
+        <v>1.120125683060109</v>
       </c>
       <c r="E118" t="n">
-        <v>0.7442498204319862</v>
+        <v>0.8470260915234316</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -6061,32 +6061,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>7.347379490456304</v>
+        <v>7.111226623936073</v>
       </c>
       <c r="C119" t="n">
-        <v>2.710605004506615</v>
+        <v>2.666688325233392</v>
       </c>
       <c r="D119" t="n">
-        <v>1.275300903876867</v>
+        <v>1.337683242048498</v>
       </c>
       <c r="E119" t="n">
-        <v>0.7710133067956784</v>
+        <v>0.7783731912368494</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -6095,32 +6095,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>7.951775334235136</v>
+        <v>4.124780603089613</v>
       </c>
       <c r="C120" t="n">
-        <v>2.819889241483633</v>
+        <v>2.030955588655157</v>
       </c>
       <c r="D120" t="n">
-        <v>1.304334907341904</v>
+        <v>1.081322766388076</v>
       </c>
       <c r="E120" t="n">
-        <v>0.7521768487315318</v>
+        <v>0.8714480623028008</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -6129,12 +6129,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
     </row>
@@ -6145,16 +6145,16 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>6.620218579234972</v>
+        <v>7.896174863387978</v>
       </c>
       <c r="C121" t="n">
-        <v>2.572978542319188</v>
+        <v>2.810013320855967</v>
       </c>
       <c r="D121" t="n">
-        <v>1.213114754098361</v>
+        <v>1.39344262295082</v>
       </c>
       <c r="E121" t="n">
-        <v>0.7936758319455359</v>
+        <v>0.7539096798690049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -6163,826 +6163,10 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
-        <is>
-          <t>iqr</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>14.49438625267525</v>
-      </c>
-      <c r="C122" t="n">
-        <v>3.80714936043692</v>
-      </c>
-      <c r="D122" t="n">
-        <v>2.51308617188589</v>
-      </c>
-      <c r="E122" t="n">
-        <v>0.5482713826967225</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>robust</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>zscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>5.027872897540983</v>
-      </c>
-      <c r="C123" t="n">
-        <v>2.242291885000921</v>
-      </c>
-      <c r="D123" t="n">
-        <v>1.128363387978142</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0.8433025012312194</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>robust</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>zscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>7.032789844724642</v>
-      </c>
-      <c r="C124" t="n">
-        <v>2.651940769460102</v>
-      </c>
-      <c r="D124" t="n">
-        <v>1.306476838809563</v>
-      </c>
-      <c r="E124" t="n">
-        <v>0.780817733365176</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>robust</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>zscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>4.9314393467451</v>
-      </c>
-      <c r="C125" t="n">
-        <v>2.22068443204907</v>
-      </c>
-      <c r="D125" t="n">
-        <v>1.164602598191787</v>
-      </c>
-      <c r="E125" t="n">
-        <v>0.8463079264905765</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>robust</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>zscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>CatBoost</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>6.544108413780192</v>
-      </c>
-      <c r="C126" t="n">
-        <v>2.558145502855573</v>
-      </c>
-      <c r="D126" t="n">
-        <v>1.238762069384752</v>
-      </c>
-      <c r="E126" t="n">
-        <v>0.7960478633792413</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>robust</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>zscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>5.016393442622951</v>
-      </c>
-      <c r="C127" t="n">
-        <v>2.2397306629644</v>
-      </c>
-      <c r="D127" t="n">
-        <v>1.224043715846995</v>
-      </c>
-      <c r="E127" t="n">
-        <v>0.8436602672108973</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>robust</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>zscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>13.72845943825635</v>
-      </c>
-      <c r="C128" t="n">
-        <v>3.70519357635419</v>
-      </c>
-      <c r="D128" t="n">
-        <v>2.36226253209677</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0.572142076826258</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>isolation_forest</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>7.991676229508196</v>
-      </c>
-      <c r="C129" t="n">
-        <v>2.826955293156967</v>
-      </c>
-      <c r="D129" t="n">
-        <v>1.25792349726776</v>
-      </c>
-      <c r="E129" t="n">
-        <v>0.7509333068569984</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>isolation_forest</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>8.252315787393226</v>
-      </c>
-      <c r="C130" t="n">
-        <v>2.872684421824511</v>
-      </c>
-      <c r="D130" t="n">
-        <v>1.322194113271492</v>
-      </c>
-      <c r="E130" t="n">
-        <v>0.7428102759783222</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>isolation_forest</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>10.67125457121626</v>
-      </c>
-      <c r="C131" t="n">
-        <v>3.266688624772226</v>
-      </c>
-      <c r="D131" t="n">
-        <v>1.448192620252738</v>
-      </c>
-      <c r="E131" t="n">
-        <v>0.6674222013741996</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>isolation_forest</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>CatBoost</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>8.829030975843679</v>
-      </c>
-      <c r="C132" t="n">
-        <v>2.971368535850725</v>
-      </c>
-      <c r="D132" t="n">
-        <v>1.337508594503017</v>
-      </c>
-      <c r="E132" t="n">
-        <v>0.7248365066779189</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>isolation_forest</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>9.984972677595628</v>
-      </c>
-      <c r="C133" t="n">
-        <v>3.159900738566898</v>
-      </c>
-      <c r="D133" t="n">
-        <v>1.549180327868853</v>
-      </c>
-      <c r="E133" t="n">
-        <v>0.6888107007201656</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>isolation_forest</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>12.79271156190146</v>
-      </c>
-      <c r="C134" t="n">
-        <v>3.57669002876982</v>
-      </c>
-      <c r="D134" t="n">
-        <v>2.311776993139845</v>
-      </c>
-      <c r="E134" t="n">
-        <v>0.6013053740477775</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>iqr</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>6.843666982581968</v>
-      </c>
-      <c r="C135" t="n">
-        <v>2.616040325106241</v>
-      </c>
-      <c r="D135" t="n">
-        <v>1.19667349726776</v>
-      </c>
-      <c r="E135" t="n">
-        <v>0.7867118918018867</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>iqr</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>8.206825745910425</v>
-      </c>
-      <c r="C136" t="n">
-        <v>2.864755791670631</v>
-      </c>
-      <c r="D136" t="n">
-        <v>1.32209300281908</v>
-      </c>
-      <c r="E136" t="n">
-        <v>0.744228007863058</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>iqr</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>7.347379490456304</v>
-      </c>
-      <c r="C137" t="n">
-        <v>2.710605004506615</v>
-      </c>
-      <c r="D137" t="n">
-        <v>1.275300903876867</v>
-      </c>
-      <c r="E137" t="n">
-        <v>0.7710133067956784</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>iqr</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>CatBoost</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>7.98493602062988</v>
-      </c>
-      <c r="C138" t="n">
-        <v>2.825762909486548</v>
-      </c>
-      <c r="D138" t="n">
-        <v>1.306673919509726</v>
-      </c>
-      <c r="E138" t="n">
-        <v>0.7511433706143635</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>iqr</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>6.741803278688525</v>
-      </c>
-      <c r="C139" t="n">
-        <v>2.596498272421633</v>
-      </c>
-      <c r="D139" t="n">
-        <v>1.237704918032787</v>
-      </c>
-      <c r="E139" t="n">
-        <v>0.789886551929678</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>iqr</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>13.0302233856245</v>
-      </c>
-      <c r="C140" t="n">
-        <v>3.609740071753712</v>
-      </c>
-      <c r="D140" t="n">
-        <v>2.370166356375336</v>
-      </c>
-      <c r="E140" t="n">
-        <v>0.59390313666751</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>zscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>5.006354318306011</v>
-      </c>
-      <c r="C141" t="n">
-        <v>2.237488395122087</v>
-      </c>
-      <c r="D141" t="n">
-        <v>1.119674863387978</v>
-      </c>
-      <c r="E141" t="n">
-        <v>0.8439731441873742</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>zscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>6.99879978176956</v>
-      </c>
-      <c r="C142" t="n">
-        <v>2.645524481415653</v>
-      </c>
-      <c r="D142" t="n">
-        <v>1.307005347339744</v>
-      </c>
-      <c r="E142" t="n">
-        <v>0.7818770596362636</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>zscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>4.9314393467451</v>
-      </c>
-      <c r="C143" t="n">
-        <v>2.22068443204907</v>
-      </c>
-      <c r="D143" t="n">
-        <v>1.164602598191787</v>
-      </c>
-      <c r="E143" t="n">
-        <v>0.8463079264905765</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>zscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>CatBoost</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>6.557625641540588</v>
-      </c>
-      <c r="C144" t="n">
-        <v>2.560786137407923</v>
-      </c>
-      <c r="D144" t="n">
-        <v>1.239776933793123</v>
-      </c>
-      <c r="E144" t="n">
-        <v>0.7956265886526311</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>zscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>4.881147540983607</v>
-      </c>
-      <c r="C145" t="n">
-        <v>2.209331921867696</v>
-      </c>
-      <c r="D145" t="n">
-        <v>1.199453551912568</v>
-      </c>
-      <c r="E145" t="n">
-        <v>0.8478753090262897</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
         <is>
           <t>zscore</t>
         </is>
@@ -7056,22 +6240,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7849271941101076</v>
+        <v>0.7684014337337335</v>
       </c>
       <c r="E2" t="n">
-        <v>6.900931669161561</v>
+        <v>7.431185332177795</v>
       </c>
       <c r="F2" t="n">
-        <v>1.400113275166756</v>
+        <v>1.461107580309341</v>
       </c>
       <c r="G2" t="n">
-        <v>2.580592573269357</v>
+        <v>2.668931832342693</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7085,27 +6269,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7780715702241299</v>
+        <v>0.7625833435452005</v>
       </c>
       <c r="E3" t="n">
-        <v>6.825593557307276</v>
+        <v>7.301946858867508</v>
       </c>
       <c r="F3" t="n">
-        <v>1.390597494698184</v>
+        <v>1.453374252935564</v>
       </c>
       <c r="G3" t="n">
-        <v>2.563920527182227</v>
+        <v>2.647721551907941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7114,27 +6298,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7764012790623055</v>
+        <v>0.7608995577195691</v>
       </c>
       <c r="E4" t="n">
-        <v>7.174498366348186</v>
+        <v>7.353733093262636</v>
       </c>
       <c r="F4" t="n">
-        <v>1.429222463682855</v>
+        <v>1.471758053345773</v>
       </c>
       <c r="G4" t="n">
-        <v>2.619990435461164</v>
+        <v>2.658583743193927</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7143,22 +6327,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7763307361005394</v>
+        <v>0.7597737896642778</v>
       </c>
       <c r="E5" t="n">
-        <v>6.879134359584474</v>
+        <v>7.70801615671096</v>
       </c>
       <c r="F5" t="n">
-        <v>1.393583149101872</v>
+        <v>1.484660811812581</v>
       </c>
       <c r="G5" t="n">
-        <v>2.572550339874818</v>
+        <v>2.705476920323415</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7172,22 +6356,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7739393101809262</v>
+        <v>0.7588234559079498</v>
       </c>
       <c r="E6" t="n">
-        <v>6.952684654002248</v>
+        <v>7.417585332311118</v>
       </c>
       <c r="F6" t="n">
-        <v>1.415710792057568</v>
+        <v>1.474271432047075</v>
       </c>
       <c r="G6" t="n">
-        <v>2.591069203314092</v>
+        <v>2.670403692621864</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7201,22 +6385,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7706212667568185</v>
+        <v>0.7541928888739091</v>
       </c>
       <c r="E7" t="n">
-        <v>7.054733840946562</v>
+        <v>7.56000227522441</v>
       </c>
       <c r="F7" t="n">
-        <v>1.413550598186365</v>
+        <v>1.474694267909985</v>
       </c>
       <c r="G7" t="n">
-        <v>2.595696349049179</v>
+        <v>2.682392262736036</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7230,22 +6414,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7692721169045366</v>
+        <v>0.752499335738111</v>
       </c>
       <c r="E8" t="n">
-        <v>7.096228067481114</v>
+        <v>7.612088911372538</v>
       </c>
       <c r="F8" t="n">
-        <v>1.413162110098043</v>
+        <v>1.493318797654427</v>
       </c>
       <c r="G8" t="n">
-        <v>2.60192706214428</v>
+        <v>2.693331512129927</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7259,22 +6443,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7674017976689097</v>
+        <v>0.7503464079802475</v>
       </c>
       <c r="E9" t="n">
-        <v>7.153751292142754</v>
+        <v>7.678303996336015</v>
       </c>
       <c r="F9" t="n">
-        <v>1.43326579582687</v>
+        <v>1.496554686975512</v>
       </c>
       <c r="G9" t="n">
-        <v>2.617140378051686</v>
+        <v>2.7055008119037</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7288,22 +6472,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7432601860868605</v>
+        <v>0.7384313989539995</v>
       </c>
       <c r="E10" t="n">
-        <v>7.896246648163004</v>
+        <v>8.392818586003585</v>
       </c>
       <c r="F10" t="n">
-        <v>1.409498141062684</v>
+        <v>1.455022630045817</v>
       </c>
       <c r="G10" t="n">
-        <v>2.788599287220091</v>
+        <v>2.874622307341991</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7317,22 +6501,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7413085705532879</v>
+        <v>0.7319436368633315</v>
       </c>
       <c r="E11" t="n">
-        <v>7.956270208126668</v>
+        <v>8.244296537711081</v>
       </c>
       <c r="F11" t="n">
-        <v>1.414562050415189</v>
+        <v>1.462879937893037</v>
       </c>
       <c r="G11" t="n">
-        <v>2.798125123197345</v>
+        <v>2.8513450755519</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7346,16 +6530,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7407147505087405</v>
+        <v>0.7318582799590385</v>
       </c>
       <c r="E12" t="n">
-        <v>8.31955384669476</v>
+        <v>8.246921760340751</v>
       </c>
       <c r="F12" t="n">
-        <v>1.441703872441011</v>
+        <v>1.459459520639837</v>
       </c>
       <c r="G12" t="n">
-        <v>2.865058721993581</v>
+        <v>2.851317214600118</v>
       </c>
     </row>
     <row r="13">
@@ -7375,16 +6559,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7380617308509502</v>
+        <v>0.7314217202433815</v>
       </c>
       <c r="E13" t="n">
-        <v>8.05612946534877</v>
+        <v>8.260348517721848</v>
       </c>
       <c r="F13" t="n">
-        <v>1.417949268469599</v>
+        <v>1.464084904706317</v>
       </c>
       <c r="G13" t="n">
-        <v>2.817773466350075</v>
+        <v>2.854148826320528</v>
       </c>
     </row>
     <row r="14">
@@ -7404,16 +6588,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.733368061432884</v>
+        <v>0.7279407279681209</v>
       </c>
       <c r="E14" t="n">
-        <v>8.555283320243431</v>
+        <v>8.7294274070847</v>
       </c>
       <c r="F14" t="n">
-        <v>1.463298633245535</v>
+        <v>1.488941607420576</v>
       </c>
       <c r="G14" t="n">
-        <v>2.895187190544179</v>
+        <v>2.920838841138348</v>
       </c>
     </row>
     <row r="15">
@@ -7433,16 +6617,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.7324912709541652</v>
+        <v>0.7214742162190524</v>
       </c>
       <c r="E15" t="n">
-        <v>8.22745359547997</v>
+        <v>8.566292282783042</v>
       </c>
       <c r="F15" t="n">
-        <v>1.440764714983661</v>
+        <v>1.492709522129138</v>
       </c>
       <c r="G15" t="n">
-        <v>2.835170217281133</v>
+        <v>2.895841381991699</v>
       </c>
     </row>
     <row r="16">
@@ -7462,16 +6646,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.7320762222060214</v>
+        <v>0.721360312483511</v>
       </c>
       <c r="E16" t="n">
-        <v>8.240218765152733</v>
+        <v>8.569795486965806</v>
       </c>
       <c r="F16" t="n">
-        <v>1.44093578175406</v>
+        <v>1.495804948216018</v>
       </c>
       <c r="G16" t="n">
-        <v>2.838507130599666</v>
+        <v>2.896906652148339</v>
       </c>
     </row>
     <row r="17">
@@ -7491,22 +6675,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7293008737369711</v>
+        <v>0.7210339436317338</v>
       </c>
       <c r="E17" t="n">
-        <v>8.325576917097322</v>
+        <v>8.579833232622121</v>
       </c>
       <c r="F17" t="n">
-        <v>1.445064357889944</v>
+        <v>1.496604910981668</v>
       </c>
       <c r="G17" t="n">
-        <v>2.854199239187755</v>
+        <v>2.898606411703435</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7520,22 +6704,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.7131307929136529</v>
+        <v>0.6984895474710907</v>
       </c>
       <c r="E18" t="n">
-        <v>8.822901210340165</v>
+        <v>9.273204899077268</v>
       </c>
       <c r="F18" t="n">
-        <v>1.459813297914285</v>
+        <v>1.499214670416661</v>
       </c>
       <c r="G18" t="n">
-        <v>2.950977042970826</v>
+        <v>3.023727105358379</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7549,27 +6733,27 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.7073091198115176</v>
+        <v>0.6973501461986943</v>
       </c>
       <c r="E19" t="n">
-        <v>9.001951611673668</v>
+        <v>9.710971836364093</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4616654584226</v>
+        <v>1.547033802742398</v>
       </c>
       <c r="G19" t="n">
-        <v>2.982283718140724</v>
+        <v>3.097020781186702</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7578,27 +6762,27 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.7064190493997634</v>
+        <v>0.6968320813903595</v>
       </c>
       <c r="E20" t="n">
-        <v>9.029326467946719</v>
+        <v>9.324181647813425</v>
       </c>
       <c r="F20" t="n">
-        <v>1.478296044076899</v>
+        <v>1.502992490705599</v>
       </c>
       <c r="G20" t="n">
-        <v>2.978060400418576</v>
+        <v>3.032739646614405</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7607,27 +6791,27 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.7033062237519566</v>
+        <v>0.6937095556455837</v>
       </c>
       <c r="E21" t="n">
-        <v>9.12506401138876</v>
+        <v>9.420217525810633</v>
       </c>
       <c r="F21" t="n">
-        <v>1.475982283772601</v>
+        <v>1.501678063253718</v>
       </c>
       <c r="G21" t="n">
-        <v>2.997625085471234</v>
+        <v>3.048321474812925</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -7636,16 +6820,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7018727905804635</v>
+        <v>0.6903983233378498</v>
       </c>
       <c r="E22" t="n">
-        <v>9.169150441550304</v>
+        <v>9.522057231202329</v>
       </c>
       <c r="F22" t="n">
-        <v>1.468798166636697</v>
+        <v>1.528527446624669</v>
       </c>
       <c r="G22" t="n">
-        <v>3.009160809895652</v>
+        <v>3.057944844552671</v>
       </c>
     </row>
     <row r="23">
@@ -7665,16 +6849,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.6978866920398582</v>
+        <v>0.6896906156082456</v>
       </c>
       <c r="E23" t="n">
-        <v>9.291746219590211</v>
+        <v>9.543823371414835</v>
       </c>
       <c r="F23" t="n">
-        <v>1.479639060105246</v>
+        <v>1.526324702240442</v>
       </c>
       <c r="G23" t="n">
-        <v>3.024820793965154</v>
+        <v>3.062139175540382</v>
       </c>
     </row>
     <row r="24">
@@ -7685,7 +6869,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7694,22 +6878,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6911591780723104</v>
+        <v>0.6893743936746362</v>
       </c>
       <c r="E24" t="n">
-        <v>9.909618279968889</v>
+        <v>9.966885748636415</v>
       </c>
       <c r="F24" t="n">
-        <v>1.546210280876772</v>
+        <v>1.57589644650905</v>
       </c>
       <c r="G24" t="n">
-        <v>3.133798531754253</v>
+        <v>3.13131259038262</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7723,16 +6907,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6852030422576633</v>
+        <v>0.688369542223954</v>
       </c>
       <c r="E25" t="n">
-        <v>10.1007297786963</v>
+        <v>9.584454082809753</v>
       </c>
       <c r="F25" t="n">
-        <v>1.568593510175373</v>
+        <v>1.523528669025294</v>
       </c>
       <c r="G25" t="n">
-        <v>3.159145842460453</v>
+        <v>3.068408159475235</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/experiment_results.xlsx
+++ b/outputs/results/experiment_results.xlsx
@@ -485,16 +485,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7279407279681209</v>
+        <v>0.7210339436317338</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7294274070847</v>
+        <v>8.579833232622121</v>
       </c>
       <c r="F2" t="n">
-        <v>1.488941607420576</v>
+        <v>1.496604910981668</v>
       </c>
       <c r="G2" t="n">
-        <v>2.920838841138348</v>
+        <v>2.898606411703435</v>
       </c>
     </row>
     <row r="3">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6893743936746362</v>
+        <v>0.7510702611565285</v>
       </c>
       <c r="E3" t="n">
-        <v>9.966885748636415</v>
+        <v>7.656041289473947</v>
       </c>
       <c r="F3" t="n">
-        <v>1.57589644650905</v>
+        <v>1.464502076096448</v>
       </c>
       <c r="G3" t="n">
-        <v>3.13131259038262</v>
+        <v>2.718897244795108</v>
       </c>
     </row>
     <row r="4">
@@ -543,16 +543,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7597737896642778</v>
+        <v>0.7541928888739091</v>
       </c>
       <c r="E4" t="n">
-        <v>7.70801615671096</v>
+        <v>7.56000227522441</v>
       </c>
       <c r="F4" t="n">
-        <v>1.484660811812581</v>
+        <v>1.474694267909985</v>
       </c>
       <c r="G4" t="n">
-        <v>2.705476920323415</v>
+        <v>2.682392262736036</v>
       </c>
     </row>
     <row r="5">
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7384313989539995</v>
+        <v>0.7314217202433815</v>
       </c>
       <c r="E5" t="n">
-        <v>8.392818586003585</v>
+        <v>8.260348517721848</v>
       </c>
       <c r="F5" t="n">
-        <v>1.455022630045817</v>
+        <v>1.464084904706317</v>
       </c>
       <c r="G5" t="n">
-        <v>2.874622307341991</v>
+        <v>2.854148826320528</v>
       </c>
     </row>
     <row r="6">
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6973501461986943</v>
+        <v>0.7591824763890805</v>
       </c>
       <c r="E6" t="n">
-        <v>9.710971836364093</v>
+        <v>7.406543358619767</v>
       </c>
       <c r="F6" t="n">
-        <v>1.547033802742398</v>
+        <v>1.440416400603951</v>
       </c>
       <c r="G6" t="n">
-        <v>3.097020781186702</v>
+        <v>2.684299947141111</v>
       </c>
     </row>
     <row r="7">
@@ -630,16 +630,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7684014337337335</v>
+        <v>0.7625833435452005</v>
       </c>
       <c r="E7" t="n">
-        <v>7.431185332177795</v>
+        <v>7.301946858867508</v>
       </c>
       <c r="F7" t="n">
-        <v>1.461107580309341</v>
+        <v>1.453374252935564</v>
       </c>
       <c r="G7" t="n">
-        <v>2.668931832342693</v>
+        <v>2.647721551907941</v>
       </c>
     </row>
     <row r="8">
@@ -688,16 +688,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.688369542223954</v>
+        <v>0.7404458018019563</v>
       </c>
       <c r="E9" t="n">
-        <v>9.584454082809753</v>
+        <v>7.982805379111669</v>
       </c>
       <c r="F9" t="n">
-        <v>1.523528669025294</v>
+        <v>1.474224465462455</v>
       </c>
       <c r="G9" t="n">
-        <v>3.068408159475235</v>
+        <v>2.769164926398047</v>
       </c>
     </row>
     <row r="10">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.6937095556455837</v>
+        <v>0.7484151104614505</v>
       </c>
       <c r="E12" t="n">
-        <v>9.420217525810633</v>
+        <v>7.737702658845629</v>
       </c>
       <c r="F12" t="n">
-        <v>1.501678063253718</v>
+        <v>1.450233806848774</v>
       </c>
       <c r="G12" t="n">
-        <v>3.048321474812925</v>
+        <v>2.73523744632631</v>
       </c>
     </row>
     <row r="13">
@@ -862,16 +862,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.6903983233378498</v>
+        <v>0.74168487282217</v>
       </c>
       <c r="E15" t="n">
-        <v>9.522057231202329</v>
+        <v>7.944696718670292</v>
       </c>
       <c r="F15" t="n">
-        <v>1.528527446624669</v>
+        <v>1.451467819982617</v>
       </c>
       <c r="G15" t="n">
-        <v>3.057944844552671</v>
+        <v>2.756385478425933</v>
       </c>
     </row>
     <row r="16">
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.6984895474710907</v>
+        <v>0.7498136265114418</v>
       </c>
       <c r="E18" t="n">
-        <v>9.273204899077268</v>
+        <v>7.694690133815593</v>
       </c>
       <c r="F18" t="n">
-        <v>1.499214670416661</v>
+        <v>1.429013677817497</v>
       </c>
       <c r="G18" t="n">
-        <v>3.023727105358379</v>
+        <v>2.721600451197589</v>
       </c>
     </row>
     <row r="19">
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6896906156082456</v>
+        <v>0.7520867366290632</v>
       </c>
       <c r="E21" t="n">
-        <v>9.543823371414835</v>
+        <v>7.624778740356194</v>
       </c>
       <c r="F21" t="n">
-        <v>1.526324702240442</v>
+        <v>1.455935263582135</v>
       </c>
       <c r="G21" t="n">
-        <v>3.062139175540382</v>
+        <v>2.703583174802635</v>
       </c>
     </row>
     <row r="22">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6968320813903595</v>
+        <v>0.759473054982568</v>
       </c>
       <c r="E24" t="n">
-        <v>9.324181647813425</v>
+        <v>7.397606372143528</v>
       </c>
       <c r="F24" t="n">
-        <v>1.502992490705599</v>
+        <v>1.433710724260695</v>
       </c>
       <c r="G24" t="n">
-        <v>3.032739646614405</v>
+        <v>2.673831396952504</v>
       </c>
     </row>
     <row r="25">
@@ -1242,16 +1242,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.792234478173077</v>
+        <v>0.7866208433183421</v>
       </c>
       <c r="F2" t="n">
-        <v>6.666466564207651</v>
+        <v>6.562653548177084</v>
       </c>
       <c r="G2" t="n">
-        <v>1.15957650273224</v>
+        <v>1.1729296875</v>
       </c>
       <c r="H2" t="n">
-        <v>2.58195014750627</v>
+        <v>2.56176766085004</v>
       </c>
     </row>
     <row r="3">
@@ -1272,20 +1272,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.7607017181311997</v>
+        <v>0.8336727685103763</v>
       </c>
       <c r="F3" t="n">
-        <v>7.678242188228045</v>
+        <v>5.115532430013021</v>
       </c>
       <c r="G3" t="n">
-        <v>1.28388548304942</v>
+        <v>1.10529296875</v>
       </c>
       <c r="H3" t="n">
-        <v>2.770964126117125</v>
+        <v>2.261754281528615</v>
       </c>
     </row>
     <row r="4">
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8714480623028008</v>
+        <v>0.8664022178760558</v>
       </c>
       <c r="F4" t="n">
-        <v>4.124780603089613</v>
+        <v>4.108910975744135</v>
       </c>
       <c r="G4" t="n">
-        <v>1.081322766388076</v>
+        <v>1.081957858672392</v>
       </c>
       <c r="H4" t="n">
-        <v>2.030955588655157</v>
+        <v>2.027044887451715</v>
       </c>
     </row>
     <row r="5">
@@ -1344,16 +1344,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7895576072989532</v>
+        <v>0.7838902467226974</v>
       </c>
       <c r="F5" t="n">
-        <v>6.752357957650273</v>
+        <v>6.646635319010417</v>
       </c>
       <c r="G5" t="n">
-        <v>1.163811475409836</v>
+        <v>1.177513020833333</v>
       </c>
       <c r="H5" t="n">
-        <v>2.598529960891402</v>
+        <v>2.578106925441693</v>
       </c>
     </row>
     <row r="6">
@@ -1374,20 +1374,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7606033590963361</v>
+        <v>0.8332430227830193</v>
       </c>
       <c r="F6" t="n">
-        <v>7.681398184523484</v>
+        <v>5.12874961751302</v>
       </c>
       <c r="G6" t="n">
-        <v>1.286100831315334</v>
+        <v>1.104407552083333</v>
       </c>
       <c r="H6" t="n">
-        <v>2.771533543820728</v>
+        <v>2.264674285082299</v>
       </c>
     </row>
     <row r="7">
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8714480623028008</v>
+        <v>0.8664022178760558</v>
       </c>
       <c r="F7" t="n">
-        <v>4.124780603089613</v>
+        <v>4.108910975744135</v>
       </c>
       <c r="G7" t="n">
-        <v>1.081322766388076</v>
+        <v>1.081957858672392</v>
       </c>
       <c r="H7" t="n">
-        <v>2.030955588655157</v>
+        <v>2.027044887451715</v>
       </c>
     </row>
     <row r="8">
@@ -1476,20 +1476,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7633867899815057</v>
+        <v>0.8352912414456735</v>
       </c>
       <c r="F9" t="n">
-        <v>7.277236195052044</v>
+        <v>5.065754947916666</v>
       </c>
       <c r="G9" t="n">
-        <v>1.226473334554635</v>
+        <v>1.091197916666667</v>
       </c>
       <c r="H9" t="n">
-        <v>2.697635296894679</v>
+        <v>2.250723205531206</v>
       </c>
     </row>
     <row r="10">
@@ -1578,20 +1578,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.7633681944944954</v>
+        <v>0.8344501638320561</v>
       </c>
       <c r="F12" t="n">
-        <v>7.277808114731106</v>
+        <v>5.091622989908855</v>
       </c>
       <c r="G12" t="n">
-        <v>1.227003489121217</v>
+        <v>1.09474609375</v>
       </c>
       <c r="H12" t="n">
-        <v>2.697741298703622</v>
+        <v>2.256462494682518</v>
       </c>
     </row>
     <row r="13">
@@ -1680,20 +1680,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7665019904937718</v>
+        <v>0.8370011472178656</v>
       </c>
       <c r="F15" t="n">
-        <v>7.181425610677084</v>
+        <v>5.013165372826788</v>
       </c>
       <c r="G15" t="n">
-        <v>1.184356770833333</v>
+        <v>1.074109767469357</v>
       </c>
       <c r="H15" t="n">
-        <v>2.679818204781265</v>
+        <v>2.239009909050603</v>
       </c>
     </row>
     <row r="16">
@@ -1782,20 +1782,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.7684897835723414</v>
+        <v>0.8370011472178656</v>
       </c>
       <c r="F18" t="n">
-        <v>7.120289380208334</v>
+        <v>5.013165372826788</v>
       </c>
       <c r="G18" t="n">
-        <v>1.178119791666667</v>
+        <v>1.074109767469357</v>
       </c>
       <c r="H18" t="n">
-        <v>2.668387037183387</v>
+        <v>2.239009909050603</v>
       </c>
     </row>
     <row r="19">
@@ -1888,16 +1888,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.7689197068574851</v>
+        <v>0.836660225104804</v>
       </c>
       <c r="F21" t="n">
-        <v>7.107066731770833</v>
+        <v>5.023650716145833</v>
       </c>
       <c r="G21" t="n">
-        <v>1.187213541666667</v>
+        <v>1.09015625</v>
       </c>
       <c r="H21" t="n">
-        <v>2.665908237687643</v>
+        <v>2.241350199354361</v>
       </c>
     </row>
     <row r="22">
@@ -1990,16 +1990,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.7708161427715885</v>
+        <v>0.8348522058453867</v>
       </c>
       <c r="F24" t="n">
-        <v>7.048740266927084</v>
+        <v>5.079257853190104</v>
       </c>
       <c r="G24" t="n">
-        <v>1.1812890625</v>
+        <v>1.096100260416667</v>
       </c>
       <c r="H24" t="n">
-        <v>2.654946377410867</v>
+        <v>2.253720890702774</v>
       </c>
     </row>
     <row r="25">
@@ -2099,16 +2099,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.60794876394004</v>
+        <v>13.91403651561131</v>
       </c>
       <c r="C2" t="n">
-        <v>3.82203463667456</v>
+        <v>3.730152344826055</v>
       </c>
       <c r="D2" t="n">
-        <v>2.450784007202378</v>
+        <v>2.445973981812569</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5250348406759622</v>
+        <v>0.5475968134012457</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2133,16 +2133,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.384395011718749</v>
+        <v>5.065754947916666</v>
       </c>
       <c r="C3" t="n">
-        <v>2.717424334129425</v>
+        <v>2.250723205531206</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2092265625</v>
+        <v>1.091197916666667</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7599026112474786</v>
+        <v>0.8352912414456735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2167,16 +2167,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.277236195052044</v>
+        <v>5.896989963831719</v>
       </c>
       <c r="C4" t="n">
-        <v>2.697635296894679</v>
+        <v>2.42837187511133</v>
       </c>
       <c r="D4" t="n">
-        <v>1.226473334554635</v>
+        <v>1.169644306329891</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7633867899815057</v>
+        <v>0.8082643345096086</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2201,16 +2201,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.897482110004605</v>
+        <v>5.56198505153198</v>
       </c>
       <c r="C5" t="n">
-        <v>3.14602640008068</v>
+        <v>2.358386111630574</v>
       </c>
       <c r="D5" t="n">
-        <v>1.356159440869457</v>
+        <v>1.187743622503149</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6781916993787966</v>
+        <v>0.8191567372771731</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.755208333333334</v>
+        <v>9.475260416666666</v>
       </c>
       <c r="C6" t="n">
-        <v>2.958920129596832</v>
+        <v>3.078191094891067</v>
       </c>
       <c r="D6" t="n">
-        <v>1.375</v>
+        <v>1.4765625</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7153317698360269</v>
+        <v>0.6919198823760808</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2609,16 +2609,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13.48114083660913</v>
+        <v>12.74180102904483</v>
       </c>
       <c r="C17" t="n">
-        <v>3.671667310175192</v>
+        <v>3.569565944067266</v>
       </c>
       <c r="D17" t="n">
-        <v>2.327680511277916</v>
+        <v>2.330081840530846</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5616720520586753</v>
+        <v>0.5857110636385369</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2643,16 +2643,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.315750317708333</v>
+        <v>5.091622989908855</v>
       </c>
       <c r="C18" t="n">
-        <v>2.704764373787176</v>
+        <v>2.256462494682518</v>
       </c>
       <c r="D18" t="n">
-        <v>1.209526041666667</v>
+        <v>1.09474609375</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7621345356986301</v>
+        <v>0.8344501638320561</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2677,16 +2677,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.277808114731106</v>
+        <v>5.853000057075814</v>
       </c>
       <c r="C19" t="n">
-        <v>2.697741298703622</v>
+        <v>2.419297430469394</v>
       </c>
       <c r="D19" t="n">
-        <v>1.227003489121217</v>
+        <v>1.169847477459873</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7633681944944954</v>
+        <v>0.8096946293038061</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,16 +2711,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.897482110004605</v>
+        <v>5.56198505153198</v>
       </c>
       <c r="C20" t="n">
-        <v>3.14602640008068</v>
+        <v>2.358386111630574</v>
       </c>
       <c r="D20" t="n">
-        <v>1.356159440869457</v>
+        <v>1.187743622503149</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6781916993787966</v>
+        <v>0.8191567372771731</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2745,16 +2745,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.12890625</v>
+        <v>9.440104166666666</v>
       </c>
       <c r="C21" t="n">
-        <v>3.021407991317955</v>
+        <v>3.072475250781797</v>
       </c>
       <c r="D21" t="n">
-        <v>1.388020833333333</v>
+        <v>1.46875</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7031812965973205</v>
+        <v>0.6930629582556802</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3119,16 +3119,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>14.62754429687408</v>
+        <v>13.9330943842419</v>
       </c>
       <c r="C32" t="n">
-        <v>3.824597272507797</v>
+        <v>3.732706040427226</v>
       </c>
       <c r="D32" t="n">
-        <v>2.449263688889946</v>
+        <v>2.443907239918674</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5243977084151321</v>
+        <v>0.5469771628427191</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3153,16 +3153,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7.181425610677084</v>
+        <v>5.125802473958334</v>
       </c>
       <c r="C33" t="n">
-        <v>2.679818204781265</v>
+        <v>2.264023514444657</v>
       </c>
       <c r="D33" t="n">
-        <v>1.184356770833333</v>
+        <v>1.093880208333333</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7665019904937718</v>
+        <v>0.8333388466752456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7.338588243826723</v>
+        <v>5.782931778991105</v>
       </c>
       <c r="C34" t="n">
-        <v>2.708982879943453</v>
+        <v>2.404772708384538</v>
       </c>
       <c r="D34" t="n">
-        <v>1.242082918155629</v>
+        <v>1.184504384191723</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7613919797523615</v>
+        <v>0.8119728403929781</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3221,16 +3221,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9.04606133796708</v>
+        <v>5.013165372826788</v>
       </c>
       <c r="C35" t="n">
-        <v>3.007667092277182</v>
+        <v>2.239009909050603</v>
       </c>
       <c r="D35" t="n">
-        <v>1.33464218857777</v>
+        <v>1.074109767469357</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7058749291859038</v>
+        <v>0.8370011472178656</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9.416666666666666</v>
+        <v>9.868489583333334</v>
       </c>
       <c r="C36" t="n">
-        <v>3.068658773253661</v>
+        <v>3.141415219822641</v>
       </c>
       <c r="D36" t="n">
-        <v>1.432291666666667</v>
+        <v>1.4609375</v>
       </c>
       <c r="E36" t="n">
-        <v>0.69382500884208</v>
+        <v>0.6791343669820415</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3629,16 +3629,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>13.50822095005087</v>
+        <v>12.7674922675529</v>
       </c>
       <c r="C47" t="n">
-        <v>3.675353173512836</v>
+        <v>3.573162782123549</v>
       </c>
       <c r="D47" t="n">
-        <v>2.327165953683237</v>
+        <v>2.329059453452995</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5607915649620119</v>
+        <v>0.5848757346413995</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3663,16 +3663,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7.120289380208334</v>
+        <v>5.148455281575521</v>
       </c>
       <c r="C48" t="n">
-        <v>2.668387037183387</v>
+        <v>2.26902077592417</v>
       </c>
       <c r="D48" t="n">
-        <v>1.178119791666667</v>
+        <v>1.095162760416666</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7684897835723414</v>
+        <v>0.8326023097012392</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3697,16 +3697,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7.338588243826723</v>
+        <v>5.735743997122751</v>
       </c>
       <c r="C49" t="n">
-        <v>2.708982879943453</v>
+        <v>2.394941334797734</v>
       </c>
       <c r="D49" t="n">
-        <v>1.242082918155629</v>
+        <v>1.206632241081802</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7613919797523615</v>
+        <v>0.8135071114049751</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3731,16 +3731,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9.04606133796708</v>
+        <v>5.013165372826788</v>
       </c>
       <c r="C50" t="n">
-        <v>3.007667092277182</v>
+        <v>2.239009909050603</v>
       </c>
       <c r="D50" t="n">
-        <v>1.33464218857777</v>
+        <v>1.074109767469357</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7058749291859038</v>
+        <v>0.8370011472178656</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3765,16 +3765,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>9.352864583333334</v>
+        <v>9.80859375</v>
       </c>
       <c r="C51" t="n">
-        <v>3.058245343875035</v>
+        <v>3.131867454091887</v>
       </c>
       <c r="D51" t="n">
-        <v>1.4140625</v>
+        <v>1.440104166666667</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6958994798828346</v>
+        <v>0.6810818295917296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4139,16 +4139,16 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>14.66075845287511</v>
+        <v>13.97049005525031</v>
       </c>
       <c r="C62" t="n">
-        <v>3.828936987321039</v>
+        <v>3.737711874295598</v>
       </c>
       <c r="D62" t="n">
-        <v>2.453247114415234</v>
+        <v>2.445259063909666</v>
       </c>
       <c r="E62" t="n">
-        <v>0.5233177780873517</v>
+        <v>0.5457612740738328</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4173,16 +4173,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>7.107066731770833</v>
+        <v>5.023650716145833</v>
       </c>
       <c r="C63" t="n">
-        <v>2.665908237687643</v>
+        <v>2.241350199354361</v>
       </c>
       <c r="D63" t="n">
-        <v>1.187213541666667</v>
+        <v>1.09015625</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7689197068574851</v>
+        <v>0.836660225104804</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -4207,16 +4207,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>7.64877452991</v>
+        <v>5.685269249311088</v>
       </c>
       <c r="C64" t="n">
-        <v>2.765641793492064</v>
+        <v>2.384380265249461</v>
       </c>
       <c r="D64" t="n">
-        <v>1.287068127821274</v>
+        <v>1.201513333607042</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7513065337277043</v>
+        <v>0.8151482553481539</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4241,16 +4241,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>9.159287975851562</v>
+        <v>5.263494097740407</v>
       </c>
       <c r="C65" t="n">
-        <v>3.026431558098012</v>
+        <v>2.294230611281352</v>
       </c>
       <c r="D65" t="n">
-        <v>1.323886393965703</v>
+        <v>1.149518503727298</v>
       </c>
       <c r="E65" t="n">
-        <v>0.7021934603519439</v>
+        <v>0.8288619194157062</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>9.143229166666666</v>
+        <v>8.180989583333334</v>
       </c>
       <c r="C66" t="n">
-        <v>3.023777301103153</v>
+        <v>2.860242923832403</v>
       </c>
       <c r="D66" t="n">
-        <v>1.380208333333333</v>
+        <v>1.393229166666667</v>
       </c>
       <c r="E66" t="n">
-        <v>0.7027155990167431</v>
+        <v>0.7340020092028192</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4649,16 +4649,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>13.54405338304514</v>
+        <v>12.79610124920624</v>
       </c>
       <c r="C77" t="n">
-        <v>3.680224637579226</v>
+        <v>3.577163855515461</v>
       </c>
       <c r="D77" t="n">
-        <v>2.329489702574353</v>
+        <v>2.330287914262844</v>
       </c>
       <c r="E77" t="n">
-        <v>0.5596265035614609</v>
+        <v>0.5839455376816032</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4683,16 +4683,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>7.048740266927084</v>
+        <v>5.079257853190104</v>
       </c>
       <c r="C78" t="n">
-        <v>2.654946377410867</v>
+        <v>2.253720890702774</v>
       </c>
       <c r="D78" t="n">
-        <v>1.1812890625</v>
+        <v>1.096100260416667</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7708161427715885</v>
+        <v>0.8348522058453867</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4717,16 +4717,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7.64877452991</v>
+        <v>5.756730743914223</v>
       </c>
       <c r="C79" t="n">
-        <v>2.765641793492064</v>
+        <v>2.399318808310855</v>
       </c>
       <c r="D79" t="n">
-        <v>1.287068127821274</v>
+        <v>1.220251109563332</v>
       </c>
       <c r="E79" t="n">
-        <v>0.7513065337277043</v>
+        <v>0.8128247449964817</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4751,16 +4751,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>9.159287975851562</v>
+        <v>5.263494097740407</v>
       </c>
       <c r="C80" t="n">
-        <v>3.026431558098012</v>
+        <v>2.294230611281352</v>
       </c>
       <c r="D80" t="n">
-        <v>1.323886393965703</v>
+        <v>1.149518503727298</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7021934603519439</v>
+        <v>0.8288619194157062</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4785,16 +4785,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>9.220052083333334</v>
+        <v>8.092447916666666</v>
       </c>
       <c r="C81" t="n">
-        <v>3.036453866491855</v>
+        <v>2.844722818952079</v>
       </c>
       <c r="D81" t="n">
-        <v>1.393229166666667</v>
+        <v>1.372395833333333</v>
       </c>
       <c r="E81" t="n">
-        <v>0.7002177665390996</v>
+        <v>0.7368808669736625</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -5159,16 +5159,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>14.94827431030217</v>
+        <v>13.76629646971218</v>
       </c>
       <c r="C92" t="n">
-        <v>3.866299821573874</v>
+        <v>3.71029600836809</v>
       </c>
       <c r="D92" t="n">
-        <v>2.495309613221678</v>
+        <v>2.439560340245118</v>
       </c>
       <c r="E92" t="n">
-        <v>0.5341256147346998</v>
+        <v>0.5524004566486973</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5193,16 +5193,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>7.708303367904539</v>
+        <v>5.115532430013021</v>
       </c>
       <c r="C93" t="n">
-        <v>2.776383145011606</v>
+        <v>2.261754281528615</v>
       </c>
       <c r="D93" t="n">
-        <v>1.224106167056987</v>
+        <v>1.10529296875</v>
       </c>
       <c r="E93" t="n">
-        <v>0.7597648385080793</v>
+        <v>0.8336727685103763</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5227,16 +5227,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>7.678242188228045</v>
+        <v>6.176123219613963</v>
       </c>
       <c r="C94" t="n">
-        <v>2.770964126117125</v>
+        <v>2.485180721721051</v>
       </c>
       <c r="D94" t="n">
-        <v>1.28388548304942</v>
+        <v>1.237245725325212</v>
       </c>
       <c r="E94" t="n">
-        <v>0.7607017181311997</v>
+        <v>0.7991885516295013</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5261,16 +5261,16 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>10.24551051609158</v>
+        <v>6.019129328030568</v>
       </c>
       <c r="C95" t="n">
-        <v>3.200860902334181</v>
+        <v>2.453391393159797</v>
       </c>
       <c r="D95" t="n">
-        <v>1.373448728780005</v>
+        <v>1.160203012828579</v>
       </c>
       <c r="E95" t="n">
-        <v>0.6806908400039355</v>
+        <v>0.8042930758809059</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5295,16 +5295,16 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>9.254098360655737</v>
+        <v>7.203125</v>
       </c>
       <c r="C96" t="n">
-        <v>3.042054956876311</v>
+        <v>2.683863819197986</v>
       </c>
       <c r="D96" t="n">
-        <v>1.502732240437158</v>
+        <v>1.380208333333333</v>
       </c>
       <c r="E96" t="n">
-        <v>0.7115889569952663</v>
+        <v>0.7657964531131618</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5329,16 +5329,16 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>14.3507287695129</v>
+        <v>13.87265249496716</v>
       </c>
       <c r="C97" t="n">
-        <v>3.788235574711913</v>
+        <v>3.724600984664955</v>
       </c>
       <c r="D97" t="n">
-        <v>2.471510011728463</v>
+        <v>2.420509662653716</v>
       </c>
       <c r="E97" t="n">
-        <v>0.5527485778744226</v>
+        <v>0.5489423800017558</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5363,16 +5363,16 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>6.666466564207651</v>
+        <v>6.562653548177084</v>
       </c>
       <c r="C98" t="n">
-        <v>2.58195014750627</v>
+        <v>2.56176766085004</v>
       </c>
       <c r="D98" t="n">
-        <v>1.15957650273224</v>
+        <v>1.1729296875</v>
       </c>
       <c r="E98" t="n">
-        <v>0.792234478173077</v>
+        <v>0.7866208433183421</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5397,16 +5397,16 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>8.287833824785851</v>
+        <v>8.009253332519807</v>
       </c>
       <c r="C99" t="n">
-        <v>2.878859813326424</v>
+        <v>2.830062425551742</v>
       </c>
       <c r="D99" t="n">
-        <v>1.329805644994232</v>
+        <v>1.323560415327578</v>
       </c>
       <c r="E99" t="n">
-        <v>0.7417033292169348</v>
+        <v>0.7395858688567298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5431,16 +5431,16 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>7.38855596434879</v>
+        <v>7.327002620779894</v>
       </c>
       <c r="C100" t="n">
-        <v>2.718189832287067</v>
+        <v>2.706843663897103</v>
       </c>
       <c r="D100" t="n">
-        <v>1.276165604423903</v>
+        <v>1.300399789427047</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7697300105392781</v>
+        <v>0.7617686765347249</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5465,16 +5465,16 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>6.953551912568306</v>
+        <v>7.127604166666667</v>
       </c>
       <c r="C101" t="n">
-        <v>2.636958837860065</v>
+        <v>2.669757323553335</v>
       </c>
       <c r="D101" t="n">
-        <v>1.207650273224044</v>
+        <v>1.265625</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7832872440368919</v>
+        <v>0.7682519494471164</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -5499,16 +5499,16 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>14.55867869860561</v>
+        <v>14.05633128457117</v>
       </c>
       <c r="C102" t="n">
-        <v>3.815583664212542</v>
+        <v>3.749177414389878</v>
       </c>
       <c r="D102" t="n">
-        <v>2.514117722757477</v>
+        <v>2.461773244413503</v>
       </c>
       <c r="E102" t="n">
-        <v>0.5462676595174947</v>
+        <v>0.5429702187504737</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -5533,16 +5533,16 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>4.891569721311476</v>
+        <v>4.812175697916667</v>
       </c>
       <c r="C103" t="n">
-        <v>2.211689336527957</v>
+        <v>2.193667180298021</v>
       </c>
       <c r="D103" t="n">
-        <v>1.115863387978142</v>
+        <v>1.12228125</v>
       </c>
       <c r="E103" t="n">
-        <v>0.8475504938166822</v>
+        <v>0.843536157335222</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -5567,16 +5567,16 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>7.111226623936073</v>
+        <v>6.947593417890073</v>
       </c>
       <c r="C104" t="n">
-        <v>2.666688325233392</v>
+        <v>2.635828791460112</v>
       </c>
       <c r="D104" t="n">
-        <v>1.337683242048498</v>
+        <v>1.337667319797364</v>
       </c>
       <c r="E104" t="n">
-        <v>0.7783731912368494</v>
+        <v>0.7741048474380903</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -5601,16 +5601,16 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>4.124780603089613</v>
+        <v>4.108910975744135</v>
       </c>
       <c r="C105" t="n">
-        <v>2.030955588655157</v>
+        <v>2.027044887451715</v>
       </c>
       <c r="D105" t="n">
-        <v>1.081322766388076</v>
+        <v>1.081957858672392</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8714480623028008</v>
+        <v>0.8664022178760558</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -5635,16 +5635,16 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>7.853825136612022</v>
+        <v>7.875</v>
       </c>
       <c r="C106" t="n">
-        <v>2.802467686988027</v>
+        <v>2.806243040080456</v>
       </c>
       <c r="D106" t="n">
-        <v>1.37431693989071</v>
+        <v>1.369791666666667</v>
       </c>
       <c r="E106" t="n">
-        <v>0.7552295414475622</v>
+        <v>0.7439510029697041</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -5669,16 +5669,16 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>13.73486255045933</v>
+        <v>12.53775242113775</v>
       </c>
       <c r="C107" t="n">
-        <v>3.706057548185042</v>
+        <v>3.540868879404849</v>
       </c>
       <c r="D107" t="n">
-        <v>2.359791975084253</v>
+        <v>2.317662342011924</v>
       </c>
       <c r="E107" t="n">
-        <v>0.5719425189442293</v>
+        <v>0.5923455323877479</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -5703,16 +5703,16 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>7.684071537303446</v>
+        <v>5.12874961751302</v>
       </c>
       <c r="C108" t="n">
-        <v>2.77201578951193</v>
+        <v>2.264674285082299</v>
       </c>
       <c r="D108" t="n">
-        <v>1.221291959406714</v>
+        <v>1.104407552083333</v>
       </c>
       <c r="E108" t="n">
-        <v>0.7605200420152398</v>
+        <v>0.8332430227830193</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -5737,16 +5737,16 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>7.681398184523484</v>
+        <v>6.143960426417496</v>
       </c>
       <c r="C109" t="n">
-        <v>2.771533543820728</v>
+        <v>2.478701358860622</v>
       </c>
       <c r="D109" t="n">
-        <v>1.286100831315334</v>
+        <v>1.239600762762587</v>
       </c>
       <c r="E109" t="n">
-        <v>0.7606033590963361</v>
+        <v>0.8002342977805678</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -5771,16 +5771,16 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>10.24551051609158</v>
+        <v>6.019129328030568</v>
       </c>
       <c r="C110" t="n">
-        <v>3.200860902334181</v>
+        <v>2.453391393159797</v>
       </c>
       <c r="D110" t="n">
-        <v>1.373448728780005</v>
+        <v>1.160203012828579</v>
       </c>
       <c r="E110" t="n">
-        <v>0.6806908400039355</v>
+        <v>0.8042930758809059</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5805,16 +5805,16 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>9.209016393442623</v>
+        <v>7.203125</v>
       </c>
       <c r="C111" t="n">
-        <v>3.034636122081628</v>
+        <v>2.683863819197986</v>
       </c>
       <c r="D111" t="n">
-        <v>1.494535519125683</v>
+        <v>1.380208333333333</v>
       </c>
       <c r="E111" t="n">
-        <v>0.7129939709337305</v>
+        <v>0.7657964531131618</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -5839,16 +5839,16 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>12.71181801929431</v>
+        <v>12.31517698817004</v>
       </c>
       <c r="C112" t="n">
-        <v>3.565363658772315</v>
+        <v>3.509298646192718</v>
       </c>
       <c r="D112" t="n">
-        <v>2.307818342830007</v>
+        <v>2.262989260909706</v>
       </c>
       <c r="E112" t="n">
-        <v>0.6038264830836254</v>
+        <v>0.5995823852607594</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -5873,16 +5873,16 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>6.752357957650273</v>
+        <v>6.646635319010417</v>
       </c>
       <c r="C113" t="n">
-        <v>2.598529960891402</v>
+        <v>2.578106925441693</v>
       </c>
       <c r="D113" t="n">
-        <v>1.163811475409836</v>
+        <v>1.177513020833333</v>
       </c>
       <c r="E113" t="n">
-        <v>0.7895576072989532</v>
+        <v>0.7838902467226974</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5907,16 +5907,16 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>8.288956617139855</v>
+        <v>8.010323493982217</v>
       </c>
       <c r="C114" t="n">
-        <v>2.879054813153069</v>
+        <v>2.830251489529193</v>
       </c>
       <c r="D114" t="n">
-        <v>1.330596416089928</v>
+        <v>1.324314119028163</v>
       </c>
       <c r="E114" t="n">
-        <v>0.7416683365357166</v>
+        <v>0.7395510734574777</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5941,16 +5941,16 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>7.38855596434879</v>
+        <v>7.327002620779894</v>
       </c>
       <c r="C115" t="n">
-        <v>2.718189832287067</v>
+        <v>2.706843663897103</v>
       </c>
       <c r="D115" t="n">
-        <v>1.276165604423903</v>
+        <v>1.300399789427047</v>
       </c>
       <c r="E115" t="n">
-        <v>0.7697300105392781</v>
+        <v>0.7617686765347249</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -5975,16 +5975,16 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>6.8224043715847</v>
+        <v>7.002604166666667</v>
       </c>
       <c r="C116" t="n">
-        <v>2.611973271606105</v>
+        <v>2.646243406541935</v>
       </c>
       <c r="D116" t="n">
-        <v>1.19672131147541</v>
+        <v>1.255208333333333</v>
       </c>
       <c r="E116" t="n">
-        <v>0.787374557312424</v>
+        <v>0.772316219241248</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -6009,16 +6009,16 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>13.11534861965564</v>
+        <v>12.71046696320333</v>
       </c>
       <c r="C117" t="n">
-        <v>3.621511924549695</v>
+        <v>3.565174184132289</v>
       </c>
       <c r="D117" t="n">
-        <v>2.372963587099203</v>
+        <v>2.333089836208065</v>
       </c>
       <c r="E117" t="n">
-        <v>0.5912501437365807</v>
+        <v>0.5867298644171525</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -6043,16 +6043,16 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>4.908395950819672</v>
+        <v>4.827398354166667</v>
       </c>
       <c r="C118" t="n">
-        <v>2.215490002419255</v>
+        <v>2.197134122935299</v>
       </c>
       <c r="D118" t="n">
-        <v>1.120125683060109</v>
+        <v>1.126135416666667</v>
       </c>
       <c r="E118" t="n">
-        <v>0.8470260915234316</v>
+        <v>0.8430412054793553</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -6077,16 +6077,16 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>7.111226623936073</v>
+        <v>6.947593417890073</v>
       </c>
       <c r="C119" t="n">
-        <v>2.666688325233392</v>
+        <v>2.635828791460112</v>
       </c>
       <c r="D119" t="n">
-        <v>1.337683242048498</v>
+        <v>1.337667319797364</v>
       </c>
       <c r="E119" t="n">
-        <v>0.7783731912368494</v>
+        <v>0.7741048474380903</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -6111,16 +6111,16 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>4.124780603089613</v>
+        <v>4.108910975744135</v>
       </c>
       <c r="C120" t="n">
-        <v>2.030955588655157</v>
+        <v>2.027044887451715</v>
       </c>
       <c r="D120" t="n">
-        <v>1.081322766388076</v>
+        <v>1.081957858672392</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8714480623028008</v>
+        <v>0.8664022178760558</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -6145,16 +6145,16 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>7.896174863387978</v>
+        <v>7.915364583333333</v>
       </c>
       <c r="C121" t="n">
-        <v>2.810013320855967</v>
+        <v>2.813425773560293</v>
       </c>
       <c r="D121" t="n">
-        <v>1.39344262295082</v>
+        <v>1.388020833333333</v>
       </c>
       <c r="E121" t="n">
-        <v>0.7539096798690049</v>
+        <v>0.742638582515349</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -6240,16 +6240,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7684014337337335</v>
+        <v>0.7625833435452005</v>
       </c>
       <c r="E2" t="n">
-        <v>7.431185332177795</v>
+        <v>7.301946858867508</v>
       </c>
       <c r="F2" t="n">
-        <v>1.461107580309341</v>
+        <v>1.453374252935564</v>
       </c>
       <c r="G2" t="n">
-        <v>2.668931832342693</v>
+        <v>2.647721551907941</v>
       </c>
     </row>
     <row r="3">
@@ -6313,36 +6313,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7597737896642778</v>
+        <v>0.759473054982568</v>
       </c>
       <c r="E5" t="n">
-        <v>7.70801615671096</v>
+        <v>7.397606372143528</v>
       </c>
       <c r="F5" t="n">
-        <v>1.484660811812581</v>
+        <v>1.433710724260695</v>
       </c>
       <c r="G5" t="n">
-        <v>2.705476920323415</v>
+        <v>2.673831396952504</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6352,31 +6352,31 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7588234559079498</v>
+        <v>0.7591824763890805</v>
       </c>
       <c r="E6" t="n">
-        <v>7.417585332311118</v>
+        <v>7.406543358619767</v>
       </c>
       <c r="F6" t="n">
-        <v>1.474271432047075</v>
+        <v>1.440416400603951</v>
       </c>
       <c r="G6" t="n">
-        <v>2.670403692621864</v>
+        <v>2.684299947141111</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6385,22 +6385,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7541928888739091</v>
+        <v>0.7588234559079498</v>
       </c>
       <c r="E7" t="n">
-        <v>7.56000227522441</v>
+        <v>7.417585332311118</v>
       </c>
       <c r="F7" t="n">
-        <v>1.474694267909985</v>
+        <v>1.474271432047075</v>
       </c>
       <c r="G7" t="n">
-        <v>2.682392262736036</v>
+        <v>2.670403692621864</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6414,22 +6414,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.752499335738111</v>
+        <v>0.7541928888739091</v>
       </c>
       <c r="E8" t="n">
-        <v>7.612088911372538</v>
+        <v>7.56000227522441</v>
       </c>
       <c r="F8" t="n">
-        <v>1.493318797654427</v>
+        <v>1.474694267909985</v>
       </c>
       <c r="G8" t="n">
-        <v>2.693331512129927</v>
+        <v>2.682392262736036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6443,196 +6443,196 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7503464079802475</v>
+        <v>0.7541928888739091</v>
       </c>
       <c r="E9" t="n">
-        <v>7.678303996336015</v>
+        <v>7.56000227522441</v>
       </c>
       <c r="F9" t="n">
-        <v>1.496554686975512</v>
+        <v>1.474694267909985</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7055008119037</v>
+        <v>2.682392262736036</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7384313989539995</v>
+        <v>0.752499335738111</v>
       </c>
       <c r="E10" t="n">
-        <v>8.392818586003585</v>
+        <v>7.612088911372538</v>
       </c>
       <c r="F10" t="n">
-        <v>1.455022630045817</v>
+        <v>1.493318797654427</v>
       </c>
       <c r="G10" t="n">
-        <v>2.874622307341991</v>
+        <v>2.693331512129927</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7319436368633315</v>
+        <v>0.7520867366290632</v>
       </c>
       <c r="E11" t="n">
-        <v>8.244296537711081</v>
+        <v>7.624778740356194</v>
       </c>
       <c r="F11" t="n">
-        <v>1.462879937893037</v>
+        <v>1.455935263582135</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8513450755519</v>
+        <v>2.703583174802635</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7318582799590385</v>
+        <v>0.7510702611565285</v>
       </c>
       <c r="E12" t="n">
-        <v>8.246921760340751</v>
+        <v>7.656041289473947</v>
       </c>
       <c r="F12" t="n">
-        <v>1.459459520639837</v>
+        <v>1.464502076096448</v>
       </c>
       <c r="G12" t="n">
-        <v>2.851317214600118</v>
+        <v>2.718897244795108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>zscore</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7314217202433815</v>
+        <v>0.7503464079802475</v>
       </c>
       <c r="E13" t="n">
-        <v>8.260348517721848</v>
+        <v>7.678303996336015</v>
       </c>
       <c r="F13" t="n">
-        <v>1.464084904706317</v>
+        <v>1.496554686975512</v>
       </c>
       <c r="G13" t="n">
-        <v>2.854148826320528</v>
+        <v>2.7055008119037</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.7279407279681209</v>
+        <v>0.7498136265114418</v>
       </c>
       <c r="E14" t="n">
-        <v>8.7294274070847</v>
+        <v>7.694690133815593</v>
       </c>
       <c r="F14" t="n">
-        <v>1.488941607420576</v>
+        <v>1.429013677817497</v>
       </c>
       <c r="G14" t="n">
-        <v>2.920838841138348</v>
+        <v>2.721600451197589</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.7214742162190524</v>
+        <v>0.7484151104614505</v>
       </c>
       <c r="E15" t="n">
-        <v>8.566292282783042</v>
+        <v>7.737702658845629</v>
       </c>
       <c r="F15" t="n">
-        <v>1.492709522129138</v>
+        <v>1.450233806848774</v>
       </c>
       <c r="G15" t="n">
-        <v>2.895841381991699</v>
+        <v>2.73523744632631</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6642,26 +6642,26 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.721360312483511</v>
+        <v>0.74168487282217</v>
       </c>
       <c r="E16" t="n">
-        <v>8.569795486965806</v>
+        <v>7.944696718670292</v>
       </c>
       <c r="F16" t="n">
-        <v>1.495804948216018</v>
+        <v>1.451467819982617</v>
       </c>
       <c r="G16" t="n">
-        <v>2.896906652148339</v>
+        <v>2.756385478425933</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6671,26 +6671,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>iqr</t>
+          <t>isolation_forest</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7210339436317338</v>
+        <v>0.7404458018019563</v>
       </c>
       <c r="E17" t="n">
-        <v>8.579833232622121</v>
+        <v>7.982805379111669</v>
       </c>
       <c r="F17" t="n">
-        <v>1.496604910981668</v>
+        <v>1.474224465462455</v>
       </c>
       <c r="G17" t="n">
-        <v>2.898606411703435</v>
+        <v>2.769164926398047</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6700,26 +6700,26 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.6984895474710907</v>
+        <v>0.7319436368633315</v>
       </c>
       <c r="E18" t="n">
-        <v>9.273204899077268</v>
+        <v>8.244296537711081</v>
       </c>
       <c r="F18" t="n">
-        <v>1.499214670416661</v>
+        <v>1.462879937893037</v>
       </c>
       <c r="G18" t="n">
-        <v>3.023727105358379</v>
+        <v>2.8513450755519</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6729,26 +6729,26 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.6973501461986943</v>
+        <v>0.7318582799590385</v>
       </c>
       <c r="E19" t="n">
-        <v>9.710971836364093</v>
+        <v>8.246921760340751</v>
       </c>
       <c r="F19" t="n">
-        <v>1.547033802742398</v>
+        <v>1.459459520639837</v>
       </c>
       <c r="G19" t="n">
-        <v>3.097020781186702</v>
+        <v>2.851317214600118</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6758,26 +6758,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.6968320813903595</v>
+        <v>0.7314217202433815</v>
       </c>
       <c r="E20" t="n">
-        <v>9.324181647813425</v>
+        <v>8.260348517721848</v>
       </c>
       <c r="F20" t="n">
-        <v>1.502992490705599</v>
+        <v>1.464084904706317</v>
       </c>
       <c r="G20" t="n">
-        <v>3.032739646614405</v>
+        <v>2.854148826320528</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6787,26 +6787,26 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6937095556455837</v>
+        <v>0.7314217202433815</v>
       </c>
       <c r="E21" t="n">
-        <v>9.420217525810633</v>
+        <v>8.260348517721848</v>
       </c>
       <c r="F21" t="n">
-        <v>1.501678063253718</v>
+        <v>1.464084904706317</v>
       </c>
       <c r="G21" t="n">
-        <v>3.048321474812925</v>
+        <v>2.854148826320528</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6816,26 +6816,26 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.6903983233378498</v>
+        <v>0.7214742162190524</v>
       </c>
       <c r="E22" t="n">
-        <v>9.522057231202329</v>
+        <v>8.566292282783042</v>
       </c>
       <c r="F22" t="n">
-        <v>1.528527446624669</v>
+        <v>1.492709522129138</v>
       </c>
       <c r="G22" t="n">
-        <v>3.057944844552671</v>
+        <v>2.895841381991699</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6845,20 +6845,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.6896906156082456</v>
+        <v>0.721360312483511</v>
       </c>
       <c r="E23" t="n">
-        <v>9.543823371414835</v>
+        <v>8.569795486965806</v>
       </c>
       <c r="F23" t="n">
-        <v>1.526324702240442</v>
+        <v>1.495804948216018</v>
       </c>
       <c r="G23" t="n">
-        <v>3.062139175540382</v>
+        <v>2.896906652148339</v>
       </c>
     </row>
     <row r="24">
@@ -6874,26 +6874,26 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6893743936746362</v>
+        <v>0.7210339436317338</v>
       </c>
       <c r="E24" t="n">
-        <v>9.966885748636415</v>
+        <v>8.579833232622121</v>
       </c>
       <c r="F24" t="n">
-        <v>1.57589644650905</v>
+        <v>1.496604910981668</v>
       </c>
       <c r="G24" t="n">
-        <v>3.13131259038262</v>
+        <v>2.898606411703435</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6903,20 +6903,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>isolation_forest</t>
+          <t>iqr</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.688369542223954</v>
+        <v>0.7210339436317338</v>
       </c>
       <c r="E25" t="n">
-        <v>9.584454082809753</v>
+        <v>8.579833232622121</v>
       </c>
       <c r="F25" t="n">
-        <v>1.523528669025294</v>
+        <v>1.496604910981668</v>
       </c>
       <c r="G25" t="n">
-        <v>3.068408159475235</v>
+        <v>2.898606411703435</v>
       </c>
     </row>
   </sheetData>
